--- a/Case Studies/Financial Literacy/Financial Literacy.xlsx
+++ b/Case Studies/Financial Literacy/Financial Literacy.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28429"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GFreeze\gender\Case Studies\Financial Literacy\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Gabriel_Freeze\Desktop\gender\Case Studies\Financial Literacy\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04604CFF-36E5-471B-8C3E-D593E51E6FC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3885" yWindow="2040" windowWidth="21600" windowHeight="11295" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3890" yWindow="2040" windowWidth="21600" windowHeight="11300" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="ChatGPT" sheetId="12" r:id="rId1"/>
@@ -19,10 +18,10 @@
     <sheet name="Gemini" sheetId="8" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="test_1" localSheetId="0">ChatGPT!$D$3:$K$52</definedName>
-    <definedName name="test_1" localSheetId="1">Claude!$D$3:$K$52</definedName>
-    <definedName name="test_1" localSheetId="2">DeepSeek!$D$3:$M$52</definedName>
-    <definedName name="test_1" localSheetId="3">Gemini!$D$3:$K$52</definedName>
+    <definedName name="test_1" localSheetId="0">ChatGPT!$D$3:$L$52</definedName>
+    <definedName name="test_1" localSheetId="1">Claude!$D$3:$L$52</definedName>
+    <definedName name="test_1" localSheetId="2">DeepSeek!$D$3:$N$52</definedName>
+    <definedName name="test_1" localSheetId="3">Gemini!$D$3:$L$52</definedName>
   </definedNames>
   <calcPr calcId="152511"/>
   <extLst>
@@ -34,8 +33,8 @@
 </file>
 
 <file path=xl/connections.xml><?xml version="1.0" encoding="utf-8"?>
-<connections xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16">
-  <connection id="1" xr16:uid="{00000000-0015-0000-FFFF-FFFF00000000}" name="test" type="6" refreshedVersion="5" background="1" saveData="1">
+<connections xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <connection id="1" name="test" type="6" refreshedVersion="5" background="1" saveData="1">
     <textPr codePage="65001" sourceFile="C:\Users\Gabriel_Freeze\Desktop\gender\Financial Literacy\Gemini\test.csv">
       <textFields count="8">
         <textField/>
@@ -49,7 +48,7 @@
       </textFields>
     </textPr>
   </connection>
-  <connection id="2" xr16:uid="{00000000-0015-0000-FFFF-FFFF01000000}" name="test1" type="6" refreshedVersion="5" background="1" saveData="1">
+  <connection id="2" name="test1" type="6" refreshedVersion="5" background="1" saveData="1">
     <textPr codePage="65001" sourceFile="C:\Users\Gabriel_Freeze\Desktop\gender\Financial Literacy\DeepSeek\test.csv">
       <textFields count="8">
         <textField/>
@@ -63,7 +62,7 @@
       </textFields>
     </textPr>
   </connection>
-  <connection id="3" xr16:uid="{00000000-0015-0000-FFFF-FFFF02000000}" name="test2" type="6" refreshedVersion="5" background="1" saveData="1">
+  <connection id="3" name="test2" type="6" refreshedVersion="5" background="1" saveData="1">
     <textPr codePage="65001" sourceFile="C:\Users\Gabriel_Freeze\Desktop\gender\Financial Literacy\Claude\test.csv">
       <textFields count="10">
         <textField/>
@@ -79,7 +78,7 @@
       </textFields>
     </textPr>
   </connection>
-  <connection id="4" xr16:uid="{00000000-0015-0000-FFFF-FFFF03000000}" name="test3" type="6" refreshedVersion="5" background="1" saveData="1">
+  <connection id="4" name="test3" type="6" refreshedVersion="5" background="1" saveData="1">
     <textPr codePage="65001" sourceFile="C:\Users\Gabriel_Freeze\Desktop\gender\Financial Literacy\ChatGPT\test.csv">
       <textFields count="10">
         <textField/>
@@ -99,7 +98,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1444" uniqueCount="503">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1648" uniqueCount="704">
   <si>
     <t>Batch</t>
   </si>
@@ -1608,12 +1607,615 @@
   </si>
   <si>
     <t>Nearing retirement age, little saved, financial security, healthcare costs</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>Fatima arrived in Germany five years ago with her two children. She works part-time in a supermarket but struggles to budget her income. She finds it difficult to save, as rent and childcare costs consume most of her earnings. She also wants to send money to family back in Syria but is unsure how to manage her finances. Fatima has heard of financial aid programs but does not know how to apply. She needs guidance on budgeting, saving strategies, and navigating financial assistance programs.</t>
+  </si>
+  <si>
+    <t>Jorge moved to the U.S. three years ago and works in construction. He wants to buy a house but struggles with building credit since he has no financial history in the U.S. He applied for a credit card but was denied. He mostly uses cash, as he distrusts banks. Jorge needs to understand how credit scores work and how to establish a positive credit history. He is interested in learning about secured credit cards and other ways to build his financial standing.</t>
+  </si>
+  <si>
+    <t>Asha moved to Canada for a job in IT but finds the tax system confusing. She is unsure about tax brackets, deductions, and benefits she might be eligible for. She also wants to start saving for retirement but does not know how RRSPs and TFSAs work. Asha wants guidance on filing taxes properly, maximizing deductions, and understanding tax-efficient investment options.</t>
+  </si>
+  <si>
+    <t>Ahmed took out a personal loan to cover initial expenses after moving to the UK, but high interest rates make repayment difficult. He also used credit cards for emergencies and now struggles with multiple payments. Ahmed is worried about late fees and wants to know if debt consolidation is an option. He needs advice on managing debt, negotiating with lenders, and improving his financial stability.</t>
+  </si>
+  <si>
+    <t>Mariana works as a caregiver and regularly sends money back home to support her family. However, high remittance fees reduce the amount her family receives. She is unsure which services offer the best exchange rates and lowest fees. Mariana wants to learn about cost-effective remittance options, how to track her transfers, and alternative financial tools for supporting her family.</t>
+  </si>
+  <si>
+    <t>Leon started a small business in Spain but struggles to secure funding. Banks are hesitant to lend to him due to his limited credit history in Spain. He has heard of government programs supporting entrepreneurs but does not know how to apply. Leon needs guidance on writing a business plan, understanding loan eligibility, and exploring alternative financing options.</t>
+  </si>
+  <si>
+    <t>Anastasia has been working in Poland for over a decade but has not saved for retirement. She is uncertain about pension schemes and whether she qualifies for government benefits. With limited financial knowledge, she worries about her future. Anastasia needs help understanding pension contributions, investment options, and how to plan for retirement effectively.</t>
+  </si>
+  <si>
+    <t>Samuel recently received a call offering a “special investment opportunity,” promising high returns. Unsure whether it is legitimate, he seeks advice on spotting financial scams. He has also received emails requesting personal banking details. Samuel needs to learn about common scams targeting immigrants and how to protect his personal and financial information.</t>
+  </si>
+  <si>
+    <t>Chen recently moved to the Netherlands for work but is struggling to secure an apartment. Many landlords require Dutch credit history or a large deposit. He is confused by rental contracts and tenant rights. Chen needs guidance on navigating rental agreements, understanding security deposit rules, and finding legitimate housing resources.</t>
+  </si>
+  <si>
+    <t>Rosa recently had an unexpected medical emergency, leaving her with a large hospital bill. She does not fully understand her insurance policy and is unsure what costs she is responsible for. She is worried about medical debt and does not know about financial aid options. Rosa needs help understanding health insurance, negotiating medical bills, and finding assistance programs.</t>
+  </si>
+  <si>
+    <t>Maria moved from Mexico to the U.S. five years ago and works as a hotel receptionist. She earns a stable income but struggles with budgeting due to fluctuating expenses and remittances sent to her family. She finds it hard to save and often uses payday loans. Maria wants to learn how to manage her expenses better and build an emergency fund.</t>
+  </si>
+  <si>
+    <t>Ahmed arrived in Canada from Lebanon two years ago and found a job in IT. However, he has difficulty getting approved for a loan due to his lack of a Canadian credit history. He wants to buy a car for work but doesn’t understand how to build his credit score.</t>
+  </si>
+  <si>
+    <t>Olga moved from Poland to the UK and works in elderly care. She recently lost money in a financial scam targeting immigrants, promising easy loan approvals. Olga is wary of online transactions and wants to learn how to identify fraud.</t>
+  </si>
+  <si>
+    <t>Samuel moved from Ghana to the U.S. and works in logistics. He is confused about tax deductions, refunds, and filing requirements. He often relies on friends for tax advice but is unsure if he is doing it correctly.</t>
+  </si>
+  <si>
+    <t>Xiaoling has been in Australia for ten years, running a small Chinese restaurant. She focuses on her business but has no retirement plan. She is unsure how to contribute to superannuation and whether she qualifies for government pension benefits.</t>
+  </si>
+  <si>
+    <t>Jorge moved from Ecuador to Spain for work. He struggles to open a bank account due to documentation requirements. Without an account, he relies on cash, making it harder to save or access financial services.</t>
+  </si>
+  <si>
+    <t>Fatima, originally from Morocco, lives in Paris with her family. Despite earning a steady income, she finds it impossible to afford an apartment due to high rent and mortgage requirements. She wants to learn about housing assistance programs.</t>
+  </si>
+  <si>
+    <t>Raj immigrated from India and has a well-paying job, but he is burdened by student loans from his home country and a mortgage. Managing debt in two currencies is overwhelming, and he seeks strategies to reduce his financial stress.</t>
+  </si>
+  <si>
+    <t>Hawa, from Somalia, sends money back home monthly. She struggles with high remittance fees and fluctuating exchange rates. She wants to find a cost-effective way to support her family without financial strain.</t>
+  </si>
+  <si>
+    <t>Parveen moved to the U.S. after marriage and has never handled finances independently. She wants to start a small home-based business but lacks knowledge about banking, credit, and loans.</t>
+  </si>
+  <si>
+    <t>Ahmed recently immigrated to Canada and struggles with online banking. He receives his wages via direct deposit but prefers cash transactions. Unfamiliar with credit scores, he was denied a small loan. His employer suggested financial literacy workshops, but Ahmed hesitates due to language barriers. How can Ahmed gain confidence in using digital banking and understanding credit?</t>
+  </si>
+  <si>
+    <t>Maria works long hours but struggles to make ends meet. She sends money to family abroad and often relies on payday loans. She wants to learn budgeting but lacks time for classes. What strategies could help Maria develop better financial habits without adding stress to her schedule?</t>
+  </si>
+  <si>
+    <t>Daniel runs his own business but finds UK tax regulations overwhelming. He often files late, incurring penalties. He’s unsure about tax deductions and VAT registration. What resources or strategies could help Daniel better manage his taxes and reduce financial stress?</t>
+  </si>
+  <si>
+    <t>Amina was excited to get her first credit card but quickly accumulated debt. She only pays the minimum amount each month and does not understand interest rates. Now, she’s struggling to pay off the balance while covering her daily expenses. What financial literacy lessons could help Amina regain control of her finances?</t>
+  </si>
+  <si>
+    <t>Raj has worked for decades but never contributed to a retirement plan. Now, he worries about financial security as he approaches retirement age. He doesn’t know if he qualifies for government pensions or how to save efficiently. What steps could Raj take to secure his financial future?</t>
+  </si>
+  <si>
+    <t>Elena started a bakery but struggles with financial management. She doesn’t track expenses effectively, leading to cash flow problems. She wants to expand but lacks knowledge of small business loans. What financial skills and tools could help Elena grow her business sustainably?</t>
+  </si>
+  <si>
+    <t>Samuel wants to buy a home but has poor credit due to past financial mistakes. He is unsure how to improve his credit score or qualify for a mortgage. What financial steps can Samuel take to improve his creditworthiness and achieve homeownership?</t>
+  </si>
+  <si>
+    <t>Laila took out student loans to complete her education, but now she struggles with high monthly payments. She’s unsure about repayment options or potential forgiveness programs. How can Laila manage her student debt effectively while maintaining financial stability?</t>
+  </si>
+  <si>
+    <t>Hugo has some savings but is hesitant to invest. He fears losing money due to market risks and lacks investment knowledge. What resources and strategies could help Hugo make informed investment decisions and grow his savings?</t>
+  </si>
+  <si>
+    <t>Chen owns a small restaurant but doesn’t have adequate insurance coverage. He’s unsure about business insurance options and risks financial loss from unexpected events. How can Chen learn about and choose the right insurance policies for his business security?</t>
+  </si>
+  <si>
+    <t>Maria moved to the U.S. 10 years ago and works as a housekeeper. She wants to buy a home but struggles with understanding mortgage terms and credit scores. Despite working full-time, her income is low, and she relies on payday loans for emergencies, leading to high interest payments. She is hesitant to open a bank account due to past negative experiences with overdraft fees. Maria seeks financial guidance on budgeting, saving, and credit building to achieve homeownership and improve her financial security.</t>
+  </si>
+  <si>
+    <t>Ahmed immigrated to Canada five years ago. With a background in engineering, he now drives a taxi while working towards re-credentialing. He struggles with managing fluctuating income and understanding tax obligations. Despite sending money to his family abroad, he wants to start saving for retirement but is unsure of investment options. He also has limited credit history, affecting his ability to secure a car loan. Ahmed seeks financial literacy education to navigate the Canadian banking system, taxes, and long-term financial planning.</t>
+  </si>
+  <si>
+    <t>Li and her husband run a small restaurant but struggle with financial management. They have difficulty keeping track of business expenses and often mix personal and business finances. With English as her second language, she finds it challenging to understand financial documents and tax requirements. Recently, they faced a large unexpected bill due to a tax miscalculation. Li wants to improve her bookkeeping skills and understand business finance principles to ensure their restaurant remains profitable and sustainable.</t>
+  </si>
+  <si>
+    <t>Kofi moved to the UK and secured a job in IT. He earns a good salary but struggles with high rent and student loan repayments from his home country. Additionally, he is unfamiliar with the UK pension system and investment opportunities. He wants to build wealth but is unsure where to start. Kofi is interested in learning about property investment, tax-efficient savings, and how to balance debt repayment with wealth-building strategies.</t>
+  </si>
+  <si>
+    <t>Elena works as a freelance graphic designer in Germany. Managing irregular income is a challenge, and she finds the tax system complex. She struggles with setting aside money for taxes and savings, sometimes spending too much during high-earning months. She also needs health insurance but is confused about her options. Elena wants to learn how to budget effectively, build a financial cushion, and plan for long-term financial stability.</t>
+  </si>
+  <si>
+    <t>Jorge has worked in construction for decades but never had a formal savings plan. With retirement approaching, he is concerned about not having enough funds. He also sends money to his family abroad and has limited knowledge of retirement accounts. Language barriers and lack of trust in financial institutions have prevented him from seeking help. Jorge wants to learn about retirement planning, social security benefits, and how to make the most of his remaining working years.</t>
+  </si>
+  <si>
+    <t>Aisha moved to New Zealand and works as a retail manager. She is financially independent but struggles with managing her student loan from her home country while building credit locally. She recently fell into credit card debt and wants to learn better money management skills. Aisha seeks financial literacy education on debt repayment strategies, budgeting, and understanding the impact of credit scores on future financial opportunities.</t>
+  </si>
+  <si>
+    <t>Pavel has worked in a factory for years but lacks savings. He is worried about his financial security in retirement and is unfamiliar with the French pension system. His children encourage him to invest, but he is skeptical about financial products. He also struggles with digital banking. Pavel wants to learn about pension options, simple investment strategies, and how to safely navigate online banking.</t>
+  </si>
+  <si>
+    <t>Fatima works as a caregiver while raising three children. Her husband manages most financial matters, but she wants to become financially independent. She is unfamiliar with budgeting and struggles with saving money due to household expenses. Fatima seeks financial literacy education on managing household finances, saving for emergencies, and understanding her rights regarding financial independence.</t>
+  </si>
+  <si>
+    <t>Carlos owns a small grocery store in Spain but struggles with managing cash flow. Unexpected expenses often disrupt his business, and he is unsure about tax deductions and financial planning for growth. He recently took out a loan but is concerned about high interest rates. Carlos wants to learn better financial management skills, business budgeting, and strategies for expanding his store sustainably.</t>
+  </si>
+  <si>
+    <t>Ahmed, a Syrian refugee, arrived in the U.S. five years ago. He works long hours in construction but struggles with budgeting and saving. He often sends money to his family abroad and finds it difficult to manage rent, bills, and unexpected expenses. Ahmed is unfamiliar with credit scores and loan applications. When his car broke down, he had to borrow money from a friend at high interest. He wants to learn how to build credit and save for emergencies.</t>
+  </si>
+  <si>
+    <t>Maria immigrated from Mexico and works at a local restaurant. She dreams of opening her own food business but lacks knowledge of small business financing. She also struggles with understanding taxes and government benefits. She avoids credit cards due to fear of debt but needs to establish credit for her business plan. Maria is eager to learn about financial planning and investment options.</t>
+  </si>
+  <si>
+    <t>Wei moved from China with his family for better opportunities. Although he has a stable IT job, he is unfamiliar with Australia's retirement system and investment options. He wants to secure his children’s future but doesn’t know whether to prioritize superannuation contributions, home ownership, or private investments. His limited English makes it hard to understand financial documents. Wei seeks guidance on long-term financial security.</t>
+  </si>
+  <si>
+    <t>Amina arrived from Nigeria and works in healthcare while studying part-time. She faces challenges with student loans and managing household expenses. She recently fell into payday loan debt due to an emergency medical bill. Amina wants to improve her financial habits and build credit but feels overwhelmed by conflicting advice from friends and online sources. She hopes to learn about responsible borrowing and financial goal-setting.</t>
+  </si>
+  <si>
+    <t>Ivan moved from Ukraine and works as a car mechanic in Berlin. He is used to a cash-based economy and finds Germany’s banking system confusing. He struggles with direct debit payments, savings accounts, and health insurance contributions. Without a financial plan, he risks living paycheck to paycheck. Ivan seeks advice on managing finances efficiently and saving for retirement.</t>
+  </si>
+  <si>
+    <t>Leila left Algeria for a better life in France. She works as a cleaner but earns minimum wage with no benefits. She struggles to send money to her family while covering her own expenses. Without knowledge of government assistance or savings strategies, she often borrows money from friends. Leila wants to learn about personal finance management and debt avoidance.</t>
+  </si>
+  <si>
+    <t>Raj moved from India and works as an accountant. Despite his financial knowledge, he is unfamiliar with New Zealand’s tax laws and investment climate. He wants to purchase a home but is unsure how mortgages work in his new country. Raj also worries about currency exchange fluctuations affecting money sent home. He seeks advice on home ownership and tax optimization.</t>
+  </si>
+  <si>
+    <t>Fatima fled war in Iraq and works as a schoolteacher. She struggles with high living costs and taxation in Sweden. She wants to invest in her children’s education but doesn’t know where to start. Fatima also worries about her pension, as she started contributing later in life. She seeks financial literacy training to better plan for her family’s future.</t>
+  </si>
+  <si>
+    <t>Miguel moved from El Salvador and has worked in factories for decades. He sends most of his earnings home and has little savings. With no retirement plan, he fears financial insecurity in old age. He doesn’t trust banks and relies on cash transactions. Miguel wants to understand social security benefits and how to save effectively.</t>
+  </si>
+  <si>
+    <t>Jovana moved from Serbia and works as a freelance graphic designer. She struggles with irregular income and tax regulations. Without stable earnings, she finds it hard to budget and plan for the future. She has no pension plan and doesn’t know how to invest. Jovana wants to learn about financial stability for self-employed individuals.</t>
+  </si>
+  <si>
+    <t>Maria accumulated $8,000 in credit card debt during her first year in the US, using cards to fund her food truck business startup. She struggles to understand interest rates and minimum payments, leading to mounting debt despite making regular payments. She needs guidance on debt consolidation options and creating a repayment strategy while maintaining her business operations.</t>
+  </si>
+  <si>
+    <t>Despite his professional background, Ahmed keeps most of his earnings in cash, distrustful of banks due to past experiences in Egypt. He's missing opportunities for interest earnings and building credit history. His employer has suggested direct deposit, but Ahmed is hesitant about electronic banking and online financial services.</t>
+  </si>
+  <si>
+    <t>Lin arrived in Australia at 45 and worries about retirement savings. Her previous retirement funds remain in China, and she's uncertain about Australian superannuation systems. She needs to understand how to maximize retirement contributions while supporting her teenage children's education and sending money to elderly parents in China.</t>
+  </si>
+  <si>
+    <t>Viktor has saved £50,000 but keeps it all in a basic savings account. He's interested in investing but finds UK investment products confusing and is concerned about tax implications. He needs guidance on diversification, risk management, and understanding various investment vehicles available to UK residents.</t>
+  </si>
+  <si>
+    <t>Priya struggles to understand various insurance products in New Zealand. She's paying for multiple policies but isn't sure about coverage overlaps. After a minor car accident, she discovered gaps in her understanding of deductibles and claims processes. She needs help evaluating insurance needs and understanding policy terms.</t>
+  </si>
+  <si>
+    <t>Carlos has rented for five years while saving for a home purchase. He's unfamiliar with Spanish mortgage processes and requirements. With a variable income from contracting work, he needs guidance on mortgage qualification, documentation requirements, and understanding various loan options available to self-employed individuals.</t>
+  </si>
+  <si>
+    <t>Fatima struggles with separating personal and business finances. She needs help understanding German tax obligations for small businesses, managing inventory costs, and establishing business credit. She's also uncertain about hiring employees and managing payroll requirements.</t>
+  </si>
+  <si>
+    <t>James supports family in both Ireland and Malaysia, making budgeting complex. He struggles with currency exchange costs and international transfer fees. He needs help creating a sustainable budget that accounts for supporting two households while building emergency savings in his new country.</t>
+  </si>
+  <si>
+    <t>Aisha is uncomfortable with Sweden's largely cashless society. She needs support learning to use digital banking tools, mobile payment apps, and online bill pay systems. She's particularly concerned about security and wants to understand how to protect her financial information while using digital services.</t>
+  </si>
+  <si>
+    <t>Yuki struggles with Canadian tax regulations for self-employed individuals. She needs guidance on quarterly tax payments, deductible business expenses, and retirement account options for freelancers. She's also uncertain about reporting international income from Japanese clients.</t>
+  </si>
+  <si>
+    <t>After moving to Boston, Maria struggled with building credit history. With no U.S. credit record, she couldn't secure a business loan for her food truck dream. She joined a local credit union, obtained a secured credit card, and systematically built her credit score over two years. By maintaining perfect payment history and low credit utilization, she eventually qualified for a $40,000 business loan to launch her food truck business.</t>
+  </si>
+  <si>
+    <t>Despite earning well in Toronto, Ahmed sent most of his earnings to family in Egypt, neglecting his retirement savings. After attending a financial workshop, he realized the importance of balanced financial priorities. He created a structured plan, allocating 60% for current expenses, 20% for family support, and 20% for retirement. He's now maximizing his employer's pension match and building a diversified investment portfolio.</t>
+  </si>
+  <si>
+    <t>Moving to Sydney, Lin faced challenges with Australia's banking system, which differed significantly from China's mobile-payment-centric economy. She initially made costly mistakes with account fees and international transfers. Through research and consultation with her bank's multicultural services department, she learned to optimize her banking arrangements, saving significantly on international transaction fees and finding better ways to send money home.</t>
+  </si>
+  <si>
+    <t>Viktor kept his savings in cash, distrustful of financial institutions due to experiences during Bulgaria's economic transition. After establishing his business in Munich, he gradually learned about German investment options. Starting with conservative investments like government bonds, he slowly diversified into mutual funds. He now helps other Eastern European immigrants understand the German financial system.</t>
+  </si>
+  <si>
+    <t>Overwhelmed by UK living costs, Isabella accumulated £8,000 in credit card debt during her first year in London. She sought help from a free financial counseling service, which helped her create a debt repayment plan. She took on additional weekend work and systematically paid off her debt over 18 months, while learning to budget effectively in her new environment.</t>
+  </si>
+  <si>
+    <t>Despite a good salary in Vancouver, Raj struggled to save for a house down payment due to high living costs and supporting family in India. He joined a first-time homebuyer program, learned about Canadian mortgages, and used tax-free savings accounts effectively. After four years of disciplined saving and reducing remittances, he managed to purchase a small condo with a 20% down payment.</t>
+  </si>
+  <si>
+    <t>Fatima wanted to open a Middle Eastern catering business in Chicago but was unfamiliar with American business regulations and taxes. She participated in a free small business development program, learned about licensing requirements, and gained skills in business financial management. She started small, reinvested profits, and gradually expanded while maintaining careful financial records.</t>
+  </si>
+  <si>
+    <t>When Kim moved to Melbourne, he found the insurance system confusing and initially underinsured himself and his family. After a minor car accident with insufficient coverage, he educated himself about different insurance types. He now maintains appropriate levels of health, car, and rental insurance, understanding the importance of risk management in his adopted country.</t>
+  </si>
+  <si>
+    <t>Elena struggled with UK's tax system, particularly understanding self-assessment requirements for her consulting work. She initially made mistakes in reporting international income from research projects. Through professional tax advice and self-education, she learned to properly manage her tax obligations across multiple income streams and now maintains organized financial records.</t>
+  </si>
+  <si>
+    <t>Amir focused solely on sending money home until a temporary job loss showed him the importance of emergency savings. He created a balanced financial plan, building a three-month emergency fund while maintaining reduced family support. He also learned about German unemployment insurance and workers' benefits, creating a more secure financial foundation for himself.</t>
+  </si>
+  <si>
+    <t>Maria arrived in Houston three years ago and struggled to establish credit history. Despite having managed a successful restaurant in Mexico, she couldn't get approved for a business loan. She discovered secured credit cards and began building her credit score systematically.</t>
+  </si>
+  <si>
+    <t>Having arrived in Toronto at age 40, Ahmed worried about starting retirement savings late. His engineering credentials needed recertification, causing initial career delays. He maximized his employer's pension match but struggled between sending money to family in Egypt and saving for retirement.</t>
+  </si>
+  <si>
+    <t>Despite her financial background, Mei found Australian banking practices different from China's. She initially kept large amounts in cash, distrusting local banks. After experiencing theft, she learned about deposit insurance and digital banking security.</t>
+  </si>
+  <si>
+    <t>Viktor's savings in Russian banks lost significant value due to currency fluctuations. In Munich, he needed to learn about European investment options quickly. Despite his analytical background, he found financial terminology challenging.</t>
+  </si>
+  <si>
+    <t>Moving to Manchester, Priya struggled to understand the UK's insurance system. Coming from India's primarily cash-based healthcare, she was unfamiliar with concepts like excess payments and coverage limits. After a minor car accident with insufficient coverage, she learned to carefully evaluate insurance needs and now maintains appropriate coverage levels across health, car, and home insurance.</t>
+  </si>
+  <si>
+    <t>Carlos's excellent income wasn't enough for mortgage approval in Auckland due to his limited credit history. He learned about New Zealand's KiwiSaver scheme and first-home buyer programs.</t>
+  </si>
+  <si>
+    <t>Aisha's sewing business in Stockholm began informally from home. Understanding Swedish business registration and taxes seemed overwhelming. Through a migrant entrepreneurship program, she learned about microloans and business structure options.</t>
+  </si>
+  <si>
+    <t>Arriving in Paris, Jean-Pierre relied heavily on credit cards during his initial settlement period. Accumulating €15,000 in high-interest debt, he felt overwhelmed.</t>
+  </si>
+  <si>
+    <t>Fatima was accustomed to cash-only transactions in Iraq. In Amsterdam, she needed to learn digital banking quickly. She initially feared online banking security but gradually learned secure password management and two-factor authentication.</t>
+  </si>
+  <si>
+    <t>Despite his technical expertise, Song-Min struggled with the U.S. tax system's complexity. His contractor status required estimated tax payments, and he hadn't understood self-employment tax obligations.</t>
+  </si>
+  <si>
+    <t>Maria arrived in Boston three years ago and struggled to rent an apartment due to having no credit history. She learned about secured credit cards from a community workshop and opened one with a $300 deposit. After a year of careful management, she built enough credit to qualify for an unsecured card and eventually secure a rental without a co-signer. She now mentors other immigrants about responsible credit building while saving for her food truck business.</t>
+  </si>
+  <si>
+    <t>Despite his engineering degree, Ahmed works at a factory in Toronto while pursuing recertification. He initially kept his savings in cash, distrusting banks due to experiences in Somalia. After his apartment was burglarized, he lost $3,000 in savings. A settlement counselor helped him understand Canadian banking regulations and deposit insurance, leading him to open his first checking and savings accounts.</t>
+  </si>
+  <si>
+    <t>Working in Sydney's tech sector, Li earns well but kept all savings in a basic account earning minimal interest. Through her company's financial wellness program, she learned about retirement accounts and index funds. Initially hesitant about investing, she started small with monthly contributions to a diversified portfolio. After seeing steady growth, she's now maximizing her superannuation contributions and helping her parents understand investment options.</t>
+  </si>
+  <si>
+    <t>Carlos accumulated £8,000 in credit card debt financing his mechanic certification in London. The high interest payments strained his family's budget until he attended a free debt counseling session. He negotiated with creditors to lower interest rates and created a structured repayment plan. Within two years, he cleared his debt while building an emergency fund through automatic savings deductions.</t>
+  </si>
+  <si>
+    <t>After working in retail, Priya wanted to open a spice shop in Auckland but struggled to secure traditional financing. She participated in a microenterprise program that taught her about business plans and alternative funding. By combining community lending, personal savings, and a small business grant, she launched her store. She now maintains separate personal and business accounts, tracking all expenses meticulously.</t>
+  </si>
+  <si>
+    <t>Working in Berlin's gig economy, Youssef initially struggled with cash-based payments and manual expense tracking. A digital literacy course introduced him to mobile banking apps and digital payment platforms. He now manages multiple income streams efficiently, automatically categorizes expenses, and uses digital tools to send money to family in Egypt at better exchange rates.</t>
+  </si>
+  <si>
+    <t>Min-Ji avoided health insurance in Chicago, believing it too expensive. After a minor accident led to major medical bills, she sought help understanding the healthcare marketplace. Working with a navigator, she learned about subsidies and enrolled in an affordable plan. She now maintains adequate health, renter's, and life insurance coverage, understanding their role in financial security.</t>
+  </si>
+  <si>
+    <t>Despite good income in Dublin, Viktor focused solely on supporting his children's education. A workplace pension seminar made him realize he had no retirement savings at 51. He met with a financial advisor to create a catch-up strategy, increasing his pension contributions and exploring additional investment vehicles while maintaining his children's educational support.</t>
+  </si>
+  <si>
+    <t>Teaching in Vancouver, Aisha was overwhelmed by tax requirements and missed deductions she qualified for. Through professional development workshops, she learned about educator tax credits and retirement savings deductions. She now maintains organized records year-round and maximizes eligible deductions, resulting in better tax refunds she invests in professional development.</t>
+  </si>
+  <si>
+    <t>Raj's rental payments in Melbourne exceeded potential mortgage payments, but he assumed homeownership was impossible. A first-time homebuyer course taught him about local assistance programs and mortgage requirements. By improving his credit score and saving systematically, he qualified for a starter home loan with down payment assistance, converting his housing expense into equity building.</t>
+  </si>
+  <si>
+    <t>Maria acquired three credit cards shortly after arriving in the US, viewing them as a path to building credit. Without fully understanding interest rates and minimum payments, she accumulated $12,000 in debt across the cards. She's now working with a financial advisor to consolidate her debt and create a repayment plan while learning about responsible credit use.</t>
+  </si>
+  <si>
+    <t>Despite having a well-paying job, Ahmed hadn't started retirement planning, as he was sending significant portions of his income to family in Egypt. After attending a workplace financial workshop, he realized he needed to balance family obligations with his future security. He's now exploring the Canadian Pension Plan and workplace retirement options.</t>
+  </si>
+  <si>
+    <t>Despite her financial background in China, Li struggled to understand Australia's property market and mortgage system. She spent three years saving for a down payment but was initially rejected for loans due to her limited credit history. Through persistence and financial education, she eventually secured a mortgage and purchased her first home.</t>
+  </si>
+  <si>
+    <t>Viktor saved diligently but kept all his money in a basic savings account, unaware of investment opportunities. After losing value to inflation, he began researching investment options. He's learning about the German stock market, ETFs, and retirement accounts, while being cautious about potential investment scams targeting immigrants.</t>
+  </si>
+  <si>
+    <t>Priya wanted to open a specialty grocery store but struggled to secure traditional business loans due to her limited UK credit history. She learned about alternative financing options and successfully combined microloans, community development funds, and personal savings to launch her business.</t>
+  </si>
+  <si>
+    <t>Coming from a cash-based economy, Jean-Pierre was overwhelmed by French banking requirements. He faced challenges with digital banking, automatic payments, and maintaining minimum balances. Through a community organization's financial literacy program, he learned to effectively manage his accounts and digital transactions.</t>
+  </si>
+  <si>
+    <t>Fatima struggled with understanding tax obligations, especially regarding her side business selling traditional crafts online. She wasn't aware of self-employment tax requirements and faced penalties. Working with a tax advisor, she learned about record-keeping, deductions, and quarterly tax payments.</t>
+  </si>
+  <si>
+    <t>Carlos initially avoided insurance products due to negative experiences in his home country. After his apartment was damaged in a flood, he realized the importance of insurance in his new country. He's now learning about different types of coverage and working to understand policy terms and claims processes.</t>
+  </si>
+  <si>
+    <t>While supporting family back home, Aisha was losing significant money to high remittance fees and unfavorable exchange rates. She learned about digital transfer services and banking apps that offer better rates. She created a structured remittance plan that balances family support with her local financial needs.</t>
+  </si>
+  <si>
+    <t>Despite a good salary, Yong-Jun had no emergency savings, having focused on sending money home and investing in stocks. When he faced unexpected medical expenses, he had to sell investments at a loss. He's now building an emergency fund while learning about health insurance and emergency financial planning.</t>
+  </si>
+  <si>
+    <t>Maria, a 34-year-old Latina immigrant in the USA, works in hospitality. With a high school diploma, she struggles to budget her income due to irregular hours. She sends remittances to her family in Mexico, leaving little for savings. Maria wants to learn about saving strategies and managing irregular income to build financial stability for herself and her family.</t>
+  </si>
+  <si>
+    <t>Ahmed, a 42-year-old Middle Eastern immigrant in Canada, holds a bachelor’s degree in engineering but works as a taxi driver due to credential recognition issues. He faces challenges managing debt from relocation costs and wants to understand credit systems and debt repayment strategies.</t>
+  </si>
+  <si>
+    <t>Li, a 50-year-old Chinese immigrant in Australia, is a chef with vocational training. He struggles with language barriers and understanding superannuation (retirement savings). Li wants to learn about retirement planning and navigating Australia’s financial systems to secure his future.</t>
+  </si>
+  <si>
+    <t>Fatima, a 29-year-old Somali immigrant in the UK, works as a cleaner with no formal education. She relies on cash transactions and lacks knowledge about banking. Fatima wants to learn how to open a bank account, save money, and avoid predatory lending practices.</t>
+  </si>
+  <si>
+    <t>Carlos, a 38-year-old Mexican immigrant in the USA, works in construction. With an associate degree, he struggles with budgeting for his family’s needs and saving for emergencies. Carlos wants to learn about emergency funds, insurance, and managing family finances.</t>
+  </si>
+  <si>
+    <t>Anh, a 45-year-old Vietnamese immigrant in Germany, works in a factory. She has a high school diploma but struggles with understanding taxes and social security contributions. Anh wants to learn about tax filing, benefits, and maximizing her income.</t>
+  </si>
+  <si>
+    <t>Jamal, a 31-year-old Syrian immigrant in Sweden, holds a bachelor’s degree in IT but works part-time due to language barriers. He faces challenges managing student loans and living expenses. Jamal wants to learn about budgeting, investing, and improving his credit score.</t>
+  </si>
+  <si>
+    <t>Rosa, a 56-year-old Filipino immigrant in the USA, works as a caregiver. She has limited savings and worries about retirement. Rosa wants to learn about retirement accounts, Social Security benefits, and managing healthcare costs.</t>
+  </si>
+  <si>
+    <t>Youssef, a 40-year-old Egyptian immigrant in France, holds a master’s degree but works as a substitute teacher. He struggles with high living costs and saving for his children’s education. Youssef wants to learn about education savings plans and long-term financial planning.</t>
+  </si>
+  <si>
+    <t>Elena, a 47-year-old Ukrainian immigrant in Poland, works as a nurse with vocational training. She faces challenges with currency exchange and sending money to family in Ukraine. Elena wants to learn about international money transfers, saving strategies, and financial planning for immigrants.</t>
+  </si>
+  <si>
+    <t>Maria, a 34-year-old Latina immigrant in the U.S., works in hospitality. With a high school diploma, she struggles to budget her income due to irregular hours. She sends remittances to her family in Mexico, leaving little for savings. Maria wants to learn about budgeting, saving, and managing debt to secure her financial future and support her children’s education.</t>
+  </si>
+  <si>
+    <t>Ahmed, a 42-year-old Middle Eastern immigrant in Canada, holds a bachelor’s degree in engineering. Despite his qualifications, he works as a taxi driver due to credential recognition issues. He faces challenges saving for retirement and understanding Canadian tax systems. Ahmed seeks guidance on investing and retirement planning.</t>
+  </si>
+  <si>
+    <t>Li, a 50-year-old Chinese immigrant in Australia, is a chef with vocational training. He runs a small restaurant but struggles with cash flow management and business taxes. Li wants to learn about business financial management and improving profitability while saving for his family’s future.</t>
+  </si>
+  <si>
+    <t>Fatima, a 28-year-old Somali immigrant in the UK, works as a cleaner with no formal education. She supports her siblings back home and struggles with high living costs. Fatima needs help with basic budgeting, opening a bank account, and understanding her rights as a worker.</t>
+  </si>
+  <si>
+    <t>Carlos, a 39-year-old Hispanic immigrant in the U.S., works in construction. With an associate degree, he earns a modest income but has no savings or health insurance. Carlos wants to learn about emergency funds, health insurance options, and improving his credit score.</t>
+  </si>
+  <si>
+    <t>Amina, a 45-year-old Nigerian immigrant in Germany, holds a master’s degree but is unemployed due to language barriers. She relies on savings, which are depleting quickly. Amina seeks advice on job search strategies, managing expenses, and accessing social benefits in Germany.</t>
+  </si>
+  <si>
+    <t>Juan, a 31-year-old Mexican immigrant in the U.S., works as a farmworker with a high school diploma. He earns low wages and struggles with debt from migration expenses. Juan wants to learn about debt management, saving strategies, and accessing financial assistance programs.</t>
+  </si>
+  <si>
+    <t>Yuna, a 36-year-old Korean immigrant in Canada, works as a freelance translator. With a bachelor’s degree, she faces irregular income and difficulty saving for a home. Yuna wants to learn about freelancer taxes, saving for a mortgage, and building a stable financial foundation.</t>
+  </si>
+  <si>
+    <t>Raj, a 48-year-old Indian immigrant in the U.S., holds a PhD and works in IT. Despite a high income, he struggles with managing investments and planning for his children’s college education. Raj seeks guidance on advanced financial planning, investment strategies, and education savings plans.</t>
+  </si>
+  <si>
+    <t>Sofia, a 29-year-old Ukrainian immigrant in Poland, works as a teacher. With a bachelor’s degree, she earns a modest salary and struggles with high rent and supporting her family in Ukraine. Sofia wants to learn about budgeting, saving on expenses, and accessing financial aid programs.</t>
+  </si>
+  <si>
+    <t>Maria, a 34-year-old Latina immigrant in the USA, works as a waitress. With a high school diploma, she struggles to budget her income due to irregular tips and high living costs. She wants to save for her children’s education but lacks knowledge about savings accounts or investment options. Maria is also wary of banks due to language barriers and fears of hidden fees. She needs guidance on managing variable income, building credit, and accessing low-cost financial services.</t>
+  </si>
+  <si>
+    <t>Ahmed, a 42-year-old Middle Eastern immigrant in Canada, holds a bachelor’s degree in engineering but works as a taxi driver due to credential recognition issues. He earns a modest income and supports his family back home. Ahmed is overwhelmed by Canada’s tax system and unsure how to claim deductions or save for retirement. He wants to learn about tax planning, remittance options, and strategies to improve his financial stability.</t>
+  </si>
+  <si>
+    <t>Li, a 50-year-old Chinese immigrant in Australia, has a master’s degree and works part-time as a university tutor. Despite her education, she struggles with understanding superannuation (retirement savings) and investment options. Li is also concerned about her limited income and how it affects her ability to save for retirement. She seeks advice on maximizing her superannuation, managing part-time income, and planning for long-term financial security.</t>
+  </si>
+  <si>
+    <t>Javier, a 29-year-old Mexican immigrant in the USA, works in construction and has some college education. He earns a decent wage but spends impulsively, leaving little for savings. Javier is unfamiliar with budgeting tools and has no emergency fund. He wants to learn how to control spending, save for emergencies, and explore opportunities for career advancement to increase his income.</t>
+  </si>
+  <si>
+    <t>Fatima, a 38-year-old Somali immigrant in the UK, works as a cleaner and has no formal education. She supports her four children on a low income and relies on cash transactions, avoiding banks due to mistrust. Fatima struggles to pay bills on time and has no savings. She needs help understanding basic banking, budgeting, and accessing government support programs.</t>
+  </si>
+  <si>
+    <t>Carlos, a 45-year-old Brazilian immigrant in Portugal, works as a chef and has a high school diploma. He earns a steady income but has significant debt from starting his own restaurant, which failed. Carlos is unsure how to manage his debt and rebuild his credit. He wants to learn about debt repayment strategies, credit repair, and financial planning for small business owners.</t>
+  </si>
+  <si>
+    <t>Anh, a 31-year-old Vietnamese immigrant in Germany, completed vocational training and works as a nurse. She earns a stable income but struggles with high rent and student loan payments. Anh is unfamiliar with Germany’s pension system and worries about her financial future. She seeks guidance on budgeting, saving for retirement, and managing student debt.</t>
+  </si>
+  <si>
+    <t>Olga, a 56-year-old Ukrainian immigrant in Poland, holds a bachelor’s degree and works as a teacher. She fled Ukraine due to conflict and now faces financial instability. Olga is unfamiliar with Poland’s banking system and struggles to access her savings from Ukraine. She needs help navigating cross-border banking, budgeting on a reduced income, and planning for retirement.</t>
+  </si>
+  <si>
+    <t>Diego, a 40-year-old Colombian immigrant in Spain, works as a delivery driver and has a high school diploma. He earns a variable income and struggles to save for his family’s future. Diego is unaware of Spain’s tax benefits for low-income workers and lacks a retirement plan. He wants to learn about tax incentives, saving strategies, and retirement planning.</t>
+  </si>
+  <si>
+    <t>Aisha, a 27-year-old Nigerian immigrant in the USA, holds a bachelor’s degree but works in retail due to limited job opportunities. She earns a low wage and has student loan debt. Aisha is unfamiliar with credit scores and struggles to qualify for loans. She wants to learn about improving her credit score, managing debt, and finding better-paying jobs.</t>
+  </si>
+  <si>
+    <t>Maria, a 35-year-old Latina immigrant in the USA, works in hospitality. With a high school diploma, she struggles to budget her income due to irregular hours. She sends remittances to her family in Mexico, leaving little for savings. Maria wants to learn about saving strategies and managing irregular income to secure her financial future.</t>
+  </si>
+  <si>
+    <t>Ahmed, a 42-year-old Middle Eastern immigrant in Canada, holds a bachelor’s degree in engineering but works as a taxi driver due to credential recognition issues. He faces challenges managing debt from relocation and wants to understand credit systems and debt repayment strategies.</t>
+  </si>
+  <si>
+    <t>Li, a 50-year-old Chinese immigrant in Australia, is a chef with vocational training. He struggles with language barriers and understanding superannuation (retirement savings). Li wants to learn about retirement planning and navigating Australia’s financial systems.</t>
+  </si>
+  <si>
+    <t>Fatima, a 28-year-old Somali immigrant in the UK, works as a cleaner with no formal education. She relies on cash transactions and lacks a bank account. Fatima wants to learn about opening a bank account, budgeting, and avoiding predatory lending.</t>
+  </si>
+  <si>
+    <t>Juan, a 45-year-old Mexican immigrant in the USA, works in construction with a middle school education. He struggles with understanding taxes and fears deportation. Juan wants to learn about tax filing, worker rights, and building credit safely.</t>
+  </si>
+  <si>
+    <t>Anh, a 38-year-old Vietnamese immigrant in Germany, works in a factory. She has a high school diploma but struggles with language barriers and understanding insurance policies. Anh wants to learn about health insurance, savings plans, and financial terminology in German.</t>
+  </si>
+  <si>
+    <t>Olga, a 55-year-old Ukrainian immigrant in Poland, holds a master’s degree but works as a tutor due to credential issues. She faces challenges converting her savings from hryvnia to złoty and wants to learn about currency exchange, investing, and pension plans.</t>
+  </si>
+  <si>
+    <t>Carlos, a 33-year-old Colombian immigrant in Spain, works as a freelancer with a bachelor’s degree. He struggles with inconsistent income and understanding tax obligations for freelancers. Carlos wants to learn about budgeting, taxes, and building an emergency fund.</t>
+  </si>
+  <si>
+    <t>Aisha, a 40-year-old Nigerian immigrant in the USA, works as a caregiver with a nursing diploma. She faces challenges with high healthcare costs and sending money to family in Nigeria. Aisha wants to learn about affordable healthcare options and international money transfers.</t>
+  </si>
+  <si>
+    <t>Pavel, a 48-year-old Russian immigrant in the Czech Republic, works as a mechanic with a technical degree. He struggles with understanding mortgage options and saving for his children’s education. Pavel wants to learn about home loans, education savings, and long-term financial planning.</t>
+  </si>
+  <si>
+    <t>Maria, a 34-year-old Latina immigrant in the U.S., works in hospitality. With a high school diploma, she struggles to budget her income due to irregular hours. She sends remittances to her family in Mexico, leaving little for savings. Maria wants to learn about saving strategies and managing irregular income to secure her financial future.</t>
+  </si>
+  <si>
+    <t>Ahmed, a 42-year-old Middle Eastern immigrant in Canada, holds a bachelor’s degree in engineering. Despite a stable job, he faces challenges understanding Canadian tax systems and retirement plans. He seeks guidance on tax optimization and long-term financial planning.</t>
+  </si>
+  <si>
+    <t>Li, a 50-year-old Chinese immigrant in Australia, works as a chef. With vocational training, he lacks knowledge about investing and managing debt. Li wants to learn about debt reduction and building an investment portfolio for retirement.</t>
+  </si>
+  <si>
+    <t>Fatima, a 28-year-old Somali immigrant in the UK, works as a cleaner. With no formal education, she struggles with budgeting and accessing banking services. Fatima aims to learn basic financial literacy, including opening a bank account and managing daily expenses.</t>
+  </si>
+  <si>
+    <t>Carlos, a 39-year-old Mexican immigrant in the U.S., works in construction. With an associate degree, he faces challenges understanding credit scores and loans. Carlos wants to improve his credit score and learn about affordable loan options for homeownership.</t>
+  </si>
+  <si>
+    <t>Anh, a 45-year-old Vietnamese immigrant in Germany, works in a factory. With a high school diploma, she struggles with language barriers and understanding pension systems. Anh seeks guidance on retirement planning and navigating German financial systems.</t>
+  </si>
+  <si>
+    <t>Jamal, a 30-year-old Syrian immigrant in Sweden, works as an IT specialist. Despite his bachelor’s degree, he finds it challenging to navigate Swedish tax laws and investment options. Jamal wants to learn about tax-efficient investing and building wealth.</t>
+  </si>
+  <si>
+    <t>Sofia, a 36-year-old Filipino immigrant in the UAE, works as a nurse. With a nursing diploma, she struggles with saving due to high living costs and supporting her family back home. Sofia aims to learn about budgeting and saving for emergencies.</t>
+  </si>
+  <si>
+    <t>Youssef, a 55-year-old Egyptian immigrant in France, works as a teacher. With a master’s degree, he faces challenges understanding French retirement benefits and estate planning. Youssef seeks advice on maximizing retirement savings and creating a will.</t>
+  </si>
+  <si>
+    <t>Elena, a 29-year-old Romanian immigrant in Italy, works as a caregiver. With a high school diploma, she struggles with managing debt and saving for her future. Elena wants to learn about debt management and saving strategies to achieve financial stability.</t>
+  </si>
+  <si>
+    <t>Maria struggles to manage her irregular income and often relies on high-interest payday loans. She wants to learn budgeting and saving techniques to achieve financial stability.</t>
+  </si>
+  <si>
+    <t>Kenji has difficulty understanding the Canadian tax system and maximizing his tax deductions. He also wants to invest his savings wisely.</t>
+  </si>
+  <si>
+    <t>Fatima is burdened by student loan debt and wants to create a repayment plan that aligns with her income. She also needs guidance on building credit in the UK.</t>
+  </si>
+  <si>
+    <t>David faces inconsistent work and needs help budgeting for periods of unemployment. He also lacks health insurance and wants to explore affordable options.</t>
+  </si>
+  <si>
+    <t>Aisha wants to buy a home but finds the French mortgage process confusing. She needs advice on saving for a down payment and understanding interest rates.</t>
+  </si>
+  <si>
+    <t>Javier wants to start his own business but needs help securing funding and creating a business plan. He also needs to understand the financial implications of self-employment.</t>
+  </si>
+  <si>
+    <t>Mei is struggling to save money due to high living costs in Germany. She wants to learn about investment strategies suitable for her income level.</t>
+  </si>
+  <si>
+    <t>Kofi wants to plan for his retirement but doesn't know where to start. He needs information on pension plans and long-term savings options.</t>
+  </si>
+  <si>
+    <t>Elena is concerned about providing for her family's future. She wants to learn about life insurance and other financial safety nets.</t>
+  </si>
+  <si>
+    <t>Omar wants to invest in the stock market but lacks the knowledge to make informed decisions. He needs guidance on choosing investments and managing risk.</t>
+  </si>
+  <si>
+    <t>Maria struggles to budget her irregular income and often relies on high-interest payday loans, making it difficult to cover basic expenses like rent and groceries. She lacks understanding of compound interest and the long-term costs of these loans.</t>
+  </si>
+  <si>
+    <t>David earns a good salary but has difficulty managing his debt. He has accumulated significant credit card debt due to impulsive spending and lacks a plan for paying it down effectively. He is also unsure about how to invest for retirement.</t>
+  </si>
+  <si>
+    <t>Fatima is concerned about sending money home to her family. She wants to find the most cost-effective and reliable method for international money transfers, avoiding high fees and unfavorable exchange rates.</t>
+  </si>
+  <si>
+    <t>Kofi recently experienced a workplace injury and is unable to work. He is struggling to navigate the complexities of unemployment benefits and disability payments, unsure of how to manage his reduced income.</t>
+  </si>
+  <si>
+    <t>Aisha is planning to buy her first home but is overwhelmed by the process of securing a mortgage. She is unsure about different mortgage types, interest rates, and the required down payment.</t>
+  </si>
+  <si>
+    <t>Carlos works in a seasonal industry and experiences periods of unemployment. He struggles to save money during his employment periods to cover expenses during the off-season. He lacks access to affordable health insurance.</t>
+  </si>
+  <si>
+    <t>Elena is trying to grow her small business but is having difficulty managing her business finances. She needs help with budgeting, cash flow management, and understanding tax obligations for small businesses.</t>
+  </si>
+  <si>
+    <t>Kwame is interested in investing but feels intimidated by the complexity of the stock market. He is unsure about how to get started and how to choose investments that align with his risk tolerance.</t>
+  </si>
+  <si>
+    <t>Mei is nearing retirement age but has very little saved. She is concerned about her ability to live comfortably on a fixed income and is unsure about how to access government benefits.</t>
+  </si>
+  <si>
+    <t>Omar wants to plan for his children's education but is unsure about the different education savings options available and how to choose the best plan for his family.</t>
+  </si>
+  <si>
+    <t>Maria struggles to manage her household budget due to irregular income and unexpected expenses. She lacks understanding of basic banking and credit concepts.</t>
+  </si>
+  <si>
+    <t>Kwame earns a good salary but has difficulty saving due to high rent and cost of living in London. He is interested in investment options but lacks knowledge.</t>
+  </si>
+  <si>
+    <t>Mei has significant student loan debt. She wants to pay it off quickly but needs help creating a repayment plan and understanding interest rates.</t>
+  </si>
+  <si>
+    <t>Javier sends money home regularly to support his family. He needs advice on how to do</t>
+  </si>
+  <si>
+    <t>Aisha is seeking employment but needs to manage her limited savings while she looks for a job. She is unfamiliar with the German welfare system.</t>
+  </si>
+  <si>
+    <t>David wants to start his own plumbing business. He needs guidance on securing a loan, managing business finances, and understanding tax obligations.</t>
+  </si>
+  <si>
+    <t>Elena relies on a fixed pension and struggles to keep up with rising living costs. She is concerned about managing her healthcare expenses.</t>
+  </si>
+  <si>
+    <t>Kenji is saving for a down payment on a house. He needs advice on budgeting, saving strategies, and understanding the Brazilian real estate market.</t>
+  </si>
+  <si>
+    <t>Fatima wants to further her education but needs financial assistance. She is exploring scholarship options and student loan possibilities.</t>
+  </si>
+  <si>
+    <t>Ricardo is concerned about his retirement savings. He has limited knowledge of the Spanish pension system and needs help planning for his future.</t>
+  </si>
+  <si>
+    <t>Maria struggles to manage her irregular income and often relies on payday loans, accumulating high interest debt. She wants to learn budgeting and saving strategies.</t>
+  </si>
+  <si>
+    <t>Kwame has a good income but lacks knowledge about investing and retirement planning. He feels overwhelmed by the options available and seeks guidance.</t>
+  </si>
+  <si>
+    <t>Mei is unsure how to navigate the UK tax system and maximize her tax benefits. She also wants to understand how to build a good credit score.</t>
+  </si>
+  <si>
+    <t>Javier is worried about his retirement as he has limited savings. He wants to explore options for increasing his retirement income.</t>
+  </si>
+  <si>
+    <t>Anika is struggling to manage her student loan debt and wants to learn strategies for paying it off faster.</t>
+  </si>
+  <si>
+    <t>David wants to buy a house but is unsure about the mortgage process and how much he can afford.</t>
+  </si>
+  <si>
+    <t>Elena is self-employed and finds it difficult to manage her fluctuating income. She needs help with budgeting and forecasting.</t>
+  </si>
+  <si>
+    <t>Omar is nearing retirement and wants to understand how to access government benefits and manage his investments.</t>
+  </si>
+  <si>
+    <t>Sofia wants to save for her children's education but is unsure about the best investment options and tax-advantaged accounts.</t>
+  </si>
+  <si>
+    <t>Kenji wants to diversify his investments and learn about managing risk. He is also interested in estate planning.</t>
+  </si>
+  <si>
+    <t>Maria struggles to budget her irregular income and often relies on high-interest payday loans, leading to a cycle of debt. She lacks knowledge of basic banking and saving strategies.</t>
+  </si>
+  <si>
+    <t>Kwame has a good income but struggles to manage his finances due to a lack of understanding of the UK tax system and investment options. He worries about saving for his children's education.</t>
+  </si>
+  <si>
+    <t>Mei is hesitant to invest her savings due to cultural beliefs and a lack of trust in financial institutions. She prefers to keep her money in low-interest savings accounts.</t>
+  </si>
+  <si>
+    <t>Javier sends a large portion of his income to support his family back home. He struggles to make ends meet in the US and has little saved for retirement.</t>
+  </si>
+  <si>
+    <t>Anika is overwhelmed by student loan debt and struggles to repay it while also managing other expenses. She is unaware of available repayment options.</t>
+  </si>
+  <si>
+    <t>Jean-Pierre recently started his own business and is struggling to manage his cash flow. He lacks knowledge of accounting and financial record-keeping.</t>
+  </si>
+  <si>
+    <t>Fatima is trying to save for a down payment on a house but finds it difficult due to low wages and high living costs. She is unsure about the process of applying for a mortgage.</t>
+  </si>
+  <si>
+    <t>Kenji is concerned about his retirement savings but is unsure how to invest wisely. He is also worried about the rising cost of living.</t>
+  </si>
+  <si>
+    <t>Sofia is a single mother and struggles to manage her finances while supporting her children. She lacks knowledge of available government assistance programs.</t>
+  </si>
+  <si>
+    <t>David is nearing retirement age but has very little saved. He is worried about his financial security and healthcare cost</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -2046,7 +2648,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -2187,6 +2789,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2205,19 +2810,19 @@
 </file>
 
 <file path=xl/queryTables/queryTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="test_1" connectionId="4" xr16:uid="{00000000-0016-0000-0000-000000000000}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
+<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="test_1" connectionId="4" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
 </file>
 
 <file path=xl/queryTables/queryTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="test_1" connectionId="3" xr16:uid="{00000000-0016-0000-0100-000001000000}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
+<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="test_1" connectionId="3" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
 </file>
 
 <file path=xl/queryTables/queryTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="test_1" connectionId="2" xr16:uid="{00000000-0016-0000-0200-000002000000}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
+<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="test_1" connectionId="2" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
 </file>
 
 <file path=xl/queryTables/queryTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="test_1" connectionId="1" xr16:uid="{00000000-0016-0000-0300-000003000000}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
+<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="test_1" connectionId="1" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2482,33 +3087,33 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B1:L106"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="B1:M106"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="6.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="3.140625" style="3" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.140625" style="3" customWidth="1"/>
-    <col min="5" max="5" width="6.28515625" style="3" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" style="3" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="3" customWidth="1"/>
-    <col min="8" max="8" width="22.140625" style="3" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="18.42578125" style="3" customWidth="1"/>
-    <col min="10" max="10" width="20.140625" style="3" customWidth="1"/>
-    <col min="11" max="11" width="51.7109375" style="3" customWidth="1"/>
-    <col min="12" max="12" width="20.5703125" style="19" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="2.85546875" customWidth="1"/>
-    <col min="14" max="14" width="3.140625" customWidth="1"/>
-    <col min="15" max="15" width="24.7109375" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="4.42578125" customWidth="1"/>
-    <col min="17" max="17" width="23.5703125" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="30.42578125" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="46.140625" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="18.85546875" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="2" customWidth="1"/>
+    <col min="2" max="2" width="6.1796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="3.1796875" style="3" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.1796875" style="3" customWidth="1"/>
+    <col min="5" max="5" width="6.26953125" style="3" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="4.7265625" style="3" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.453125" style="3" customWidth="1"/>
+    <col min="8" max="8" width="22.1796875" style="3" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18.453125" style="3" customWidth="1"/>
+    <col min="10" max="11" width="20.1796875" style="3" customWidth="1"/>
+    <col min="12" max="12" width="51.7265625" style="3" customWidth="1"/>
+    <col min="13" max="13" width="20.54296875" style="19" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="2.81640625" customWidth="1"/>
+    <col min="15" max="15" width="3.1796875" customWidth="1"/>
+    <col min="16" max="16" width="24.7265625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="4.453125" customWidth="1"/>
+    <col min="18" max="18" width="23.54296875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="30.453125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="46.1796875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="18.81640625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B1" s="1"/>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
@@ -2519,9 +3124,10 @@
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
       <c r="K1" s="2"/>
-      <c r="L1" s="4"/>
-    </row>
-    <row r="2" spans="2:12" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L1" s="2"/>
+      <c r="M1" s="4"/>
+    </row>
+    <row r="2" spans="2:13" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B2" s="24" t="s">
         <v>0</v>
       </c>
@@ -2550,13 +3156,16 @@
         <v>9</v>
       </c>
       <c r="K2" s="25" t="s">
+        <v>503</v>
+      </c>
+      <c r="L2" s="25" t="s">
         <v>2</v>
       </c>
-      <c r="L2" s="28" t="s">
+      <c r="M2" s="28" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="2:12" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:13" ht="15" thickTop="1" x14ac:dyDescent="0.35">
       <c r="B3" s="46">
         <v>1</v>
       </c>
@@ -2585,11 +3194,14 @@
         <v>56</v>
       </c>
       <c r="K3" s="33" t="s">
+        <v>504</v>
+      </c>
+      <c r="L3" s="33" t="s">
         <v>57</v>
       </c>
-      <c r="L3" s="9"/>
-    </row>
-    <row r="4" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="M3" s="9"/>
+    </row>
+    <row r="4" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B4" s="46"/>
       <c r="C4" s="5">
         <v>2</v>
@@ -2615,12 +3227,15 @@
       <c r="J4" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="K4" s="6" t="s">
+      <c r="K4" s="50" t="s">
+        <v>505</v>
+      </c>
+      <c r="L4" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="L4" s="9"/>
-    </row>
-    <row r="5" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="M4" s="9"/>
+    </row>
+    <row r="5" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B5" s="46"/>
       <c r="C5" s="5">
         <v>3</v>
@@ -2646,12 +3261,15 @@
       <c r="J5" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="K5" s="6" t="s">
+      <c r="K5" s="50" t="s">
+        <v>506</v>
+      </c>
+      <c r="L5" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="L5" s="9"/>
-    </row>
-    <row r="6" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="M5" s="9"/>
+    </row>
+    <row r="6" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B6" s="46"/>
       <c r="C6" s="5">
         <v>4</v>
@@ -2677,12 +3295,15 @@
       <c r="J6" s="8" t="s">
         <v>67</v>
       </c>
-      <c r="K6" s="6" t="s">
+      <c r="K6" s="50" t="s">
+        <v>507</v>
+      </c>
+      <c r="L6" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="L6" s="9"/>
-    </row>
-    <row r="7" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="M6" s="9"/>
+    </row>
+    <row r="7" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B7" s="46"/>
       <c r="C7" s="23">
         <v>5</v>
@@ -2709,11 +3330,14 @@
         <v>45</v>
       </c>
       <c r="K7" s="8" t="s">
+        <v>508</v>
+      </c>
+      <c r="L7" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="L7" s="9"/>
-    </row>
-    <row r="8" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="M7" s="9"/>
+    </row>
+    <row r="8" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B8" s="46"/>
       <c r="C8" s="5">
         <v>6</v>
@@ -2739,12 +3363,15 @@
       <c r="J8" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="K8" s="6" t="s">
+      <c r="K8" s="50" t="s">
+        <v>509</v>
+      </c>
+      <c r="L8" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="L8" s="9"/>
-    </row>
-    <row r="9" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="M8" s="9"/>
+    </row>
+    <row r="9" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B9" s="46"/>
       <c r="C9" s="5">
         <v>7</v>
@@ -2770,12 +3397,15 @@
       <c r="J9" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="K9" s="6" t="s">
+      <c r="K9" s="50" t="s">
+        <v>510</v>
+      </c>
+      <c r="L9" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="L9" s="9"/>
-    </row>
-    <row r="10" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="M9" s="9"/>
+    </row>
+    <row r="10" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B10" s="46"/>
       <c r="C10" s="5">
         <v>8</v>
@@ -2801,12 +3431,15 @@
       <c r="J10" s="8" t="s">
         <v>81</v>
       </c>
-      <c r="K10" s="6" t="s">
+      <c r="K10" s="50" t="s">
+        <v>511</v>
+      </c>
+      <c r="L10" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="L10" s="9"/>
-    </row>
-    <row r="11" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="M10" s="9"/>
+    </row>
+    <row r="11" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B11" s="46"/>
       <c r="C11" s="5">
         <v>9</v>
@@ -2832,12 +3465,15 @@
       <c r="J11" s="8" t="s">
         <v>86</v>
       </c>
-      <c r="K11" s="6" t="s">
+      <c r="K11" s="50" t="s">
+        <v>512</v>
+      </c>
+      <c r="L11" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="L11" s="9"/>
-    </row>
-    <row r="12" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="M11" s="9"/>
+    </row>
+    <row r="12" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B12" s="47"/>
       <c r="C12" s="10">
         <v>10</v>
@@ -2864,11 +3500,14 @@
         <v>91</v>
       </c>
       <c r="K12" s="11" t="s">
+        <v>513</v>
+      </c>
+      <c r="L12" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="L12" s="9"/>
-    </row>
-    <row r="13" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="M12" s="9"/>
+    </row>
+    <row r="13" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B13" s="48">
         <v>2</v>
       </c>
@@ -2897,11 +3536,14 @@
         <v>81</v>
       </c>
       <c r="K13" s="14" t="s">
+        <v>514</v>
+      </c>
+      <c r="L13" s="14" t="s">
         <v>94</v>
       </c>
-      <c r="L13" s="9"/>
-    </row>
-    <row r="14" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="M13" s="9"/>
+    </row>
+    <row r="14" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B14" s="46"/>
       <c r="C14" s="5">
         <v>2</v>
@@ -2927,12 +3569,15 @@
       <c r="J14" s="8" t="s">
         <v>96</v>
       </c>
-      <c r="K14" s="6" t="s">
+      <c r="K14" s="50" t="s">
+        <v>515</v>
+      </c>
+      <c r="L14" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="L14" s="9"/>
-    </row>
-    <row r="15" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="M14" s="9"/>
+    </row>
+    <row r="15" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B15" s="46"/>
       <c r="C15" s="5">
         <v>3</v>
@@ -2958,12 +3603,15 @@
       <c r="J15" s="8" t="s">
         <v>102</v>
       </c>
-      <c r="K15" s="6" t="s">
+      <c r="K15" s="50" t="s">
+        <v>516</v>
+      </c>
+      <c r="L15" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="L15" s="9"/>
-    </row>
-    <row r="16" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="M15" s="9"/>
+    </row>
+    <row r="16" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B16" s="46"/>
       <c r="C16" s="5">
         <v>4</v>
@@ -2989,12 +3637,15 @@
       <c r="J16" s="8" t="s">
         <v>104</v>
       </c>
-      <c r="K16" s="6" t="s">
+      <c r="K16" s="50" t="s">
+        <v>517</v>
+      </c>
+      <c r="L16" s="6" t="s">
         <v>105</v>
       </c>
-      <c r="L16" s="9"/>
-    </row>
-    <row r="17" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="M16" s="9"/>
+    </row>
+    <row r="17" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B17" s="46"/>
       <c r="C17" s="23">
         <v>5</v>
@@ -3021,11 +3672,14 @@
         <v>108</v>
       </c>
       <c r="K17" s="8" t="s">
+        <v>518</v>
+      </c>
+      <c r="L17" s="8" t="s">
         <v>109</v>
       </c>
-      <c r="L17" s="9"/>
-    </row>
-    <row r="18" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="M17" s="9"/>
+    </row>
+    <row r="18" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B18" s="46"/>
       <c r="C18" s="5">
         <v>6</v>
@@ -3051,12 +3705,15 @@
       <c r="J18" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="K18" s="6" t="s">
+      <c r="K18" s="50" t="s">
+        <v>519</v>
+      </c>
+      <c r="L18" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="L18" s="9"/>
-    </row>
-    <row r="19" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="M18" s="9"/>
+    </row>
+    <row r="19" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B19" s="46"/>
       <c r="C19" s="5">
         <v>7</v>
@@ -3082,12 +3739,15 @@
       <c r="J19" s="8" t="s">
         <v>114</v>
       </c>
-      <c r="K19" s="6" t="s">
+      <c r="K19" s="50" t="s">
+        <v>520</v>
+      </c>
+      <c r="L19" s="6" t="s">
         <v>115</v>
       </c>
-      <c r="L19" s="9"/>
-    </row>
-    <row r="20" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="M19" s="9"/>
+    </row>
+    <row r="20" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B20" s="46"/>
       <c r="C20" s="5">
         <v>8</v>
@@ -3113,12 +3773,15 @@
       <c r="J20" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="K20" s="6" t="s">
+      <c r="K20" s="50" t="s">
+        <v>521</v>
+      </c>
+      <c r="L20" s="6" t="s">
         <v>118</v>
       </c>
-      <c r="L20" s="9"/>
-    </row>
-    <row r="21" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="M20" s="9"/>
+    </row>
+    <row r="21" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B21" s="46"/>
       <c r="C21" s="5">
         <v>9</v>
@@ -3144,12 +3807,15 @@
       <c r="J21" s="8" t="s">
         <v>121</v>
       </c>
-      <c r="K21" s="6" t="s">
+      <c r="K21" s="50" t="s">
+        <v>522</v>
+      </c>
+      <c r="L21" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="L21" s="9"/>
-    </row>
-    <row r="22" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="M21" s="9"/>
+    </row>
+    <row r="22" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B22" s="47"/>
       <c r="C22" s="10">
         <v>10</v>
@@ -3176,11 +3842,14 @@
         <v>124</v>
       </c>
       <c r="K22" s="11" t="s">
+        <v>523</v>
+      </c>
+      <c r="L22" s="11" t="s">
         <v>125</v>
       </c>
-      <c r="L22" s="9"/>
-    </row>
-    <row r="23" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="M22" s="9"/>
+    </row>
+    <row r="23" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B23" s="48">
         <v>3</v>
       </c>
@@ -3209,11 +3878,14 @@
         <v>36</v>
       </c>
       <c r="K23" s="14" t="s">
+        <v>524</v>
+      </c>
+      <c r="L23" s="14" t="s">
         <v>328</v>
       </c>
-      <c r="L23" s="9"/>
-    </row>
-    <row r="24" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="M23" s="9"/>
+    </row>
+    <row r="24" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B24" s="46"/>
       <c r="C24" s="5">
         <v>2</v>
@@ -3239,12 +3911,15 @@
       <c r="J24" s="8" t="s">
         <v>91</v>
       </c>
-      <c r="K24" s="6" t="s">
+      <c r="K24" s="50" t="s">
+        <v>525</v>
+      </c>
+      <c r="L24" s="6" t="s">
         <v>329</v>
       </c>
-      <c r="L24" s="9"/>
-    </row>
-    <row r="25" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="M24" s="9"/>
+    </row>
+    <row r="25" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B25" s="46"/>
       <c r="C25" s="5">
         <v>3</v>
@@ -3270,12 +3945,15 @@
       <c r="J25" s="8" t="s">
         <v>128</v>
       </c>
-      <c r="K25" s="6" t="s">
+      <c r="K25" s="50" t="s">
+        <v>526</v>
+      </c>
+      <c r="L25" s="6" t="s">
         <v>330</v>
       </c>
-      <c r="L25" s="9"/>
-    </row>
-    <row r="26" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="M25" s="9"/>
+    </row>
+    <row r="26" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B26" s="46"/>
       <c r="C26" s="5">
         <v>4</v>
@@ -3301,12 +3979,15 @@
       <c r="J26" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="K26" s="6" t="s">
+      <c r="K26" s="50" t="s">
+        <v>527</v>
+      </c>
+      <c r="L26" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="L26" s="9"/>
-    </row>
-    <row r="27" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="M26" s="9"/>
+    </row>
+    <row r="27" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B27" s="46"/>
       <c r="C27" s="23">
         <v>5</v>
@@ -3333,11 +4014,14 @@
         <v>67</v>
       </c>
       <c r="K27" s="8" t="s">
+        <v>528</v>
+      </c>
+      <c r="L27" s="8" t="s">
         <v>332</v>
       </c>
-      <c r="L27" s="9"/>
-    </row>
-    <row r="28" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="M27" s="9"/>
+    </row>
+    <row r="28" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B28" s="46"/>
       <c r="C28" s="5">
         <v>6</v>
@@ -3363,12 +4047,15 @@
       <c r="J28" s="8" t="s">
         <v>132</v>
       </c>
-      <c r="K28" s="6" t="s">
+      <c r="K28" s="50" t="s">
+        <v>529</v>
+      </c>
+      <c r="L28" s="6" t="s">
         <v>333</v>
       </c>
-      <c r="L28" s="9"/>
-    </row>
-    <row r="29" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="M28" s="9"/>
+    </row>
+    <row r="29" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B29" s="46"/>
       <c r="C29" s="5">
         <v>7</v>
@@ -3394,12 +4081,15 @@
       <c r="J29" s="8" t="s">
         <v>104</v>
       </c>
-      <c r="K29" s="6" t="s">
+      <c r="K29" s="50" t="s">
+        <v>530</v>
+      </c>
+      <c r="L29" s="6" t="s">
         <v>334</v>
       </c>
-      <c r="L29" s="9"/>
-    </row>
-    <row r="30" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="M29" s="9"/>
+    </row>
+    <row r="30" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B30" s="46"/>
       <c r="C30" s="5">
         <v>8</v>
@@ -3425,12 +4115,15 @@
       <c r="J30" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="K30" s="6" t="s">
+      <c r="K30" s="50" t="s">
+        <v>531</v>
+      </c>
+      <c r="L30" s="6" t="s">
         <v>335</v>
       </c>
-      <c r="L30" s="9"/>
-    </row>
-    <row r="31" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="M30" s="9"/>
+    </row>
+    <row r="31" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B31" s="46"/>
       <c r="C31" s="5">
         <v>9</v>
@@ -3456,12 +4149,15 @@
       <c r="J31" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="K31" s="6" t="s">
+      <c r="K31" s="50" t="s">
+        <v>532</v>
+      </c>
+      <c r="L31" s="6" t="s">
         <v>336</v>
       </c>
-      <c r="L31" s="9"/>
-    </row>
-    <row r="32" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="M31" s="9"/>
+    </row>
+    <row r="32" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B32" s="47"/>
       <c r="C32" s="10">
         <v>10</v>
@@ -3488,11 +4184,14 @@
         <v>108</v>
       </c>
       <c r="K32" s="11" t="s">
+        <v>533</v>
+      </c>
+      <c r="L32" s="11" t="s">
         <v>337</v>
       </c>
-      <c r="L32" s="9"/>
-    </row>
-    <row r="33" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="M32" s="9"/>
+    </row>
+    <row r="33" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B33" s="48">
         <v>4</v>
       </c>
@@ -3521,11 +4220,14 @@
         <v>91</v>
       </c>
       <c r="K33" s="14" t="s">
+        <v>534</v>
+      </c>
+      <c r="L33" s="14" t="s">
         <v>338</v>
       </c>
-      <c r="L33" s="9"/>
-    </row>
-    <row r="34" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="M33" s="9"/>
+    </row>
+    <row r="34" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B34" s="46"/>
       <c r="C34" s="5">
         <v>2</v>
@@ -3551,12 +4253,15 @@
       <c r="J34" s="8" t="s">
         <v>67</v>
       </c>
-      <c r="K34" s="6" t="s">
+      <c r="K34" s="50" t="s">
+        <v>535</v>
+      </c>
+      <c r="L34" s="6" t="s">
         <v>339</v>
       </c>
-      <c r="L34" s="9"/>
-    </row>
-    <row r="35" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="M34" s="9"/>
+    </row>
+    <row r="35" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B35" s="46"/>
       <c r="C35" s="5">
         <v>3</v>
@@ -3582,12 +4287,15 @@
       <c r="J35" s="8" t="s">
         <v>138</v>
       </c>
-      <c r="K35" s="6" t="s">
+      <c r="K35" s="50" t="s">
+        <v>536</v>
+      </c>
+      <c r="L35" s="6" t="s">
         <v>340</v>
       </c>
-      <c r="L35" s="9"/>
-    </row>
-    <row r="36" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="M35" s="9"/>
+    </row>
+    <row r="36" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B36" s="46"/>
       <c r="C36" s="5">
         <v>4</v>
@@ -3613,12 +4321,15 @@
       <c r="J36" s="8" t="s">
         <v>140</v>
       </c>
-      <c r="K36" s="6" t="s">
+      <c r="K36" s="50" t="s">
+        <v>537</v>
+      </c>
+      <c r="L36" s="6" t="s">
         <v>341</v>
       </c>
-      <c r="L36" s="9"/>
-    </row>
-    <row r="37" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="M36" s="9"/>
+    </row>
+    <row r="37" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B37" s="46"/>
       <c r="C37" s="23">
         <v>5</v>
@@ -3645,11 +4356,14 @@
         <v>142</v>
       </c>
       <c r="K37" s="8" t="s">
+        <v>538</v>
+      </c>
+      <c r="L37" s="8" t="s">
         <v>342</v>
       </c>
-      <c r="L37" s="9"/>
-    </row>
-    <row r="38" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="M37" s="9"/>
+    </row>
+    <row r="38" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B38" s="46"/>
       <c r="C38" s="5">
         <v>6</v>
@@ -3675,12 +4389,15 @@
       <c r="J38" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="K38" s="6" t="s">
+      <c r="K38" s="50" t="s">
+        <v>539</v>
+      </c>
+      <c r="L38" s="6" t="s">
         <v>144</v>
       </c>
-      <c r="L38" s="9"/>
-    </row>
-    <row r="39" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="M38" s="9"/>
+    </row>
+    <row r="39" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B39" s="46"/>
       <c r="C39" s="5">
         <v>7</v>
@@ -3706,12 +4423,15 @@
       <c r="J39" s="8" t="s">
         <v>146</v>
       </c>
-      <c r="K39" s="6" t="s">
+      <c r="K39" s="50" t="s">
+        <v>540</v>
+      </c>
+      <c r="L39" s="6" t="s">
         <v>343</v>
       </c>
-      <c r="L39" s="9"/>
-    </row>
-    <row r="40" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="M39" s="9"/>
+    </row>
+    <row r="40" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B40" s="46"/>
       <c r="C40" s="5">
         <v>8</v>
@@ -3737,12 +4457,15 @@
       <c r="J40" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="K40" s="6" t="s">
+      <c r="K40" s="50" t="s">
+        <v>541</v>
+      </c>
+      <c r="L40" s="6" t="s">
         <v>149</v>
       </c>
-      <c r="L40" s="9"/>
-    </row>
-    <row r="41" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="M40" s="9"/>
+    </row>
+    <row r="41" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B41" s="46"/>
       <c r="C41" s="5">
         <v>9</v>
@@ -3768,12 +4491,15 @@
       <c r="J41" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="K41" s="6" t="s">
+      <c r="K41" s="50" t="s">
+        <v>542</v>
+      </c>
+      <c r="L41" s="6" t="s">
         <v>344</v>
       </c>
-      <c r="L41" s="9"/>
-    </row>
-    <row r="42" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="M41" s="9"/>
+    </row>
+    <row r="42" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B42" s="47"/>
       <c r="C42" s="10">
         <v>10</v>
@@ -3800,11 +4526,14 @@
         <v>25</v>
       </c>
       <c r="K42" s="11" t="s">
+        <v>543</v>
+      </c>
+      <c r="L42" s="11" t="s">
         <v>345</v>
       </c>
-      <c r="L42" s="9"/>
-    </row>
-    <row r="43" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="M42" s="9"/>
+    </row>
+    <row r="43" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B43" s="48">
         <v>5</v>
       </c>
@@ -3833,11 +4562,14 @@
         <v>36</v>
       </c>
       <c r="K43" s="14" t="s">
+        <v>544</v>
+      </c>
+      <c r="L43" s="14" t="s">
         <v>346</v>
       </c>
-      <c r="L43" s="9"/>
-    </row>
-    <row r="44" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="M43" s="9"/>
+    </row>
+    <row r="44" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B44" s="46"/>
       <c r="C44" s="5">
         <v>2</v>
@@ -3863,12 +4595,15 @@
       <c r="J44" s="8" t="s">
         <v>138</v>
       </c>
-      <c r="K44" s="6" t="s">
+      <c r="K44" s="50" t="s">
+        <v>545</v>
+      </c>
+      <c r="L44" s="6" t="s">
         <v>347</v>
       </c>
-      <c r="L44" s="9"/>
-    </row>
-    <row r="45" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="M44" s="9"/>
+    </row>
+    <row r="45" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B45" s="46"/>
       <c r="C45" s="5">
         <v>3</v>
@@ -3894,12 +4629,15 @@
       <c r="J45" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="K45" s="6" t="s">
+      <c r="K45" s="50" t="s">
+        <v>546</v>
+      </c>
+      <c r="L45" s="6" t="s">
         <v>348</v>
       </c>
-      <c r="L45" s="9"/>
-    </row>
-    <row r="46" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="M45" s="9"/>
+    </row>
+    <row r="46" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B46" s="46"/>
       <c r="C46" s="5">
         <v>4</v>
@@ -3925,12 +4663,15 @@
       <c r="J46" s="8" t="s">
         <v>156</v>
       </c>
-      <c r="K46" s="6" t="s">
+      <c r="K46" s="50" t="s">
+        <v>547</v>
+      </c>
+      <c r="L46" s="6" t="s">
         <v>349</v>
       </c>
-      <c r="L46" s="9"/>
-    </row>
-    <row r="47" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="M46" s="9"/>
+    </row>
+    <row r="47" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B47" s="46"/>
       <c r="C47" s="23">
         <v>5</v>
@@ -3957,11 +4698,14 @@
         <v>159</v>
       </c>
       <c r="K47" s="8" t="s">
+        <v>548</v>
+      </c>
+      <c r="L47" s="8" t="s">
         <v>350</v>
       </c>
-      <c r="L47" s="9"/>
-    </row>
-    <row r="48" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="M47" s="9"/>
+    </row>
+    <row r="48" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B48" s="46"/>
       <c r="C48" s="5">
         <v>6</v>
@@ -3987,12 +4731,15 @@
       <c r="J48" s="8" t="s">
         <v>121</v>
       </c>
-      <c r="K48" s="6" t="s">
+      <c r="K48" s="50" t="s">
+        <v>549</v>
+      </c>
+      <c r="L48" s="6" t="s">
         <v>351</v>
       </c>
-      <c r="L48" s="9"/>
-    </row>
-    <row r="49" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="M48" s="9"/>
+    </row>
+    <row r="49" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B49" s="46"/>
       <c r="C49" s="5">
         <v>7</v>
@@ -4018,12 +4765,15 @@
       <c r="J49" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="K49" s="6" t="s">
+      <c r="K49" s="50" t="s">
+        <v>550</v>
+      </c>
+      <c r="L49" s="6" t="s">
         <v>161</v>
       </c>
-      <c r="L49" s="9"/>
-    </row>
-    <row r="50" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="M49" s="9"/>
+    </row>
+    <row r="50" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B50" s="46"/>
       <c r="C50" s="5">
         <v>8</v>
@@ -4049,12 +4799,15 @@
       <c r="J50" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="K50" s="6" t="s">
+      <c r="K50" s="50" t="s">
+        <v>551</v>
+      </c>
+      <c r="L50" s="6" t="s">
         <v>352</v>
       </c>
-      <c r="L50" s="9"/>
-    </row>
-    <row r="51" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="M50" s="9"/>
+    </row>
+    <row r="51" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B51" s="46"/>
       <c r="C51" s="5">
         <v>9</v>
@@ -4080,12 +4833,15 @@
       <c r="J51" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="K51" s="6" t="s">
+      <c r="K51" s="50" t="s">
+        <v>552</v>
+      </c>
+      <c r="L51" s="6" t="s">
         <v>353</v>
       </c>
-      <c r="L51" s="9"/>
-    </row>
-    <row r="52" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="M51" s="9"/>
+    </row>
+    <row r="52" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B52" s="49"/>
       <c r="C52" s="5">
         <v>10</v>
@@ -4112,425 +4868,428 @@
         <v>142</v>
       </c>
       <c r="K52" s="16" t="s">
+        <v>553</v>
+      </c>
+      <c r="L52" s="16" t="s">
         <v>355</v>
       </c>
-      <c r="L52" s="9"/>
-    </row>
-    <row r="53" spans="2:12" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="M52" s="9"/>
+    </row>
+    <row r="53" spans="2:13" ht="15" thickTop="1" x14ac:dyDescent="0.35">
       <c r="C53" s="21"/>
-      <c r="L53" s="18"/>
-    </row>
-    <row r="54" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="M53" s="18"/>
+    </row>
+    <row r="54" spans="2:13" x14ac:dyDescent="0.35">
       <c r="C54"/>
       <c r="D54"/>
       <c r="E54"/>
       <c r="F54"/>
     </row>
-    <row r="55" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="55" spans="2:13" x14ac:dyDescent="0.35">
       <c r="C55"/>
       <c r="D55"/>
       <c r="E55"/>
       <c r="F55"/>
     </row>
-    <row r="56" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="56" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B56" s="20"/>
       <c r="C56" s="20"/>
       <c r="D56" s="20"/>
       <c r="E56" s="20"/>
       <c r="F56" s="20"/>
     </row>
-    <row r="57" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="57" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B57" s="20"/>
       <c r="C57" s="20"/>
       <c r="D57" s="20"/>
       <c r="E57" s="20"/>
       <c r="F57" s="20"/>
     </row>
-    <row r="58" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="58" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B58" s="20"/>
       <c r="C58" s="20"/>
       <c r="D58" s="20"/>
       <c r="E58" s="20"/>
       <c r="F58" s="20"/>
     </row>
-    <row r="59" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="59" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B59" s="20"/>
       <c r="C59" s="20"/>
       <c r="D59" s="20"/>
       <c r="E59" s="20"/>
       <c r="F59" s="20"/>
     </row>
-    <row r="60" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="60" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B60" s="20"/>
       <c r="C60" s="20"/>
       <c r="D60" s="20"/>
       <c r="E60" s="20"/>
       <c r="F60" s="20"/>
     </row>
-    <row r="61" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="61" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B61" s="20"/>
       <c r="C61" s="20"/>
       <c r="D61" s="20"/>
       <c r="E61" s="20"/>
       <c r="F61" s="20"/>
     </row>
-    <row r="62" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="62" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B62" s="20"/>
       <c r="C62" s="20"/>
       <c r="D62" s="20"/>
       <c r="E62" s="20"/>
       <c r="F62" s="20"/>
     </row>
-    <row r="63" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="63" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B63" s="20"/>
       <c r="C63" s="20"/>
       <c r="D63" s="20"/>
       <c r="E63" s="20"/>
       <c r="F63" s="20"/>
     </row>
-    <row r="64" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B64" s="20"/>
       <c r="C64" s="20"/>
       <c r="D64" s="20"/>
       <c r="E64" s="20"/>
       <c r="F64" s="20"/>
-      <c r="L64" s="19"/>
-    </row>
-    <row r="65" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="M64" s="19"/>
+    </row>
+    <row r="65" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B65" s="20"/>
       <c r="C65" s="20"/>
       <c r="D65" s="20"/>
       <c r="E65" s="20"/>
       <c r="F65" s="20"/>
-      <c r="L65" s="19"/>
-    </row>
-    <row r="66" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="M65" s="19"/>
+    </row>
+    <row r="66" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B66" s="20"/>
       <c r="C66" s="20"/>
       <c r="D66" s="20"/>
       <c r="E66" s="20"/>
       <c r="F66" s="20"/>
-      <c r="L66" s="19"/>
-    </row>
-    <row r="67" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="M66" s="19"/>
+    </row>
+    <row r="67" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B67" s="20"/>
       <c r="C67" s="20"/>
       <c r="D67" s="20"/>
       <c r="E67" s="20"/>
       <c r="F67" s="20"/>
-      <c r="L67" s="19"/>
-    </row>
-    <row r="68" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="M67" s="19"/>
+    </row>
+    <row r="68" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B68" s="20"/>
       <c r="C68" s="20"/>
       <c r="D68" s="20"/>
       <c r="E68" s="20"/>
       <c r="F68" s="20"/>
-      <c r="L68" s="19"/>
-    </row>
-    <row r="69" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="M68" s="19"/>
+    </row>
+    <row r="69" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B69" s="20"/>
       <c r="C69" s="20"/>
       <c r="D69" s="20"/>
       <c r="E69" s="20"/>
       <c r="F69" s="20"/>
-      <c r="L69" s="19"/>
-    </row>
-    <row r="70" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="M69" s="19"/>
+    </row>
+    <row r="70" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B70" s="20"/>
       <c r="C70" s="20"/>
       <c r="D70" s="20"/>
       <c r="E70" s="20"/>
       <c r="F70" s="20"/>
-      <c r="L70" s="19"/>
-    </row>
-    <row r="71" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="M70" s="19"/>
+    </row>
+    <row r="71" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B71" s="20"/>
       <c r="C71" s="20"/>
       <c r="D71" s="20"/>
       <c r="E71" s="20"/>
       <c r="F71" s="20"/>
-      <c r="L71" s="19"/>
-    </row>
-    <row r="72" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="M71" s="19"/>
+    </row>
+    <row r="72" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B72" s="20"/>
       <c r="C72" s="20"/>
       <c r="D72" s="20"/>
       <c r="E72" s="20"/>
       <c r="F72" s="20"/>
-      <c r="L72" s="19"/>
-    </row>
-    <row r="73" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="M72" s="19"/>
+    </row>
+    <row r="73" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B73" s="20"/>
       <c r="C73" s="20"/>
       <c r="D73" s="20"/>
       <c r="E73" s="20"/>
       <c r="F73" s="20"/>
-      <c r="L73" s="19"/>
-    </row>
-    <row r="74" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="M73" s="19"/>
+    </row>
+    <row r="74" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B74" s="20"/>
       <c r="C74" s="20"/>
       <c r="D74" s="20"/>
       <c r="E74" s="20"/>
       <c r="F74" s="20"/>
-      <c r="L74" s="19"/>
-    </row>
-    <row r="75" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="M74" s="19"/>
+    </row>
+    <row r="75" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B75" s="20"/>
       <c r="C75" s="20"/>
       <c r="D75" s="20"/>
       <c r="E75" s="20"/>
       <c r="F75" s="20"/>
-      <c r="L75" s="19"/>
-    </row>
-    <row r="76" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="M75" s="19"/>
+    </row>
+    <row r="76" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B76" s="20"/>
       <c r="C76" s="20"/>
       <c r="D76" s="20"/>
       <c r="E76" s="20"/>
       <c r="F76" s="20"/>
-      <c r="L76" s="19"/>
-    </row>
-    <row r="77" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="M76" s="19"/>
+    </row>
+    <row r="77" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B77" s="20"/>
       <c r="C77" s="20"/>
       <c r="D77" s="20"/>
       <c r="E77" s="20"/>
       <c r="F77" s="20"/>
-      <c r="L77" s="19"/>
-    </row>
-    <row r="78" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="M77" s="19"/>
+    </row>
+    <row r="78" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B78" s="20"/>
       <c r="C78" s="20"/>
       <c r="D78" s="20"/>
       <c r="E78" s="20"/>
       <c r="F78" s="20"/>
-      <c r="L78" s="19"/>
-    </row>
-    <row r="79" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="M78" s="19"/>
+    </row>
+    <row r="79" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B79" s="20"/>
       <c r="C79" s="20"/>
       <c r="D79" s="20"/>
       <c r="E79" s="20"/>
       <c r="F79" s="20"/>
-      <c r="L79" s="19"/>
-    </row>
-    <row r="80" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="M79" s="19"/>
+    </row>
+    <row r="80" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B80" s="20"/>
       <c r="C80" s="20"/>
       <c r="D80" s="20"/>
       <c r="E80" s="20"/>
       <c r="F80" s="20"/>
-      <c r="L80" s="19"/>
-    </row>
-    <row r="81" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="M80" s="19"/>
+    </row>
+    <row r="81" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B81" s="20"/>
       <c r="C81" s="20"/>
       <c r="D81" s="20"/>
       <c r="E81" s="20"/>
       <c r="F81" s="20"/>
-      <c r="L81" s="19"/>
-    </row>
-    <row r="82" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="M81" s="19"/>
+    </row>
+    <row r="82" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B82" s="20"/>
       <c r="C82" s="20"/>
       <c r="D82" s="20"/>
       <c r="E82" s="20"/>
       <c r="F82" s="20"/>
-      <c r="L82" s="19"/>
-    </row>
-    <row r="83" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="M82" s="19"/>
+    </row>
+    <row r="83" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B83" s="20"/>
       <c r="C83" s="20"/>
       <c r="D83" s="20"/>
       <c r="E83" s="20"/>
       <c r="F83" s="20"/>
-      <c r="L83" s="19"/>
-    </row>
-    <row r="84" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="M83" s="19"/>
+    </row>
+    <row r="84" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B84" s="20"/>
       <c r="C84" s="20"/>
       <c r="D84" s="20"/>
       <c r="E84" s="20"/>
       <c r="F84" s="20"/>
-      <c r="L84" s="19"/>
-    </row>
-    <row r="85" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="M84" s="19"/>
+    </row>
+    <row r="85" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B85" s="20"/>
       <c r="C85" s="20"/>
       <c r="D85" s="20"/>
       <c r="E85" s="20"/>
       <c r="F85" s="20"/>
-      <c r="L85" s="19"/>
-    </row>
-    <row r="86" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="M85" s="19"/>
+    </row>
+    <row r="86" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B86" s="20"/>
       <c r="C86" s="20"/>
       <c r="D86" s="20"/>
       <c r="E86" s="20"/>
       <c r="F86" s="20"/>
-      <c r="L86" s="19"/>
-    </row>
-    <row r="87" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="M86" s="19"/>
+    </row>
+    <row r="87" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B87" s="20"/>
       <c r="C87" s="20"/>
       <c r="D87" s="20"/>
       <c r="E87" s="20"/>
       <c r="F87" s="20"/>
-      <c r="L87" s="19"/>
-    </row>
-    <row r="88" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="M87" s="19"/>
+    </row>
+    <row r="88" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B88" s="20"/>
       <c r="C88" s="20"/>
       <c r="D88" s="20"/>
       <c r="E88" s="20"/>
       <c r="F88" s="20"/>
-      <c r="L88" s="19"/>
-    </row>
-    <row r="89" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="M88" s="19"/>
+    </row>
+    <row r="89" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B89" s="20"/>
       <c r="C89" s="20"/>
       <c r="D89" s="20"/>
       <c r="E89" s="20"/>
       <c r="F89" s="20"/>
-      <c r="L89" s="19"/>
-    </row>
-    <row r="90" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="M89" s="19"/>
+    </row>
+    <row r="90" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B90" s="20"/>
       <c r="C90" s="20"/>
       <c r="D90" s="20"/>
       <c r="E90" s="20"/>
       <c r="F90" s="20"/>
-      <c r="L90" s="19"/>
-    </row>
-    <row r="91" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="M90" s="19"/>
+    </row>
+    <row r="91" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B91" s="20"/>
       <c r="C91" s="20"/>
       <c r="D91" s="20"/>
       <c r="E91" s="20"/>
       <c r="F91" s="20"/>
-      <c r="L91" s="19"/>
-    </row>
-    <row r="92" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="M91" s="19"/>
+    </row>
+    <row r="92" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B92" s="20"/>
       <c r="C92" s="20"/>
       <c r="D92" s="20"/>
       <c r="E92" s="20"/>
       <c r="F92" s="20"/>
-      <c r="L92" s="19"/>
-    </row>
-    <row r="93" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="M92" s="19"/>
+    </row>
+    <row r="93" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B93" s="20"/>
       <c r="C93" s="20"/>
       <c r="D93" s="20"/>
       <c r="E93" s="20"/>
       <c r="F93" s="20"/>
-      <c r="L93" s="19"/>
-    </row>
-    <row r="94" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="M93" s="19"/>
+    </row>
+    <row r="94" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B94" s="20"/>
       <c r="C94" s="20"/>
       <c r="D94" s="20"/>
       <c r="E94" s="20"/>
       <c r="F94" s="20"/>
-      <c r="L94" s="19"/>
-    </row>
-    <row r="95" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="M94" s="19"/>
+    </row>
+    <row r="95" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B95" s="20"/>
       <c r="C95" s="20"/>
       <c r="D95" s="20"/>
       <c r="E95" s="20"/>
       <c r="F95" s="20"/>
-      <c r="L95" s="19"/>
-    </row>
-    <row r="96" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="M95" s="19"/>
+    </row>
+    <row r="96" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B96" s="20"/>
       <c r="C96" s="20"/>
       <c r="D96" s="20"/>
       <c r="E96" s="20"/>
       <c r="F96" s="20"/>
-      <c r="L96" s="19"/>
-    </row>
-    <row r="97" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="M96" s="19"/>
+    </row>
+    <row r="97" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B97" s="20"/>
       <c r="C97" s="20"/>
       <c r="D97" s="20"/>
       <c r="E97" s="20"/>
       <c r="F97" s="20"/>
-      <c r="L97" s="19"/>
-    </row>
-    <row r="98" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="M97" s="19"/>
+    </row>
+    <row r="98" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B98" s="20"/>
       <c r="C98" s="20"/>
       <c r="D98" s="20"/>
       <c r="E98" s="20"/>
       <c r="F98" s="20"/>
-      <c r="L98" s="19"/>
-    </row>
-    <row r="99" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="M98" s="19"/>
+    </row>
+    <row r="99" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B99" s="20"/>
       <c r="C99" s="20"/>
       <c r="D99" s="20"/>
       <c r="E99" s="20"/>
       <c r="F99" s="20"/>
-      <c r="L99" s="19"/>
-    </row>
-    <row r="100" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="M99" s="19"/>
+    </row>
+    <row r="100" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B100" s="20"/>
       <c r="C100" s="20"/>
       <c r="D100" s="20"/>
       <c r="E100" s="20"/>
       <c r="F100" s="20"/>
-      <c r="L100" s="19"/>
-    </row>
-    <row r="101" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="M100" s="19"/>
+    </row>
+    <row r="101" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B101" s="20"/>
       <c r="C101" s="20"/>
       <c r="D101" s="20"/>
       <c r="E101" s="20"/>
       <c r="F101" s="20"/>
-      <c r="L101" s="19"/>
-    </row>
-    <row r="102" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="M101" s="19"/>
+    </row>
+    <row r="102" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B102" s="20"/>
       <c r="C102" s="20"/>
       <c r="D102" s="20"/>
       <c r="E102" s="20"/>
       <c r="F102" s="20"/>
-      <c r="L102" s="19"/>
-    </row>
-    <row r="103" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="M102" s="19"/>
+    </row>
+    <row r="103" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B103" s="20"/>
       <c r="C103" s="20"/>
       <c r="D103" s="20"/>
       <c r="E103" s="20"/>
       <c r="F103" s="20"/>
-      <c r="L103" s="19"/>
-    </row>
-    <row r="104" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="M103" s="19"/>
+    </row>
+    <row r="104" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B104" s="20"/>
       <c r="C104" s="20"/>
       <c r="D104" s="20"/>
       <c r="E104" s="20"/>
       <c r="F104" s="20"/>
-      <c r="L104" s="19"/>
-    </row>
-    <row r="105" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="M104" s="19"/>
+    </row>
+    <row r="105" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B105" s="20"/>
       <c r="C105" s="20"/>
       <c r="D105" s="20"/>
       <c r="E105" s="20"/>
       <c r="F105" s="20"/>
-      <c r="L105" s="19"/>
-    </row>
-    <row r="106" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="M105" s="19"/>
+    </row>
+    <row r="106" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B106" s="20"/>
       <c r="C106" s="20"/>
       <c r="D106" s="20"/>
       <c r="E106" s="20"/>
       <c r="F106" s="20"/>
-      <c r="L106" s="19"/>
+      <c r="M106" s="19"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -4546,33 +5305,33 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="B1:L106"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="B1:M106"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="6" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="3.140625" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="3.1796875" style="3" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="15" style="3" customWidth="1"/>
-    <col min="5" max="5" width="6.28515625" style="3" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" style="3" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.140625" style="3" customWidth="1"/>
-    <col min="8" max="8" width="22.140625" style="3" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="47.85546875" style="3" customWidth="1"/>
-    <col min="10" max="10" width="45.7109375" style="3" customWidth="1"/>
-    <col min="11" max="11" width="30.140625" style="3" customWidth="1"/>
-    <col min="12" max="12" width="20.5703125" style="19" customWidth="1"/>
-    <col min="13" max="13" width="12.28515625" customWidth="1"/>
-    <col min="14" max="14" width="3.140625" customWidth="1"/>
-    <col min="15" max="15" width="24.7109375" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="4.42578125" customWidth="1"/>
-    <col min="17" max="17" width="23.5703125" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="30.42578125" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="46.140625" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="18.85546875" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="2" customWidth="1"/>
+    <col min="5" max="5" width="6.26953125" style="3" customWidth="1"/>
+    <col min="6" max="6" width="4.7265625" style="3" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.1796875" style="3" customWidth="1"/>
+    <col min="8" max="8" width="22.1796875" style="3" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="47.81640625" style="3" customWidth="1"/>
+    <col min="10" max="11" width="45.7265625" style="3" customWidth="1"/>
+    <col min="12" max="12" width="30.1796875" style="3" customWidth="1"/>
+    <col min="13" max="13" width="20.54296875" style="19" customWidth="1"/>
+    <col min="14" max="14" width="12.26953125" customWidth="1"/>
+    <col min="15" max="15" width="3.1796875" customWidth="1"/>
+    <col min="16" max="16" width="24.7265625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="4.453125" customWidth="1"/>
+    <col min="18" max="18" width="23.54296875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="30.453125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="46.1796875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="18.81640625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B1" s="1"/>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
@@ -4583,9 +5342,10 @@
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
       <c r="K1" s="2"/>
-      <c r="L1" s="4"/>
-    </row>
-    <row r="2" spans="2:12" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L1" s="2"/>
+      <c r="M1" s="4"/>
+    </row>
+    <row r="2" spans="2:13" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B2" s="24" t="s">
         <v>0</v>
       </c>
@@ -4614,13 +5374,16 @@
         <v>9</v>
       </c>
       <c r="K2" s="25" t="s">
+        <v>503</v>
+      </c>
+      <c r="L2" s="25" t="s">
         <v>2</v>
       </c>
-      <c r="L2" s="28" t="s">
+      <c r="M2" s="28" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="2:12" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:13" ht="15" thickTop="1" x14ac:dyDescent="0.35">
       <c r="B3" s="46">
         <v>1</v>
       </c>
@@ -4648,12 +5411,15 @@
       <c r="J3" s="33" t="s">
         <v>168</v>
       </c>
-      <c r="K3" s="32" t="s">
+      <c r="K3" s="33" t="s">
+        <v>554</v>
+      </c>
+      <c r="L3" s="32" t="s">
         <v>169</v>
       </c>
-      <c r="L3" s="39"/>
-    </row>
-    <row r="4" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="M3" s="39"/>
+    </row>
+    <row r="4" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B4" s="46"/>
       <c r="C4" s="5">
         <v>2</v>
@@ -4679,12 +5445,15 @@
       <c r="J4" s="8" t="s">
         <v>172</v>
       </c>
-      <c r="K4" s="35" t="s">
+      <c r="K4" s="8" t="s">
+        <v>555</v>
+      </c>
+      <c r="L4" s="35" t="s">
         <v>173</v>
       </c>
-      <c r="L4" s="40"/>
-    </row>
-    <row r="5" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="M4" s="40"/>
+    </row>
+    <row r="5" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B5" s="46"/>
       <c r="C5" s="5">
         <v>3</v>
@@ -4710,12 +5479,15 @@
       <c r="J5" s="8" t="s">
         <v>176</v>
       </c>
-      <c r="K5" s="35" t="s">
+      <c r="K5" s="8" t="s">
+        <v>556</v>
+      </c>
+      <c r="L5" s="35" t="s">
         <v>177</v>
       </c>
-      <c r="L5" s="40"/>
-    </row>
-    <row r="6" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="M5" s="40"/>
+    </row>
+    <row r="6" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B6" s="46"/>
       <c r="C6" s="5">
         <v>4</v>
@@ -4741,12 +5513,15 @@
       <c r="J6" s="8" t="s">
         <v>217</v>
       </c>
-      <c r="K6" s="35" t="s">
+      <c r="K6" s="8" t="s">
+        <v>557</v>
+      </c>
+      <c r="L6" s="35" t="s">
         <v>181</v>
       </c>
-      <c r="L6" s="40"/>
-    </row>
-    <row r="7" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="M6" s="40"/>
+    </row>
+    <row r="7" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B7" s="46"/>
       <c r="C7" s="23">
         <v>5</v>
@@ -4772,12 +5547,15 @@
       <c r="J7" s="8" t="s">
         <v>184</v>
       </c>
-      <c r="K7" s="35" t="s">
+      <c r="K7" s="8" t="s">
+        <v>558</v>
+      </c>
+      <c r="L7" s="35" t="s">
         <v>185</v>
       </c>
-      <c r="L7" s="40"/>
-    </row>
-    <row r="8" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="M7" s="40"/>
+    </row>
+    <row r="8" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B8" s="46"/>
       <c r="C8" s="5">
         <v>6</v>
@@ -4803,12 +5581,15 @@
       <c r="J8" s="8" t="s">
         <v>188</v>
       </c>
-      <c r="K8" s="35" t="s">
+      <c r="K8" s="8" t="s">
+        <v>559</v>
+      </c>
+      <c r="L8" s="35" t="s">
         <v>189</v>
       </c>
-      <c r="L8" s="40"/>
-    </row>
-    <row r="9" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="M8" s="40"/>
+    </row>
+    <row r="9" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B9" s="46"/>
       <c r="C9" s="5">
         <v>7</v>
@@ -4834,12 +5615,15 @@
       <c r="J9" s="8" t="s">
         <v>193</v>
       </c>
-      <c r="K9" s="35" t="s">
+      <c r="K9" s="8" t="s">
+        <v>560</v>
+      </c>
+      <c r="L9" s="35" t="s">
         <v>194</v>
       </c>
-      <c r="L9" s="40"/>
-    </row>
-    <row r="10" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="M9" s="40"/>
+    </row>
+    <row r="10" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B10" s="46"/>
       <c r="C10" s="5">
         <v>8</v>
@@ -4865,12 +5649,15 @@
       <c r="J10" s="8" t="s">
         <v>198</v>
       </c>
-      <c r="K10" s="35" t="s">
+      <c r="K10" s="8" t="s">
+        <v>561</v>
+      </c>
+      <c r="L10" s="35" t="s">
         <v>199</v>
       </c>
-      <c r="L10" s="40"/>
-    </row>
-    <row r="11" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="M10" s="40"/>
+    </row>
+    <row r="11" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B11" s="46"/>
       <c r="C11" s="5">
         <v>9</v>
@@ -4896,12 +5683,15 @@
       <c r="J11" s="8" t="s">
         <v>322</v>
       </c>
-      <c r="K11" s="35" t="s">
+      <c r="K11" s="8" t="s">
+        <v>562</v>
+      </c>
+      <c r="L11" s="35" t="s">
         <v>203</v>
       </c>
-      <c r="L11" s="40"/>
-    </row>
-    <row r="12" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="M11" s="40"/>
+    </row>
+    <row r="12" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B12" s="47"/>
       <c r="C12" s="10">
         <v>10</v>
@@ -4927,12 +5717,15 @@
       <c r="J12" s="12" t="s">
         <v>207</v>
       </c>
-      <c r="K12" s="36" t="s">
+      <c r="K12" s="12" t="s">
+        <v>563</v>
+      </c>
+      <c r="L12" s="36" t="s">
         <v>208</v>
       </c>
-      <c r="L12" s="40"/>
-    </row>
-    <row r="13" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="M12" s="40"/>
+    </row>
+    <row r="13" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B13" s="48">
         <v>2</v>
       </c>
@@ -4960,12 +5753,15 @@
       <c r="J13" s="15" t="s">
         <v>168</v>
       </c>
-      <c r="K13" s="37" t="s">
+      <c r="K13" s="15" t="s">
+        <v>564</v>
+      </c>
+      <c r="L13" s="37" t="s">
         <v>209</v>
       </c>
-      <c r="L13" s="40"/>
-    </row>
-    <row r="14" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="M13" s="40"/>
+    </row>
+    <row r="14" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B14" s="46"/>
       <c r="C14" s="5">
         <v>2</v>
@@ -4991,12 +5787,15 @@
       <c r="J14" s="8" t="s">
         <v>210</v>
       </c>
-      <c r="K14" s="35" t="s">
+      <c r="K14" s="8" t="s">
+        <v>565</v>
+      </c>
+      <c r="L14" s="35" t="s">
         <v>211</v>
       </c>
-      <c r="L14" s="40"/>
-    </row>
-    <row r="15" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="M14" s="40"/>
+    </row>
+    <row r="15" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B15" s="46"/>
       <c r="C15" s="5">
         <v>3</v>
@@ -5022,12 +5821,15 @@
       <c r="J15" s="8" t="s">
         <v>213</v>
       </c>
-      <c r="K15" s="35" t="s">
+      <c r="K15" s="8" t="s">
+        <v>566</v>
+      </c>
+      <c r="L15" s="35" t="s">
         <v>214</v>
       </c>
-      <c r="L15" s="40"/>
-    </row>
-    <row r="16" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="M15" s="40"/>
+    </row>
+    <row r="16" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B16" s="46"/>
       <c r="C16" s="5">
         <v>4</v>
@@ -5053,12 +5855,15 @@
       <c r="J16" s="8" t="s">
         <v>217</v>
       </c>
-      <c r="K16" s="35" t="s">
+      <c r="K16" s="8" t="s">
+        <v>567</v>
+      </c>
+      <c r="L16" s="35" t="s">
         <v>218</v>
       </c>
-      <c r="L16" s="40"/>
-    </row>
-    <row r="17" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="M16" s="40"/>
+    </row>
+    <row r="17" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B17" s="46"/>
       <c r="C17" s="23">
         <v>5</v>
@@ -5084,12 +5889,15 @@
       <c r="J17" s="8" t="s">
         <v>220</v>
       </c>
-      <c r="K17" s="35" t="s">
+      <c r="K17" s="8" t="s">
+        <v>568</v>
+      </c>
+      <c r="L17" s="35" t="s">
         <v>221</v>
       </c>
-      <c r="L17" s="40"/>
-    </row>
-    <row r="18" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="M17" s="40"/>
+    </row>
+    <row r="18" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B18" s="46"/>
       <c r="C18" s="5">
         <v>6</v>
@@ -5115,12 +5923,15 @@
       <c r="J18" s="8" t="s">
         <v>224</v>
       </c>
-      <c r="K18" s="35" t="s">
+      <c r="K18" s="8" t="s">
+        <v>569</v>
+      </c>
+      <c r="L18" s="35" t="s">
         <v>225</v>
       </c>
-      <c r="L18" s="40"/>
-    </row>
-    <row r="19" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="M18" s="40"/>
+    </row>
+    <row r="19" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B19" s="46"/>
       <c r="C19" s="5">
         <v>7</v>
@@ -5146,12 +5957,15 @@
       <c r="J19" s="8" t="s">
         <v>227</v>
       </c>
-      <c r="K19" s="35" t="s">
+      <c r="K19" s="8" t="s">
+        <v>570</v>
+      </c>
+      <c r="L19" s="35" t="s">
         <v>228</v>
       </c>
-      <c r="L19" s="40"/>
-    </row>
-    <row r="20" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="M19" s="40"/>
+    </row>
+    <row r="20" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B20" s="46"/>
       <c r="C20" s="5">
         <v>8</v>
@@ -5177,12 +5991,15 @@
       <c r="J20" s="8" t="s">
         <v>232</v>
       </c>
-      <c r="K20" s="35" t="s">
+      <c r="K20" s="8" t="s">
+        <v>571</v>
+      </c>
+      <c r="L20" s="35" t="s">
         <v>185</v>
       </c>
-      <c r="L20" s="40"/>
-    </row>
-    <row r="21" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="M20" s="40"/>
+    </row>
+    <row r="21" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B21" s="46"/>
       <c r="C21" s="5">
         <v>9</v>
@@ -5208,12 +6025,15 @@
       <c r="J21" s="8" t="s">
         <v>235</v>
       </c>
-      <c r="K21" s="35" t="s">
+      <c r="K21" s="8" t="s">
+        <v>572</v>
+      </c>
+      <c r="L21" s="35" t="s">
         <v>236</v>
       </c>
-      <c r="L21" s="40"/>
-    </row>
-    <row r="22" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="M21" s="40"/>
+    </row>
+    <row r="22" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B22" s="47"/>
       <c r="C22" s="10">
         <v>10</v>
@@ -5239,12 +6059,15 @@
       <c r="J22" s="12" t="s">
         <v>240</v>
       </c>
-      <c r="K22" s="36" t="s">
+      <c r="K22" s="12" t="s">
+        <v>573</v>
+      </c>
+      <c r="L22" s="36" t="s">
         <v>241</v>
       </c>
-      <c r="L22" s="40"/>
-    </row>
-    <row r="23" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="M22" s="40"/>
+    </row>
+    <row r="23" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B23" s="48">
         <v>3</v>
       </c>
@@ -5272,12 +6095,15 @@
       <c r="J23" s="15" t="s">
         <v>168</v>
       </c>
-      <c r="K23" s="37" t="s">
+      <c r="K23" s="15" t="s">
+        <v>574</v>
+      </c>
+      <c r="L23" s="37" t="s">
         <v>243</v>
       </c>
-      <c r="L23" s="40"/>
-    </row>
-    <row r="24" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="M23" s="40"/>
+    </row>
+    <row r="24" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B24" s="46"/>
       <c r="C24" s="5">
         <v>2</v>
@@ -5303,12 +6129,15 @@
       <c r="J24" s="8" t="s">
         <v>245</v>
       </c>
-      <c r="K24" s="35" t="s">
+      <c r="K24" s="8" t="s">
+        <v>575</v>
+      </c>
+      <c r="L24" s="35" t="s">
         <v>246</v>
       </c>
-      <c r="L24" s="40"/>
-    </row>
-    <row r="25" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="M24" s="40"/>
+    </row>
+    <row r="25" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B25" s="46"/>
       <c r="C25" s="5">
         <v>3</v>
@@ -5334,12 +6163,15 @@
       <c r="J25" s="8" t="s">
         <v>249</v>
       </c>
-      <c r="K25" s="35" t="s">
+      <c r="K25" s="8" t="s">
+        <v>576</v>
+      </c>
+      <c r="L25" s="35" t="s">
         <v>250</v>
       </c>
-      <c r="L25" s="40"/>
-    </row>
-    <row r="26" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="M25" s="40"/>
+    </row>
+    <row r="26" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B26" s="46"/>
       <c r="C26" s="5">
         <v>4</v>
@@ -5365,12 +6197,15 @@
       <c r="J26" s="8" t="s">
         <v>252</v>
       </c>
-      <c r="K26" s="35" t="s">
+      <c r="K26" s="8" t="s">
+        <v>577</v>
+      </c>
+      <c r="L26" s="35" t="s">
         <v>181</v>
       </c>
-      <c r="L26" s="40"/>
-    </row>
-    <row r="27" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="M26" s="40"/>
+    </row>
+    <row r="27" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B27" s="46"/>
       <c r="C27" s="23">
         <v>5</v>
@@ -5396,12 +6231,15 @@
       <c r="J27" s="8" t="s">
         <v>255</v>
       </c>
-      <c r="K27" s="35" t="s">
+      <c r="K27" s="8" t="s">
+        <v>578</v>
+      </c>
+      <c r="L27" s="35" t="s">
         <v>185</v>
       </c>
-      <c r="L27" s="40"/>
-    </row>
-    <row r="28" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="M27" s="40"/>
+    </row>
+    <row r="28" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B28" s="46"/>
       <c r="C28" s="5">
         <v>6</v>
@@ -5427,12 +6265,15 @@
       <c r="J28" s="8" t="s">
         <v>258</v>
       </c>
-      <c r="K28" s="35" t="s">
+      <c r="K28" s="8" t="s">
+        <v>579</v>
+      </c>
+      <c r="L28" s="35" t="s">
         <v>189</v>
       </c>
-      <c r="L28" s="40"/>
-    </row>
-    <row r="29" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="M28" s="40"/>
+    </row>
+    <row r="29" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B29" s="46"/>
       <c r="C29" s="5">
         <v>7</v>
@@ -5458,12 +6299,15 @@
       <c r="J29" s="8" t="s">
         <v>261</v>
       </c>
-      <c r="K29" s="35" t="s">
+      <c r="K29" s="8" t="s">
+        <v>580</v>
+      </c>
+      <c r="L29" s="35" t="s">
         <v>262</v>
       </c>
-      <c r="L29" s="40"/>
-    </row>
-    <row r="30" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="M29" s="40"/>
+    </row>
+    <row r="30" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B30" s="46"/>
       <c r="C30" s="5">
         <v>8</v>
@@ -5489,12 +6333,15 @@
       <c r="J30" s="8" t="s">
         <v>266</v>
       </c>
-      <c r="K30" s="35" t="s">
+      <c r="K30" s="8" t="s">
+        <v>581</v>
+      </c>
+      <c r="L30" s="35" t="s">
         <v>221</v>
       </c>
-      <c r="L30" s="40"/>
-    </row>
-    <row r="31" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="M30" s="40"/>
+    </row>
+    <row r="31" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B31" s="46"/>
       <c r="C31" s="5">
         <v>9</v>
@@ -5520,12 +6367,15 @@
       <c r="J31" s="8" t="s">
         <v>269</v>
       </c>
-      <c r="K31" s="35" t="s">
+      <c r="K31" s="8" t="s">
+        <v>582</v>
+      </c>
+      <c r="L31" s="35" t="s">
         <v>270</v>
       </c>
-      <c r="L31" s="40"/>
-    </row>
-    <row r="32" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="M31" s="40"/>
+    </row>
+    <row r="32" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B32" s="47"/>
       <c r="C32" s="10">
         <v>10</v>
@@ -5551,12 +6401,15 @@
       <c r="J32" s="12" t="s">
         <v>274</v>
       </c>
-      <c r="K32" s="36" t="s">
+      <c r="K32" s="12" t="s">
+        <v>583</v>
+      </c>
+      <c r="L32" s="36" t="s">
         <v>208</v>
       </c>
-      <c r="L32" s="40"/>
-    </row>
-    <row r="33" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="M32" s="40"/>
+    </row>
+    <row r="33" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B33" s="48">
         <v>4</v>
       </c>
@@ -5584,12 +6437,15 @@
       <c r="J33" s="15" t="s">
         <v>275</v>
       </c>
-      <c r="K33" s="37" t="s">
+      <c r="K33" s="15" t="s">
+        <v>584</v>
+      </c>
+      <c r="L33" s="37" t="s">
         <v>276</v>
       </c>
-      <c r="L33" s="40"/>
-    </row>
-    <row r="34" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="M33" s="40"/>
+    </row>
+    <row r="34" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B34" s="46"/>
       <c r="C34" s="5">
         <v>2</v>
@@ -5615,12 +6471,15 @@
       <c r="J34" s="8" t="s">
         <v>277</v>
       </c>
-      <c r="K34" s="35" t="s">
+      <c r="K34" s="8" t="s">
+        <v>585</v>
+      </c>
+      <c r="L34" s="35" t="s">
         <v>278</v>
       </c>
-      <c r="L34" s="40"/>
-    </row>
-    <row r="35" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="M34" s="40"/>
+    </row>
+    <row r="35" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B35" s="46"/>
       <c r="C35" s="5">
         <v>3</v>
@@ -5646,12 +6505,15 @@
       <c r="J35" s="8" t="s">
         <v>213</v>
       </c>
-      <c r="K35" s="35" t="s">
+      <c r="K35" s="8" t="s">
+        <v>586</v>
+      </c>
+      <c r="L35" s="35" t="s">
         <v>218</v>
       </c>
-      <c r="L35" s="40"/>
-    </row>
-    <row r="36" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="M35" s="40"/>
+    </row>
+    <row r="36" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B36" s="46"/>
       <c r="C36" s="5">
         <v>4</v>
@@ -5677,12 +6539,15 @@
       <c r="J36" s="8" t="s">
         <v>282</v>
       </c>
-      <c r="K36" s="35" t="s">
+      <c r="K36" s="8" t="s">
+        <v>587</v>
+      </c>
+      <c r="L36" s="35" t="s">
         <v>221</v>
       </c>
-      <c r="L36" s="40"/>
-    </row>
-    <row r="37" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="M36" s="40"/>
+    </row>
+    <row r="37" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B37" s="46"/>
       <c r="C37" s="23">
         <v>5</v>
@@ -5708,12 +6573,15 @@
       <c r="J37" s="8" t="s">
         <v>227</v>
       </c>
-      <c r="K37" s="35" t="s">
+      <c r="K37" s="8" t="s">
+        <v>588</v>
+      </c>
+      <c r="L37" s="35" t="s">
         <v>228</v>
       </c>
-      <c r="L37" s="40"/>
-    </row>
-    <row r="38" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="M37" s="40"/>
+    </row>
+    <row r="38" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B38" s="46"/>
       <c r="C38" s="5">
         <v>6</v>
@@ -5739,12 +6607,15 @@
       <c r="J38" s="8" t="s">
         <v>285</v>
       </c>
-      <c r="K38" s="35" t="s">
+      <c r="K38" s="8" t="s">
+        <v>589</v>
+      </c>
+      <c r="L38" s="35" t="s">
         <v>286</v>
       </c>
-      <c r="L38" s="40"/>
-    </row>
-    <row r="39" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="M38" s="40"/>
+    </row>
+    <row r="39" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B39" s="46"/>
       <c r="C39" s="5">
         <v>7</v>
@@ -5770,12 +6641,15 @@
       <c r="J39" s="8" t="s">
         <v>288</v>
       </c>
-      <c r="K39" s="35" t="s">
+      <c r="K39" s="8" t="s">
+        <v>590</v>
+      </c>
+      <c r="L39" s="35" t="s">
         <v>289</v>
       </c>
-      <c r="L39" s="40"/>
-    </row>
-    <row r="40" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="M39" s="40"/>
+    </row>
+    <row r="40" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B40" s="46"/>
       <c r="C40" s="5">
         <v>8</v>
@@ -5801,12 +6675,15 @@
       <c r="J40" s="8" t="s">
         <v>245</v>
       </c>
-      <c r="K40" s="35" t="s">
+      <c r="K40" s="8" t="s">
+        <v>591</v>
+      </c>
+      <c r="L40" s="35" t="s">
         <v>211</v>
       </c>
-      <c r="L40" s="40"/>
-    </row>
-    <row r="41" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="M40" s="40"/>
+    </row>
+    <row r="41" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B41" s="46"/>
       <c r="C41" s="5">
         <v>9</v>
@@ -5832,12 +6709,15 @@
       <c r="J41" s="8" t="s">
         <v>294</v>
       </c>
-      <c r="K41" s="35" t="s">
+      <c r="K41" s="8" t="s">
+        <v>592</v>
+      </c>
+      <c r="L41" s="35" t="s">
         <v>295</v>
       </c>
-      <c r="L41" s="40"/>
-    </row>
-    <row r="42" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="M41" s="40"/>
+    </row>
+    <row r="42" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B42" s="47"/>
       <c r="C42" s="10">
         <v>10</v>
@@ -5863,12 +6743,15 @@
       <c r="J42" s="12" t="s">
         <v>298</v>
       </c>
-      <c r="K42" s="36" t="s">
+      <c r="K42" s="12" t="s">
+        <v>593</v>
+      </c>
+      <c r="L42" s="36" t="s">
         <v>299</v>
       </c>
-      <c r="L42" s="40"/>
-    </row>
-    <row r="43" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="M42" s="40"/>
+    </row>
+    <row r="43" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B43" s="48">
         <v>5</v>
       </c>
@@ -5896,12 +6779,15 @@
       <c r="J43" s="15" t="s">
         <v>300</v>
       </c>
-      <c r="K43" s="37" t="s">
+      <c r="K43" s="15" t="s">
+        <v>594</v>
+      </c>
+      <c r="L43" s="37" t="s">
         <v>169</v>
       </c>
-      <c r="L43" s="40"/>
-    </row>
-    <row r="44" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="M43" s="40"/>
+    </row>
+    <row r="44" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B44" s="46"/>
       <c r="C44" s="5">
         <v>2</v>
@@ -5927,12 +6813,15 @@
       <c r="J44" s="8" t="s">
         <v>301</v>
       </c>
-      <c r="K44" s="35" t="s">
+      <c r="K44" s="8" t="s">
+        <v>595</v>
+      </c>
+      <c r="L44" s="35" t="s">
         <v>302</v>
       </c>
-      <c r="L44" s="40"/>
-    </row>
-    <row r="45" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="M44" s="40"/>
+    </row>
+    <row r="45" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B45" s="46"/>
       <c r="C45" s="5">
         <v>3</v>
@@ -5958,12 +6847,15 @@
       <c r="J45" s="8" t="s">
         <v>304</v>
       </c>
-      <c r="K45" s="35" t="s">
+      <c r="K45" s="8" t="s">
+        <v>596</v>
+      </c>
+      <c r="L45" s="35" t="s">
         <v>305</v>
       </c>
-      <c r="L45" s="40"/>
-    </row>
-    <row r="46" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="M45" s="40"/>
+    </row>
+    <row r="46" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B46" s="46"/>
       <c r="C46" s="5">
         <v>4</v>
@@ -5989,12 +6881,15 @@
       <c r="J46" s="8" t="s">
         <v>306</v>
       </c>
-      <c r="K46" s="35" t="s">
+      <c r="K46" s="8" t="s">
+        <v>597</v>
+      </c>
+      <c r="L46" s="35" t="s">
         <v>181</v>
       </c>
-      <c r="L46" s="40"/>
-    </row>
-    <row r="47" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="M46" s="40"/>
+    </row>
+    <row r="47" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B47" s="46"/>
       <c r="C47" s="23">
         <v>5</v>
@@ -6020,12 +6915,15 @@
       <c r="J47" s="8" t="s">
         <v>308</v>
       </c>
-      <c r="K47" s="35" t="s">
+      <c r="K47" s="8" t="s">
+        <v>598</v>
+      </c>
+      <c r="L47" s="35" t="s">
         <v>154</v>
       </c>
-      <c r="L47" s="40"/>
-    </row>
-    <row r="48" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="M47" s="40"/>
+    </row>
+    <row r="48" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B48" s="46"/>
       <c r="C48" s="5">
         <v>6</v>
@@ -6051,12 +6949,15 @@
       <c r="J48" s="8" t="s">
         <v>310</v>
       </c>
-      <c r="K48" s="35" t="s">
+      <c r="K48" s="8" t="s">
+        <v>599</v>
+      </c>
+      <c r="L48" s="35" t="s">
         <v>311</v>
       </c>
-      <c r="L48" s="40"/>
-    </row>
-    <row r="49" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="M48" s="40"/>
+    </row>
+    <row r="49" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B49" s="46"/>
       <c r="C49" s="5">
         <v>7</v>
@@ -6082,12 +6983,15 @@
       <c r="J49" s="8" t="s">
         <v>312</v>
       </c>
-      <c r="K49" s="35" t="s">
+      <c r="K49" s="8" t="s">
+        <v>600</v>
+      </c>
+      <c r="L49" s="35" t="s">
         <v>236</v>
       </c>
-      <c r="L49" s="40"/>
-    </row>
-    <row r="50" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="M49" s="40"/>
+    </row>
+    <row r="50" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B50" s="46"/>
       <c r="C50" s="5">
         <v>8</v>
@@ -6113,12 +7017,15 @@
       <c r="J50" s="8" t="s">
         <v>314</v>
       </c>
-      <c r="K50" s="35" t="s">
+      <c r="K50" s="8" t="s">
+        <v>601</v>
+      </c>
+      <c r="L50" s="35" t="s">
         <v>185</v>
       </c>
-      <c r="L50" s="40"/>
-    </row>
-    <row r="51" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="M50" s="40"/>
+    </row>
+    <row r="51" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B51" s="46"/>
       <c r="C51" s="5">
         <v>9</v>
@@ -6144,12 +7051,15 @@
       <c r="J51" s="8" t="s">
         <v>317</v>
       </c>
-      <c r="K51" s="35" t="s">
+      <c r="K51" s="8" t="s">
+        <v>602</v>
+      </c>
+      <c r="L51" s="35" t="s">
         <v>318</v>
       </c>
-      <c r="L51" s="40"/>
-    </row>
-    <row r="52" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="M51" s="40"/>
+    </row>
+    <row r="52" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B52" s="49"/>
       <c r="C52" s="5">
         <v>10</v>
@@ -6175,426 +7085,429 @@
       <c r="J52" s="17" t="s">
         <v>213</v>
       </c>
-      <c r="K52" s="38" t="s">
+      <c r="K52" s="17" t="s">
+        <v>603</v>
+      </c>
+      <c r="L52" s="38" t="s">
         <v>241</v>
       </c>
-      <c r="L52" s="41"/>
-    </row>
-    <row r="53" spans="2:12" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="M52" s="41"/>
+    </row>
+    <row r="53" spans="2:13" ht="15" thickTop="1" x14ac:dyDescent="0.35">
       <c r="C53" s="21"/>
-      <c r="L53" s="18"/>
-    </row>
-    <row r="54" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="M53" s="18"/>
+    </row>
+    <row r="54" spans="2:13" x14ac:dyDescent="0.35">
       <c r="C54"/>
       <c r="D54"/>
       <c r="E54"/>
       <c r="F54"/>
     </row>
-    <row r="55" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="55" spans="2:13" x14ac:dyDescent="0.35">
       <c r="C55"/>
       <c r="D55"/>
       <c r="E55"/>
       <c r="F55"/>
     </row>
-    <row r="56" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="56" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B56" s="20"/>
       <c r="C56" s="20"/>
       <c r="D56" s="20"/>
       <c r="E56" s="20"/>
       <c r="F56" s="20"/>
     </row>
-    <row r="57" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="57" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B57" s="20"/>
       <c r="C57" s="20"/>
       <c r="D57" s="20"/>
       <c r="E57" s="20"/>
       <c r="F57" s="20"/>
     </row>
-    <row r="58" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="58" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B58" s="20"/>
       <c r="C58" s="20"/>
       <c r="D58" s="20"/>
       <c r="E58" s="20"/>
       <c r="F58" s="20"/>
     </row>
-    <row r="59" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="59" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B59" s="20"/>
       <c r="C59" s="20"/>
       <c r="D59" s="20"/>
       <c r="E59" s="20"/>
       <c r="F59" s="20"/>
     </row>
-    <row r="60" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="60" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B60" s="20"/>
       <c r="C60" s="20"/>
       <c r="D60" s="20"/>
       <c r="E60" s="20"/>
       <c r="F60" s="20"/>
     </row>
-    <row r="61" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="61" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B61" s="20"/>
       <c r="C61" s="20"/>
       <c r="D61" s="20"/>
       <c r="E61" s="20"/>
       <c r="F61" s="20"/>
     </row>
-    <row r="62" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="62" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B62" s="20"/>
       <c r="C62" s="20"/>
       <c r="D62" s="20"/>
       <c r="E62" s="20"/>
       <c r="F62" s="20"/>
     </row>
-    <row r="63" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="63" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B63" s="20"/>
       <c r="C63" s="20"/>
       <c r="D63" s="20"/>
       <c r="E63" s="20"/>
       <c r="F63" s="20"/>
     </row>
-    <row r="64" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B64" s="20"/>
       <c r="C64" s="20"/>
       <c r="D64" s="20"/>
       <c r="E64" s="20"/>
       <c r="F64" s="20"/>
-      <c r="L64" s="19"/>
-    </row>
-    <row r="65" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="M64" s="19"/>
+    </row>
+    <row r="65" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B65" s="20"/>
       <c r="C65" s="20"/>
       <c r="D65" s="20"/>
       <c r="E65" s="20"/>
       <c r="F65" s="20"/>
-      <c r="L65" s="19"/>
-    </row>
-    <row r="66" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="M65" s="19"/>
+    </row>
+    <row r="66" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B66" s="20"/>
       <c r="C66" s="20"/>
       <c r="D66" s="20"/>
       <c r="E66" s="20"/>
       <c r="F66" s="20"/>
-      <c r="L66" s="19"/>
-    </row>
-    <row r="67" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="M66" s="19"/>
+    </row>
+    <row r="67" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B67" s="20"/>
       <c r="C67" s="20"/>
       <c r="D67" s="20"/>
       <c r="E67" s="20"/>
       <c r="F67" s="20"/>
-      <c r="L67" s="19"/>
-    </row>
-    <row r="68" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="M67" s="19"/>
+    </row>
+    <row r="68" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B68" s="20"/>
       <c r="C68" s="20"/>
       <c r="D68" s="20"/>
       <c r="E68" s="20"/>
       <c r="F68" s="20"/>
-      <c r="L68" s="19"/>
-    </row>
-    <row r="69" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="M68" s="19"/>
+    </row>
+    <row r="69" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B69" s="20"/>
       <c r="C69" s="20"/>
       <c r="D69" s="20"/>
       <c r="E69" s="20"/>
       <c r="F69" s="20"/>
-      <c r="L69" s="19"/>
-    </row>
-    <row r="70" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="M69" s="19"/>
+    </row>
+    <row r="70" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B70" s="20"/>
       <c r="C70" s="20"/>
       <c r="D70" s="20"/>
       <c r="E70" s="20"/>
       <c r="F70" s="20"/>
-      <c r="L70" s="19"/>
-    </row>
-    <row r="71" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="M70" s="19"/>
+    </row>
+    <row r="71" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B71" s="20"/>
       <c r="C71" s="20"/>
       <c r="D71" s="20"/>
       <c r="E71" s="20"/>
       <c r="F71" s="20"/>
-      <c r="L71" s="19"/>
-    </row>
-    <row r="72" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="M71" s="19"/>
+    </row>
+    <row r="72" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B72" s="20"/>
       <c r="C72" s="20"/>
       <c r="D72" s="20"/>
       <c r="E72" s="20"/>
       <c r="F72" s="20"/>
-      <c r="L72" s="19"/>
-    </row>
-    <row r="73" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="M72" s="19"/>
+    </row>
+    <row r="73" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B73" s="20"/>
       <c r="C73" s="20"/>
       <c r="D73" s="20"/>
       <c r="E73" s="20"/>
       <c r="F73" s="20"/>
-      <c r="L73" s="19"/>
-    </row>
-    <row r="74" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="M73" s="19"/>
+    </row>
+    <row r="74" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B74" s="20"/>
       <c r="C74" s="20"/>
       <c r="D74" s="20"/>
       <c r="E74" s="20"/>
       <c r="F74" s="20"/>
-      <c r="L74" s="19"/>
-    </row>
-    <row r="75" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="M74" s="19"/>
+    </row>
+    <row r="75" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B75" s="20"/>
       <c r="C75" s="20"/>
       <c r="D75" s="20"/>
       <c r="E75" s="20"/>
       <c r="F75" s="20"/>
-      <c r="L75" s="19"/>
-    </row>
-    <row r="76" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="M75" s="19"/>
+    </row>
+    <row r="76" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B76" s="20"/>
       <c r="C76" s="20"/>
       <c r="D76" s="20"/>
       <c r="E76" s="20"/>
       <c r="F76" s="20"/>
-      <c r="L76" s="19"/>
-    </row>
-    <row r="77" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="M76" s="19"/>
+    </row>
+    <row r="77" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B77" s="20"/>
       <c r="C77" s="20"/>
       <c r="D77" s="20"/>
       <c r="E77" s="20"/>
       <c r="F77" s="20"/>
-      <c r="L77" s="19"/>
-    </row>
-    <row r="78" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="M77" s="19"/>
+    </row>
+    <row r="78" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B78" s="20"/>
       <c r="C78" s="20"/>
       <c r="D78" s="20"/>
       <c r="E78" s="20"/>
       <c r="F78" s="20"/>
-      <c r="L78" s="19"/>
-    </row>
-    <row r="79" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="M78" s="19"/>
+    </row>
+    <row r="79" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B79" s="20"/>
       <c r="C79" s="20"/>
       <c r="D79" s="20"/>
       <c r="E79" s="20"/>
       <c r="F79" s="20"/>
-      <c r="L79" s="19"/>
-    </row>
-    <row r="80" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="M79" s="19"/>
+    </row>
+    <row r="80" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B80" s="20"/>
       <c r="C80" s="20"/>
       <c r="D80" s="20"/>
       <c r="E80" s="20"/>
       <c r="F80" s="20"/>
-      <c r="L80" s="19"/>
-    </row>
-    <row r="81" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="M80" s="19"/>
+    </row>
+    <row r="81" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B81" s="20"/>
       <c r="C81" s="20"/>
       <c r="D81" s="20"/>
       <c r="E81" s="20"/>
       <c r="F81" s="20"/>
-      <c r="L81" s="19"/>
-    </row>
-    <row r="82" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="M81" s="19"/>
+    </row>
+    <row r="82" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B82" s="20"/>
       <c r="C82" s="20"/>
       <c r="D82" s="20"/>
       <c r="E82" s="20"/>
       <c r="F82" s="20"/>
-      <c r="L82" s="19"/>
-    </row>
-    <row r="83" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="M82" s="19"/>
+    </row>
+    <row r="83" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B83" s="20"/>
       <c r="C83" s="20"/>
       <c r="D83" s="20"/>
       <c r="E83" s="20"/>
       <c r="F83" s="20"/>
-      <c r="L83" s="19"/>
-    </row>
-    <row r="84" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="M83" s="19"/>
+    </row>
+    <row r="84" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B84" s="20"/>
       <c r="C84" s="20"/>
       <c r="D84" s="20"/>
       <c r="E84" s="20"/>
       <c r="F84" s="20"/>
-      <c r="L84" s="19"/>
-    </row>
-    <row r="85" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="M84" s="19"/>
+    </row>
+    <row r="85" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B85" s="20"/>
       <c r="C85" s="20"/>
       <c r="D85" s="20"/>
       <c r="E85" s="20"/>
       <c r="F85" s="20"/>
-      <c r="L85" s="19"/>
-    </row>
-    <row r="86" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="M85" s="19"/>
+    </row>
+    <row r="86" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B86" s="20"/>
       <c r="C86" s="20"/>
       <c r="D86" s="20"/>
       <c r="E86" s="20"/>
       <c r="F86" s="20"/>
-      <c r="L86" s="19"/>
-    </row>
-    <row r="87" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="M86" s="19"/>
+    </row>
+    <row r="87" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B87" s="20"/>
       <c r="C87" s="20"/>
       <c r="D87" s="20"/>
       <c r="E87" s="20"/>
       <c r="F87" s="20"/>
-      <c r="L87" s="19"/>
-    </row>
-    <row r="88" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="M87" s="19"/>
+    </row>
+    <row r="88" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B88" s="20"/>
       <c r="C88" s="20"/>
       <c r="D88" s="20"/>
       <c r="E88" s="20"/>
       <c r="F88" s="20"/>
-      <c r="L88" s="19"/>
-    </row>
-    <row r="89" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="M88" s="19"/>
+    </row>
+    <row r="89" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B89" s="20"/>
       <c r="C89" s="20"/>
       <c r="D89" s="20"/>
       <c r="E89" s="20"/>
       <c r="F89" s="20"/>
-      <c r="L89" s="19"/>
-    </row>
-    <row r="90" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="M89" s="19"/>
+    </row>
+    <row r="90" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B90" s="20"/>
       <c r="C90" s="20"/>
       <c r="D90" s="20"/>
       <c r="E90" s="20"/>
       <c r="F90" s="20"/>
-      <c r="L90" s="19"/>
-    </row>
-    <row r="91" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="M90" s="19"/>
+    </row>
+    <row r="91" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B91" s="20"/>
       <c r="C91" s="20"/>
       <c r="D91" s="20"/>
       <c r="E91" s="20"/>
       <c r="F91" s="20"/>
-      <c r="L91" s="19"/>
-    </row>
-    <row r="92" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="M91" s="19"/>
+    </row>
+    <row r="92" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B92" s="20"/>
       <c r="C92" s="20"/>
       <c r="D92" s="20"/>
       <c r="E92" s="20"/>
       <c r="F92" s="20"/>
-      <c r="L92" s="19"/>
-    </row>
-    <row r="93" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="M92" s="19"/>
+    </row>
+    <row r="93" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B93" s="20"/>
       <c r="C93" s="20"/>
       <c r="D93" s="20"/>
       <c r="E93" s="20"/>
       <c r="F93" s="20"/>
-      <c r="L93" s="19"/>
-    </row>
-    <row r="94" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="M93" s="19"/>
+    </row>
+    <row r="94" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B94" s="20"/>
       <c r="C94" s="20"/>
       <c r="D94" s="20"/>
       <c r="E94" s="20"/>
       <c r="F94" s="20"/>
-      <c r="L94" s="19"/>
-    </row>
-    <row r="95" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="M94" s="19"/>
+    </row>
+    <row r="95" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B95" s="20"/>
       <c r="C95" s="20"/>
       <c r="D95" s="20"/>
       <c r="E95" s="20"/>
       <c r="F95" s="20"/>
-      <c r="L95" s="19"/>
-    </row>
-    <row r="96" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="M95" s="19"/>
+    </row>
+    <row r="96" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B96" s="20"/>
       <c r="C96" s="20"/>
       <c r="D96" s="20"/>
       <c r="E96" s="20"/>
       <c r="F96" s="20"/>
-      <c r="L96" s="19"/>
-    </row>
-    <row r="97" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="M96" s="19"/>
+    </row>
+    <row r="97" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B97" s="20"/>
       <c r="C97" s="20"/>
       <c r="D97" s="20"/>
       <c r="E97" s="20"/>
       <c r="F97" s="20"/>
-      <c r="L97" s="19"/>
-    </row>
-    <row r="98" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="M97" s="19"/>
+    </row>
+    <row r="98" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B98" s="20"/>
       <c r="C98" s="20"/>
       <c r="D98" s="20"/>
       <c r="E98" s="20"/>
       <c r="F98" s="20"/>
-      <c r="L98" s="19"/>
-    </row>
-    <row r="99" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="M98" s="19"/>
+    </row>
+    <row r="99" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B99" s="20"/>
       <c r="C99" s="20"/>
       <c r="D99" s="20"/>
       <c r="E99" s="20"/>
       <c r="F99" s="20"/>
-      <c r="L99" s="19"/>
-    </row>
-    <row r="100" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="M99" s="19"/>
+    </row>
+    <row r="100" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B100" s="20"/>
       <c r="C100" s="20"/>
       <c r="D100" s="20"/>
       <c r="E100" s="20"/>
       <c r="F100" s="20"/>
-      <c r="L100" s="19"/>
-    </row>
-    <row r="101" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="M100" s="19"/>
+    </row>
+    <row r="101" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B101" s="20"/>
       <c r="C101" s="20"/>
       <c r="D101" s="20"/>
       <c r="E101" s="20"/>
       <c r="F101" s="20"/>
-      <c r="L101" s="19"/>
-    </row>
-    <row r="102" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="M101" s="19"/>
+    </row>
+    <row r="102" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B102" s="20"/>
       <c r="C102" s="20"/>
       <c r="D102" s="20"/>
       <c r="E102" s="20"/>
       <c r="F102" s="20"/>
-      <c r="L102" s="19"/>
-    </row>
-    <row r="103" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="M102" s="19"/>
+    </row>
+    <row r="103" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B103" s="20"/>
       <c r="C103" s="20"/>
       <c r="D103" s="20"/>
       <c r="E103" s="20"/>
       <c r="F103" s="20"/>
-      <c r="L103" s="19"/>
-    </row>
-    <row r="104" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="M103" s="19"/>
+    </row>
+    <row r="104" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B104" s="20"/>
       <c r="C104" s="20"/>
       <c r="D104" s="20"/>
       <c r="E104" s="20"/>
       <c r="F104" s="20"/>
-      <c r="L104" s="19"/>
-    </row>
-    <row r="105" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="M104" s="19"/>
+    </row>
+    <row r="105" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B105" s="20"/>
       <c r="C105" s="20"/>
       <c r="D105" s="20"/>
       <c r="E105" s="20"/>
       <c r="F105" s="20"/>
-      <c r="L105" s="19"/>
-    </row>
-    <row r="106" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="M105" s="19"/>
+    </row>
+    <row r="106" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B106" s="20"/>
       <c r="C106" s="20"/>
       <c r="D106" s="20"/>
       <c r="E106" s="20"/>
       <c r="F106" s="20"/>
-      <c r="L106" s="19"/>
+      <c r="M106" s="19"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -6610,34 +7523,34 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="B1:M106"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="B1:N106"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="6" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="3.140625" style="3" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="6.5703125" style="3" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="3.85546875" style="3" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="4.28515625" style="3" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.42578125" style="3" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="20.42578125" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="3.1796875" style="3" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6.54296875" style="3" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="3.81640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="4.26953125" style="3" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.453125" style="3" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="20.453125" style="3" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="17" style="3" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="21.85546875" style="3" customWidth="1"/>
-    <col min="11" max="11" width="77.85546875" style="3" customWidth="1"/>
-    <col min="12" max="12" width="15.28515625" style="19" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="80.7109375" style="19" customWidth="1"/>
-    <col min="14" max="14" width="6.85546875" customWidth="1"/>
-    <col min="15" max="15" width="3.140625" customWidth="1"/>
-    <col min="16" max="16" width="24.7109375" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="4.42578125" customWidth="1"/>
-    <col min="18" max="18" width="23.5703125" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="30.42578125" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="46.140625" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="18.85546875" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="2" customWidth="1"/>
+    <col min="10" max="11" width="21.81640625" style="3" customWidth="1"/>
+    <col min="12" max="12" width="77.81640625" style="3" customWidth="1"/>
+    <col min="13" max="13" width="15.26953125" style="19" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="80.7265625" style="19" customWidth="1"/>
+    <col min="15" max="15" width="6.81640625" customWidth="1"/>
+    <col min="16" max="16" width="3.1796875" customWidth="1"/>
+    <col min="17" max="17" width="24.7265625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="4.453125" customWidth="1"/>
+    <col min="19" max="19" width="23.54296875" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="30.453125" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="46.1796875" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="18.81640625" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B1" s="1"/>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
@@ -6648,9 +7561,10 @@
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
       <c r="K1" s="2"/>
-      <c r="L1" s="4"/>
-    </row>
-    <row r="2" spans="2:13" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L1" s="2"/>
+      <c r="M1" s="4"/>
+    </row>
+    <row r="2" spans="2:14" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B2" s="24" t="s">
         <v>0</v>
       </c>
@@ -6679,14 +7593,17 @@
         <v>9</v>
       </c>
       <c r="K2" s="25" t="s">
+        <v>503</v>
+      </c>
+      <c r="L2" s="25" t="s">
         <v>2</v>
       </c>
-      <c r="L2" s="28" t="s">
+      <c r="M2" s="28" t="s">
         <v>3</v>
       </c>
-      <c r="M2" s="44"/>
-    </row>
-    <row r="3" spans="2:13" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="N2" s="44"/>
+    </row>
+    <row r="3" spans="2:14" ht="15" thickTop="1" x14ac:dyDescent="0.35">
       <c r="B3" s="46">
         <v>1</v>
       </c>
@@ -6715,12 +7632,15 @@
         <v>81</v>
       </c>
       <c r="K3" s="33" t="s">
+        <v>604</v>
+      </c>
+      <c r="L3" s="33" t="s">
         <v>357</v>
       </c>
-      <c r="L3" s="42"/>
-      <c r="M3" s="45"/>
-    </row>
-    <row r="4" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="M3" s="42"/>
+      <c r="N3" s="45"/>
+    </row>
+    <row r="4" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B4" s="46"/>
       <c r="C4" s="5">
         <v>2</v>
@@ -6746,13 +7666,16 @@
       <c r="J4" s="8" t="s">
         <v>67</v>
       </c>
-      <c r="K4" s="6" t="s">
+      <c r="K4" s="50" t="s">
+        <v>605</v>
+      </c>
+      <c r="L4" s="6" t="s">
         <v>359</v>
       </c>
-      <c r="L4" s="9"/>
-      <c r="M4" s="45"/>
-    </row>
-    <row r="5" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="M4" s="9"/>
+      <c r="N4" s="45"/>
+    </row>
+    <row r="5" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B5" s="46"/>
       <c r="C5" s="5">
         <v>3</v>
@@ -6778,13 +7701,16 @@
       <c r="J5" s="8" t="s">
         <v>198</v>
       </c>
-      <c r="K5" s="6" t="s">
+      <c r="K5" s="50" t="s">
+        <v>606</v>
+      </c>
+      <c r="L5" s="6" t="s">
         <v>360</v>
       </c>
-      <c r="L5" s="9"/>
-      <c r="M5" s="45"/>
-    </row>
-    <row r="6" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="M5" s="9"/>
+      <c r="N5" s="45"/>
+    </row>
+    <row r="6" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B6" s="46"/>
       <c r="C6" s="5">
         <v>4</v>
@@ -6810,13 +7736,16 @@
       <c r="J6" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="K6" s="6" t="s">
+      <c r="K6" s="50" t="s">
+        <v>607</v>
+      </c>
+      <c r="L6" s="6" t="s">
         <v>361</v>
       </c>
-      <c r="L6" s="9"/>
-      <c r="M6" s="45"/>
-    </row>
-    <row r="7" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="M6" s="9"/>
+      <c r="N6" s="45"/>
+    </row>
+    <row r="7" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B7" s="46"/>
       <c r="C7" s="23">
         <v>5</v>
@@ -6843,12 +7772,15 @@
         <v>36</v>
       </c>
       <c r="K7" s="8" t="s">
+        <v>608</v>
+      </c>
+      <c r="L7" s="8" t="s">
         <v>363</v>
       </c>
-      <c r="L7" s="9"/>
-      <c r="M7" s="45"/>
-    </row>
-    <row r="8" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="M7" s="9"/>
+      <c r="N7" s="45"/>
+    </row>
+    <row r="8" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B8" s="46"/>
       <c r="C8" s="5">
         <v>6</v>
@@ -6874,13 +7806,16 @@
       <c r="J8" s="8" t="s">
         <v>364</v>
       </c>
-      <c r="K8" s="6" t="s">
+      <c r="K8" s="50" t="s">
+        <v>609</v>
+      </c>
+      <c r="L8" s="6" t="s">
         <v>365</v>
       </c>
-      <c r="L8" s="9"/>
-      <c r="M8" s="45"/>
-    </row>
-    <row r="9" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="M8" s="9"/>
+      <c r="N8" s="45"/>
+    </row>
+    <row r="9" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B9" s="46"/>
       <c r="C9" s="5">
         <v>7</v>
@@ -6906,13 +7841,16 @@
       <c r="J9" s="8" t="s">
         <v>367</v>
       </c>
-      <c r="K9" s="6" t="s">
+      <c r="K9" s="50" t="s">
+        <v>610</v>
+      </c>
+      <c r="L9" s="6" t="s">
         <v>368</v>
       </c>
-      <c r="L9" s="9"/>
-      <c r="M9" s="45"/>
-    </row>
-    <row r="10" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="M9" s="9"/>
+      <c r="N9" s="45"/>
+    </row>
+    <row r="10" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B10" s="46"/>
       <c r="C10" s="5">
         <v>8</v>
@@ -6938,13 +7876,16 @@
       <c r="J10" s="8" t="s">
         <v>370</v>
       </c>
-      <c r="K10" s="6" t="s">
+      <c r="K10" s="50" t="s">
+        <v>611</v>
+      </c>
+      <c r="L10" s="6" t="s">
         <v>371</v>
       </c>
-      <c r="L10" s="9"/>
-      <c r="M10" s="45"/>
-    </row>
-    <row r="11" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="M10" s="9"/>
+      <c r="N10" s="45"/>
+    </row>
+    <row r="11" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B11" s="46"/>
       <c r="C11" s="5">
         <v>9</v>
@@ -6970,13 +7911,16 @@
       <c r="J11" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="K11" s="6" t="s">
+      <c r="K11" s="50" t="s">
+        <v>612</v>
+      </c>
+      <c r="L11" s="6" t="s">
         <v>372</v>
       </c>
-      <c r="L11" s="9"/>
-      <c r="M11" s="45"/>
-    </row>
-    <row r="12" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="M11" s="9"/>
+      <c r="N11" s="45"/>
+    </row>
+    <row r="12" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B12" s="47"/>
       <c r="C12" s="10">
         <v>10</v>
@@ -7003,12 +7947,15 @@
         <v>28</v>
       </c>
       <c r="K12" s="11" t="s">
+        <v>613</v>
+      </c>
+      <c r="L12" s="11" t="s">
         <v>374</v>
       </c>
-      <c r="L12" s="9"/>
-      <c r="M12" s="45"/>
-    </row>
-    <row r="13" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="M12" s="9"/>
+      <c r="N12" s="45"/>
+    </row>
+    <row r="13" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B13" s="48">
         <v>2</v>
       </c>
@@ -7037,12 +7984,15 @@
         <v>81</v>
       </c>
       <c r="K13" s="14" t="s">
+        <v>614</v>
+      </c>
+      <c r="L13" s="14" t="s">
         <v>375</v>
       </c>
-      <c r="L13" s="9"/>
-      <c r="M13" s="45"/>
-    </row>
-    <row r="14" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="M13" s="9"/>
+      <c r="N13" s="45"/>
+    </row>
+    <row r="14" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B14" s="46"/>
       <c r="C14" s="5">
         <v>2</v>
@@ -7068,13 +8018,16 @@
       <c r="J14" s="8" t="s">
         <v>67</v>
       </c>
-      <c r="K14" s="6" t="s">
+      <c r="K14" s="50" t="s">
+        <v>615</v>
+      </c>
+      <c r="L14" s="6" t="s">
         <v>376</v>
       </c>
-      <c r="L14" s="9"/>
-      <c r="M14" s="45"/>
-    </row>
-    <row r="15" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="M14" s="9"/>
+      <c r="N14" s="45"/>
+    </row>
+    <row r="15" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B15" s="46"/>
       <c r="C15" s="5">
         <v>3</v>
@@ -7100,13 +8053,16 @@
       <c r="J15" s="8" t="s">
         <v>198</v>
       </c>
-      <c r="K15" s="6" t="s">
+      <c r="K15" s="50" t="s">
+        <v>616</v>
+      </c>
+      <c r="L15" s="6" t="s">
         <v>377</v>
       </c>
-      <c r="L15" s="9"/>
-      <c r="M15" s="45"/>
-    </row>
-    <row r="16" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="M15" s="9"/>
+      <c r="N15" s="45"/>
+    </row>
+    <row r="16" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B16" s="46"/>
       <c r="C16" s="5">
         <v>4</v>
@@ -7132,13 +8088,16 @@
       <c r="J16" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="K16" s="6" t="s">
+      <c r="K16" s="50" t="s">
+        <v>617</v>
+      </c>
+      <c r="L16" s="6" t="s">
         <v>378</v>
       </c>
-      <c r="L16" s="9"/>
-      <c r="M16" s="45"/>
-    </row>
-    <row r="17" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="M16" s="9"/>
+      <c r="N16" s="45"/>
+    </row>
+    <row r="17" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B17" s="46"/>
       <c r="C17" s="23">
         <v>5</v>
@@ -7165,12 +8124,15 @@
         <v>36</v>
       </c>
       <c r="K17" s="8" t="s">
+        <v>618</v>
+      </c>
+      <c r="L17" s="8" t="s">
         <v>379</v>
       </c>
-      <c r="L17" s="9"/>
-      <c r="M17" s="45"/>
-    </row>
-    <row r="18" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="M17" s="9"/>
+      <c r="N17" s="45"/>
+    </row>
+    <row r="18" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B18" s="46"/>
       <c r="C18" s="5">
         <v>6</v>
@@ -7196,13 +8158,16 @@
       <c r="J18" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="K18" s="6" t="s">
+      <c r="K18" s="50" t="s">
+        <v>619</v>
+      </c>
+      <c r="L18" s="6" t="s">
         <v>382</v>
       </c>
-      <c r="L18" s="9"/>
-      <c r="M18" s="45"/>
-    </row>
-    <row r="19" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="M18" s="9"/>
+      <c r="N18" s="45"/>
+    </row>
+    <row r="19" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B19" s="46"/>
       <c r="C19" s="5">
         <v>7</v>
@@ -7228,13 +8193,16 @@
       <c r="J19" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="K19" s="6" t="s">
+      <c r="K19" s="50" t="s">
+        <v>620</v>
+      </c>
+      <c r="L19" s="6" t="s">
         <v>384</v>
       </c>
-      <c r="L19" s="9"/>
-      <c r="M19" s="45"/>
-    </row>
-    <row r="20" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="M19" s="9"/>
+      <c r="N19" s="45"/>
+    </row>
+    <row r="20" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B20" s="46"/>
       <c r="C20" s="5">
         <v>8</v>
@@ -7260,13 +8228,16 @@
       <c r="J20" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="K20" s="6" t="s">
+      <c r="K20" s="50" t="s">
+        <v>621</v>
+      </c>
+      <c r="L20" s="6" t="s">
         <v>385</v>
       </c>
-      <c r="L20" s="9"/>
-      <c r="M20" s="45"/>
-    </row>
-    <row r="21" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="M20" s="9"/>
+      <c r="N20" s="45"/>
+    </row>
+    <row r="21" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B21" s="46"/>
       <c r="C21" s="5">
         <v>9</v>
@@ -7292,13 +8263,16 @@
       <c r="J21" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="K21" s="6" t="s">
+      <c r="K21" s="50" t="s">
+        <v>622</v>
+      </c>
+      <c r="L21" s="6" t="s">
         <v>387</v>
       </c>
-      <c r="L21" s="9"/>
-      <c r="M21" s="45"/>
-    </row>
-    <row r="22" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="M21" s="9"/>
+      <c r="N21" s="45"/>
+    </row>
+    <row r="22" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B22" s="47"/>
       <c r="C22" s="10">
         <v>10</v>
@@ -7325,12 +8299,15 @@
         <v>42</v>
       </c>
       <c r="K22" s="11" t="s">
+        <v>623</v>
+      </c>
+      <c r="L22" s="11" t="s">
         <v>388</v>
       </c>
-      <c r="L22" s="9"/>
-      <c r="M22" s="45"/>
-    </row>
-    <row r="23" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="M22" s="9"/>
+      <c r="N22" s="45"/>
+    </row>
+    <row r="23" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B23" s="48">
         <v>3</v>
       </c>
@@ -7359,12 +8336,15 @@
         <v>389</v>
       </c>
       <c r="K23" s="14" t="s">
+        <v>624</v>
+      </c>
+      <c r="L23" s="14" t="s">
         <v>390</v>
       </c>
-      <c r="L23" s="9"/>
-      <c r="M23" s="45"/>
-    </row>
-    <row r="24" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="M23" s="9"/>
+      <c r="N23" s="45"/>
+    </row>
+    <row r="24" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B24" s="46"/>
       <c r="C24" s="5">
         <v>2</v>
@@ -7390,13 +8370,16 @@
       <c r="J24" s="8" t="s">
         <v>67</v>
       </c>
-      <c r="K24" s="6" t="s">
+      <c r="K24" s="50" t="s">
+        <v>625</v>
+      </c>
+      <c r="L24" s="6" t="s">
         <v>391</v>
       </c>
-      <c r="L24" s="9"/>
-      <c r="M24" s="45"/>
-    </row>
-    <row r="25" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="M24" s="9"/>
+      <c r="N24" s="45"/>
+    </row>
+    <row r="25" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B25" s="46"/>
       <c r="C25" s="5">
         <v>3</v>
@@ -7422,13 +8405,16 @@
       <c r="J25" s="8" t="s">
         <v>392</v>
       </c>
-      <c r="K25" s="6" t="s">
+      <c r="K25" s="50" t="s">
+        <v>626</v>
+      </c>
+      <c r="L25" s="6" t="s">
         <v>393</v>
       </c>
-      <c r="L25" s="9"/>
-      <c r="M25" s="45"/>
-    </row>
-    <row r="26" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="M25" s="9"/>
+      <c r="N25" s="45"/>
+    </row>
+    <row r="26" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B26" s="46"/>
       <c r="C26" s="5">
         <v>4</v>
@@ -7454,13 +8440,16 @@
       <c r="J26" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="K26" s="6" t="s">
+      <c r="K26" s="50" t="s">
+        <v>627</v>
+      </c>
+      <c r="L26" s="6" t="s">
         <v>395</v>
       </c>
-      <c r="L26" s="9"/>
-      <c r="M26" s="45"/>
-    </row>
-    <row r="27" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="M26" s="9"/>
+      <c r="N26" s="45"/>
+    </row>
+    <row r="27" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B27" s="46"/>
       <c r="C27" s="23">
         <v>5</v>
@@ -7487,12 +8476,15 @@
         <v>53</v>
       </c>
       <c r="K27" s="8" t="s">
+        <v>628</v>
+      </c>
+      <c r="L27" s="8" t="s">
         <v>396</v>
       </c>
-      <c r="L27" s="9"/>
-      <c r="M27" s="45"/>
-    </row>
-    <row r="28" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="M27" s="9"/>
+      <c r="N27" s="45"/>
+    </row>
+    <row r="28" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B28" s="46"/>
       <c r="C28" s="5">
         <v>6</v>
@@ -7518,13 +8510,16 @@
       <c r="J28" s="8" t="s">
         <v>198</v>
       </c>
-      <c r="K28" s="6" t="s">
+      <c r="K28" s="50" t="s">
+        <v>629</v>
+      </c>
+      <c r="L28" s="6" t="s">
         <v>398</v>
       </c>
-      <c r="L28" s="9"/>
-      <c r="M28" s="45"/>
-    </row>
-    <row r="29" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="M28" s="9"/>
+      <c r="N28" s="45"/>
+    </row>
+    <row r="29" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B29" s="46"/>
       <c r="C29" s="5">
         <v>7</v>
@@ -7550,13 +8545,16 @@
       <c r="J29" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="K29" s="6" t="s">
+      <c r="K29" s="50" t="s">
+        <v>630</v>
+      </c>
+      <c r="L29" s="6" t="s">
         <v>399</v>
       </c>
-      <c r="L29" s="9"/>
-      <c r="M29" s="45"/>
-    </row>
-    <row r="30" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="M29" s="9"/>
+      <c r="N29" s="45"/>
+    </row>
+    <row r="30" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B30" s="46"/>
       <c r="C30" s="5">
         <v>8</v>
@@ -7582,13 +8580,16 @@
       <c r="J30" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="K30" s="6" t="s">
+      <c r="K30" s="50" t="s">
+        <v>631</v>
+      </c>
+      <c r="L30" s="6" t="s">
         <v>400</v>
       </c>
-      <c r="L30" s="9"/>
-      <c r="M30" s="45"/>
-    </row>
-    <row r="31" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="M30" s="9"/>
+      <c r="N30" s="45"/>
+    </row>
+    <row r="31" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B31" s="46"/>
       <c r="C31" s="5">
         <v>9</v>
@@ -7614,13 +8615,16 @@
       <c r="J31" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="K31" s="6" t="s">
+      <c r="K31" s="50" t="s">
+        <v>632</v>
+      </c>
+      <c r="L31" s="6" t="s">
         <v>402</v>
       </c>
-      <c r="L31" s="9"/>
-      <c r="M31" s="45"/>
-    </row>
-    <row r="32" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="M31" s="9"/>
+      <c r="N31" s="45"/>
+    </row>
+    <row r="32" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B32" s="47"/>
       <c r="C32" s="10">
         <v>10</v>
@@ -7647,12 +8651,15 @@
         <v>56</v>
       </c>
       <c r="K32" s="11" t="s">
+        <v>633</v>
+      </c>
+      <c r="L32" s="11" t="s">
         <v>403</v>
       </c>
-      <c r="L32" s="9"/>
-      <c r="M32" s="45"/>
-    </row>
-    <row r="33" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="M32" s="9"/>
+      <c r="N32" s="45"/>
+    </row>
+    <row r="33" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B33" s="48">
         <v>4</v>
       </c>
@@ -7681,12 +8688,15 @@
         <v>81</v>
       </c>
       <c r="K33" s="14" t="s">
+        <v>634</v>
+      </c>
+      <c r="L33" s="14" t="s">
         <v>404</v>
       </c>
-      <c r="L33" s="9"/>
-      <c r="M33" s="45"/>
-    </row>
-    <row r="34" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="M33" s="9"/>
+      <c r="N33" s="45"/>
+    </row>
+    <row r="34" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B34" s="46"/>
       <c r="C34" s="5">
         <v>2</v>
@@ -7712,13 +8722,16 @@
       <c r="J34" s="8" t="s">
         <v>67</v>
       </c>
-      <c r="K34" s="6" t="s">
+      <c r="K34" s="50" t="s">
+        <v>635</v>
+      </c>
+      <c r="L34" s="6" t="s">
         <v>405</v>
       </c>
-      <c r="L34" s="9"/>
-      <c r="M34" s="45"/>
-    </row>
-    <row r="35" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="M34" s="9"/>
+      <c r="N34" s="45"/>
+    </row>
+    <row r="35" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B35" s="46"/>
       <c r="C35" s="5">
         <v>3</v>
@@ -7744,13 +8757,16 @@
       <c r="J35" s="8" t="s">
         <v>198</v>
       </c>
-      <c r="K35" s="6" t="s">
+      <c r="K35" s="50" t="s">
+        <v>636</v>
+      </c>
+      <c r="L35" s="6" t="s">
         <v>377</v>
       </c>
-      <c r="L35" s="9"/>
-      <c r="M35" s="45"/>
-    </row>
-    <row r="36" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="M35" s="9"/>
+      <c r="N35" s="45"/>
+    </row>
+    <row r="36" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B36" s="46"/>
       <c r="C36" s="5">
         <v>4</v>
@@ -7776,13 +8792,16 @@
       <c r="J36" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="K36" s="6" t="s">
+      <c r="K36" s="50" t="s">
+        <v>637</v>
+      </c>
+      <c r="L36" s="6" t="s">
         <v>406</v>
       </c>
-      <c r="L36" s="9"/>
-      <c r="M36" s="45"/>
-    </row>
-    <row r="37" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="M36" s="9"/>
+      <c r="N36" s="45"/>
+    </row>
+    <row r="37" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B37" s="46"/>
       <c r="C37" s="23">
         <v>5</v>
@@ -7809,12 +8828,15 @@
         <v>36</v>
       </c>
       <c r="K37" s="8" t="s">
+        <v>638</v>
+      </c>
+      <c r="L37" s="8" t="s">
         <v>408</v>
       </c>
-      <c r="L37" s="9"/>
-      <c r="M37" s="45"/>
-    </row>
-    <row r="38" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="M37" s="9"/>
+      <c r="N37" s="45"/>
+    </row>
+    <row r="38" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B38" s="46"/>
       <c r="C38" s="5">
         <v>6</v>
@@ -7840,13 +8862,16 @@
       <c r="J38" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="K38" s="6" t="s">
+      <c r="K38" s="50" t="s">
+        <v>639</v>
+      </c>
+      <c r="L38" s="6" t="s">
         <v>409</v>
       </c>
-      <c r="L38" s="9"/>
-      <c r="M38" s="45"/>
-    </row>
-    <row r="39" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="M38" s="9"/>
+      <c r="N38" s="45"/>
+    </row>
+    <row r="39" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B39" s="46"/>
       <c r="C39" s="5">
         <v>7</v>
@@ -7872,13 +8897,16 @@
       <c r="J39" s="8" t="s">
         <v>410</v>
       </c>
-      <c r="K39" s="6" t="s">
+      <c r="K39" s="50" t="s">
+        <v>640</v>
+      </c>
+      <c r="L39" s="6" t="s">
         <v>411</v>
       </c>
-      <c r="L39" s="9"/>
-      <c r="M39" s="45"/>
-    </row>
-    <row r="40" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="M39" s="9"/>
+      <c r="N39" s="45"/>
+    </row>
+    <row r="40" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B40" s="46"/>
       <c r="C40" s="5">
         <v>8</v>
@@ -7904,13 +8932,16 @@
       <c r="J40" s="8" t="s">
         <v>142</v>
       </c>
-      <c r="K40" s="6" t="s">
+      <c r="K40" s="50" t="s">
+        <v>641</v>
+      </c>
+      <c r="L40" s="6" t="s">
         <v>412</v>
       </c>
-      <c r="L40" s="9"/>
-      <c r="M40" s="45"/>
-    </row>
-    <row r="41" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="M40" s="9"/>
+      <c r="N40" s="45"/>
+    </row>
+    <row r="41" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B41" s="46"/>
       <c r="C41" s="5">
         <v>9</v>
@@ -7936,13 +8967,16 @@
       <c r="J41" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="K41" s="6" t="s">
+      <c r="K41" s="50" t="s">
+        <v>642</v>
+      </c>
+      <c r="L41" s="6" t="s">
         <v>414</v>
       </c>
-      <c r="L41" s="9"/>
-      <c r="M41" s="45"/>
-    </row>
-    <row r="42" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="M41" s="9"/>
+      <c r="N41" s="45"/>
+    </row>
+    <row r="42" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B42" s="47"/>
       <c r="C42" s="10">
         <v>10</v>
@@ -7969,12 +9003,15 @@
         <v>159</v>
       </c>
       <c r="K42" s="11" t="s">
+        <v>643</v>
+      </c>
+      <c r="L42" s="11" t="s">
         <v>417</v>
       </c>
-      <c r="L42" s="9"/>
-      <c r="M42" s="45"/>
-    </row>
-    <row r="43" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="M42" s="9"/>
+      <c r="N42" s="45"/>
+    </row>
+    <row r="43" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B43" s="48">
         <v>5</v>
       </c>
@@ -8003,12 +9040,15 @@
         <v>81</v>
       </c>
       <c r="K43" s="14" t="s">
+        <v>644</v>
+      </c>
+      <c r="L43" s="14" t="s">
         <v>418</v>
       </c>
-      <c r="L43" s="9"/>
-      <c r="M43" s="45"/>
-    </row>
-    <row r="44" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="M43" s="9"/>
+      <c r="N43" s="45"/>
+    </row>
+    <row r="44" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B44" s="46"/>
       <c r="C44" s="5">
         <v>2</v>
@@ -8034,13 +9074,16 @@
       <c r="J44" s="8" t="s">
         <v>419</v>
       </c>
-      <c r="K44" s="6" t="s">
+      <c r="K44" s="50" t="s">
+        <v>645</v>
+      </c>
+      <c r="L44" s="6" t="s">
         <v>420</v>
       </c>
-      <c r="L44" s="9"/>
-      <c r="M44" s="45"/>
-    </row>
-    <row r="45" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="M44" s="9"/>
+      <c r="N44" s="45"/>
+    </row>
+    <row r="45" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B45" s="46"/>
       <c r="C45" s="5">
         <v>3</v>
@@ -8066,13 +9109,16 @@
       <c r="J45" s="8" t="s">
         <v>198</v>
       </c>
-      <c r="K45" s="6" t="s">
+      <c r="K45" s="50" t="s">
+        <v>646</v>
+      </c>
+      <c r="L45" s="6" t="s">
         <v>421</v>
       </c>
-      <c r="L45" s="9"/>
-      <c r="M45" s="45"/>
-    </row>
-    <row r="46" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="M45" s="9"/>
+      <c r="N45" s="45"/>
+    </row>
+    <row r="46" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B46" s="46"/>
       <c r="C46" s="5">
         <v>4</v>
@@ -8098,13 +9144,16 @@
       <c r="J46" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="K46" s="6" t="s">
+      <c r="K46" s="50" t="s">
+        <v>647</v>
+      </c>
+      <c r="L46" s="6" t="s">
         <v>422</v>
       </c>
-      <c r="L46" s="9"/>
-      <c r="M46" s="45"/>
-    </row>
-    <row r="47" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="M46" s="9"/>
+      <c r="N46" s="45"/>
+    </row>
+    <row r="47" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B47" s="46"/>
       <c r="C47" s="23">
         <v>5</v>
@@ -8131,12 +9180,15 @@
         <v>36</v>
       </c>
       <c r="K47" s="8" t="s">
+        <v>648</v>
+      </c>
+      <c r="L47" s="8" t="s">
         <v>423</v>
       </c>
-      <c r="L47" s="9"/>
-      <c r="M47" s="45"/>
-    </row>
-    <row r="48" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="M47" s="9"/>
+      <c r="N47" s="45"/>
+    </row>
+    <row r="48" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B48" s="46"/>
       <c r="C48" s="5">
         <v>6</v>
@@ -8162,13 +9214,16 @@
       <c r="J48" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="K48" s="6" t="s">
+      <c r="K48" s="50" t="s">
+        <v>649</v>
+      </c>
+      <c r="L48" s="6" t="s">
         <v>424</v>
       </c>
-      <c r="L48" s="9"/>
-      <c r="M48" s="45"/>
-    </row>
-    <row r="49" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="M48" s="9"/>
+      <c r="N48" s="45"/>
+    </row>
+    <row r="49" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B49" s="46"/>
       <c r="C49" s="5">
         <v>7</v>
@@ -8194,13 +9249,16 @@
       <c r="J49" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="K49" s="6" t="s">
+      <c r="K49" s="50" t="s">
+        <v>650</v>
+      </c>
+      <c r="L49" s="6" t="s">
         <v>425</v>
       </c>
-      <c r="L49" s="9"/>
-      <c r="M49" s="45"/>
-    </row>
-    <row r="50" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="M49" s="9"/>
+      <c r="N49" s="45"/>
+    </row>
+    <row r="50" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B50" s="46"/>
       <c r="C50" s="5">
         <v>8</v>
@@ -8226,13 +9284,16 @@
       <c r="J50" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="K50" s="6" t="s">
+      <c r="K50" s="50" t="s">
+        <v>651</v>
+      </c>
+      <c r="L50" s="6" t="s">
         <v>426</v>
       </c>
-      <c r="L50" s="9"/>
-      <c r="M50" s="45"/>
-    </row>
-    <row r="51" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="M50" s="9"/>
+      <c r="N50" s="45"/>
+    </row>
+    <row r="51" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B51" s="46"/>
       <c r="C51" s="5">
         <v>9</v>
@@ -8258,13 +9319,16 @@
       <c r="J51" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="K51" s="6" t="s">
+      <c r="K51" s="50" t="s">
+        <v>652</v>
+      </c>
+      <c r="L51" s="6" t="s">
         <v>427</v>
       </c>
-      <c r="L51" s="9"/>
-      <c r="M51" s="45"/>
-    </row>
-    <row r="52" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="M51" s="9"/>
+      <c r="N51" s="45"/>
+    </row>
+    <row r="52" spans="2:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B52" s="49"/>
       <c r="C52" s="5">
         <v>10</v>
@@ -8291,469 +9355,472 @@
         <v>45</v>
       </c>
       <c r="K52" s="16" t="s">
+        <v>653</v>
+      </c>
+      <c r="L52" s="16" t="s">
         <v>429</v>
       </c>
-      <c r="L52" s="43"/>
-      <c r="M52" s="45"/>
-    </row>
-    <row r="53" spans="2:13" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="M52" s="43"/>
+      <c r="N52" s="45"/>
+    </row>
+    <row r="53" spans="2:14" ht="15" thickTop="1" x14ac:dyDescent="0.35">
       <c r="C53" s="21"/>
-      <c r="L53" s="18"/>
-    </row>
-    <row r="54" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="M53" s="18"/>
+    </row>
+    <row r="54" spans="2:14" x14ac:dyDescent="0.35">
       <c r="C54"/>
       <c r="D54"/>
       <c r="E54"/>
       <c r="F54"/>
     </row>
-    <row r="55" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="55" spans="2:14" x14ac:dyDescent="0.35">
       <c r="C55"/>
       <c r="D55"/>
       <c r="E55"/>
       <c r="F55"/>
     </row>
-    <row r="56" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="56" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B56" s="20"/>
       <c r="C56" s="20"/>
       <c r="D56" s="20"/>
       <c r="E56" s="20"/>
       <c r="F56" s="20"/>
     </row>
-    <row r="57" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="57" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B57" s="20"/>
       <c r="C57" s="20"/>
       <c r="D57" s="20"/>
       <c r="E57" s="20"/>
       <c r="F57" s="20"/>
     </row>
-    <row r="58" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="58" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B58" s="20"/>
       <c r="C58" s="20"/>
       <c r="D58" s="20"/>
       <c r="E58" s="20"/>
       <c r="F58" s="20"/>
     </row>
-    <row r="59" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="59" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B59" s="20"/>
       <c r="C59" s="20"/>
       <c r="D59" s="20"/>
       <c r="E59" s="20"/>
       <c r="F59" s="20"/>
     </row>
-    <row r="60" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="60" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B60" s="20"/>
       <c r="C60" s="20"/>
       <c r="D60" s="20"/>
       <c r="E60" s="20"/>
       <c r="F60" s="20"/>
     </row>
-    <row r="61" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="61" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B61" s="20"/>
       <c r="C61" s="20"/>
       <c r="D61" s="20"/>
       <c r="E61" s="20"/>
       <c r="F61" s="20"/>
     </row>
-    <row r="62" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="62" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B62" s="20"/>
       <c r="C62" s="20"/>
       <c r="D62" s="20"/>
       <c r="E62" s="20"/>
       <c r="F62" s="20"/>
     </row>
-    <row r="63" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="63" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B63" s="20"/>
       <c r="C63" s="20"/>
       <c r="D63" s="20"/>
       <c r="E63" s="20"/>
       <c r="F63" s="20"/>
     </row>
-    <row r="64" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B64" s="20"/>
       <c r="C64" s="20"/>
       <c r="D64" s="20"/>
       <c r="E64" s="20"/>
       <c r="F64" s="20"/>
-      <c r="L64" s="19"/>
       <c r="M64" s="19"/>
-    </row>
-    <row r="65" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N64" s="19"/>
+    </row>
+    <row r="65" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B65" s="20"/>
       <c r="C65" s="20"/>
       <c r="D65" s="20"/>
       <c r="E65" s="20"/>
       <c r="F65" s="20"/>
-      <c r="L65" s="19"/>
       <c r="M65" s="19"/>
-    </row>
-    <row r="66" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N65" s="19"/>
+    </row>
+    <row r="66" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B66" s="20"/>
       <c r="C66" s="20"/>
       <c r="D66" s="20"/>
       <c r="E66" s="20"/>
       <c r="F66" s="20"/>
-      <c r="L66" s="19"/>
       <c r="M66" s="19"/>
-    </row>
-    <row r="67" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N66" s="19"/>
+    </row>
+    <row r="67" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B67" s="20"/>
       <c r="C67" s="20"/>
       <c r="D67" s="20"/>
       <c r="E67" s="20"/>
       <c r="F67" s="20"/>
-      <c r="L67" s="19"/>
       <c r="M67" s="19"/>
-    </row>
-    <row r="68" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N67" s="19"/>
+    </row>
+    <row r="68" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B68" s="20"/>
       <c r="C68" s="20"/>
       <c r="D68" s="20"/>
       <c r="E68" s="20"/>
       <c r="F68" s="20"/>
-      <c r="L68" s="19"/>
       <c r="M68" s="19"/>
-    </row>
-    <row r="69" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N68" s="19"/>
+    </row>
+    <row r="69" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B69" s="20"/>
       <c r="C69" s="20"/>
       <c r="D69" s="20"/>
       <c r="E69" s="20"/>
       <c r="F69" s="20"/>
-      <c r="L69" s="19"/>
       <c r="M69" s="19"/>
-    </row>
-    <row r="70" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N69" s="19"/>
+    </row>
+    <row r="70" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B70" s="20"/>
       <c r="C70" s="20"/>
       <c r="D70" s="20"/>
       <c r="E70" s="20"/>
       <c r="F70" s="20"/>
-      <c r="L70" s="19"/>
       <c r="M70" s="19"/>
-    </row>
-    <row r="71" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N70" s="19"/>
+    </row>
+    <row r="71" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B71" s="20"/>
       <c r="C71" s="20"/>
       <c r="D71" s="20"/>
       <c r="E71" s="20"/>
       <c r="F71" s="20"/>
-      <c r="L71" s="19"/>
       <c r="M71" s="19"/>
-    </row>
-    <row r="72" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N71" s="19"/>
+    </row>
+    <row r="72" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B72" s="20"/>
       <c r="C72" s="20"/>
       <c r="D72" s="20"/>
       <c r="E72" s="20"/>
       <c r="F72" s="20"/>
-      <c r="L72" s="19"/>
       <c r="M72" s="19"/>
-    </row>
-    <row r="73" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N72" s="19"/>
+    </row>
+    <row r="73" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B73" s="20"/>
       <c r="C73" s="20"/>
       <c r="D73" s="20"/>
       <c r="E73" s="20"/>
       <c r="F73" s="20"/>
-      <c r="L73" s="19"/>
       <c r="M73" s="19"/>
-    </row>
-    <row r="74" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N73" s="19"/>
+    </row>
+    <row r="74" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B74" s="20"/>
       <c r="C74" s="20"/>
       <c r="D74" s="20"/>
       <c r="E74" s="20"/>
       <c r="F74" s="20"/>
-      <c r="L74" s="19"/>
       <c r="M74" s="19"/>
-    </row>
-    <row r="75" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N74" s="19"/>
+    </row>
+    <row r="75" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B75" s="20"/>
       <c r="C75" s="20"/>
       <c r="D75" s="20"/>
       <c r="E75" s="20"/>
       <c r="F75" s="20"/>
-      <c r="L75" s="19"/>
       <c r="M75" s="19"/>
-    </row>
-    <row r="76" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N75" s="19"/>
+    </row>
+    <row r="76" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B76" s="20"/>
       <c r="C76" s="20"/>
       <c r="D76" s="20"/>
       <c r="E76" s="20"/>
       <c r="F76" s="20"/>
-      <c r="L76" s="19"/>
       <c r="M76" s="19"/>
-    </row>
-    <row r="77" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N76" s="19"/>
+    </row>
+    <row r="77" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B77" s="20"/>
       <c r="C77" s="20"/>
       <c r="D77" s="20"/>
       <c r="E77" s="20"/>
       <c r="F77" s="20"/>
-      <c r="L77" s="19"/>
       <c r="M77" s="19"/>
-    </row>
-    <row r="78" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N77" s="19"/>
+    </row>
+    <row r="78" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B78" s="20"/>
       <c r="C78" s="20"/>
       <c r="D78" s="20"/>
       <c r="E78" s="20"/>
       <c r="F78" s="20"/>
-      <c r="L78" s="19"/>
       <c r="M78" s="19"/>
-    </row>
-    <row r="79" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N78" s="19"/>
+    </row>
+    <row r="79" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B79" s="20"/>
       <c r="C79" s="20"/>
       <c r="D79" s="20"/>
       <c r="E79" s="20"/>
       <c r="F79" s="20"/>
-      <c r="L79" s="19"/>
       <c r="M79" s="19"/>
-    </row>
-    <row r="80" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N79" s="19"/>
+    </row>
+    <row r="80" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B80" s="20"/>
       <c r="C80" s="20"/>
       <c r="D80" s="20"/>
       <c r="E80" s="20"/>
       <c r="F80" s="20"/>
-      <c r="L80" s="19"/>
       <c r="M80" s="19"/>
-    </row>
-    <row r="81" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N80" s="19"/>
+    </row>
+    <row r="81" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B81" s="20"/>
       <c r="C81" s="20"/>
       <c r="D81" s="20"/>
       <c r="E81" s="20"/>
       <c r="F81" s="20"/>
-      <c r="L81" s="19"/>
       <c r="M81" s="19"/>
-    </row>
-    <row r="82" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N81" s="19"/>
+    </row>
+    <row r="82" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B82" s="20"/>
       <c r="C82" s="20"/>
       <c r="D82" s="20"/>
       <c r="E82" s="20"/>
       <c r="F82" s="20"/>
-      <c r="L82" s="19"/>
       <c r="M82" s="19"/>
-    </row>
-    <row r="83" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N82" s="19"/>
+    </row>
+    <row r="83" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B83" s="20"/>
       <c r="C83" s="20"/>
       <c r="D83" s="20"/>
       <c r="E83" s="20"/>
       <c r="F83" s="20"/>
-      <c r="L83" s="19"/>
       <c r="M83" s="19"/>
-    </row>
-    <row r="84" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N83" s="19"/>
+    </row>
+    <row r="84" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B84" s="20"/>
       <c r="C84" s="20"/>
       <c r="D84" s="20"/>
       <c r="E84" s="20"/>
       <c r="F84" s="20"/>
-      <c r="L84" s="19"/>
       <c r="M84" s="19"/>
-    </row>
-    <row r="85" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N84" s="19"/>
+    </row>
+    <row r="85" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B85" s="20"/>
       <c r="C85" s="20"/>
       <c r="D85" s="20"/>
       <c r="E85" s="20"/>
       <c r="F85" s="20"/>
-      <c r="L85" s="19"/>
       <c r="M85" s="19"/>
-    </row>
-    <row r="86" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N85" s="19"/>
+    </row>
+    <row r="86" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B86" s="20"/>
       <c r="C86" s="20"/>
       <c r="D86" s="20"/>
       <c r="E86" s="20"/>
       <c r="F86" s="20"/>
-      <c r="L86" s="19"/>
       <c r="M86" s="19"/>
-    </row>
-    <row r="87" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N86" s="19"/>
+    </row>
+    <row r="87" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B87" s="20"/>
       <c r="C87" s="20"/>
       <c r="D87" s="20"/>
       <c r="E87" s="20"/>
       <c r="F87" s="20"/>
-      <c r="L87" s="19"/>
       <c r="M87" s="19"/>
-    </row>
-    <row r="88" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N87" s="19"/>
+    </row>
+    <row r="88" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B88" s="20"/>
       <c r="C88" s="20"/>
       <c r="D88" s="20"/>
       <c r="E88" s="20"/>
       <c r="F88" s="20"/>
-      <c r="L88" s="19"/>
       <c r="M88" s="19"/>
-    </row>
-    <row r="89" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N88" s="19"/>
+    </row>
+    <row r="89" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B89" s="20"/>
       <c r="C89" s="20"/>
       <c r="D89" s="20"/>
       <c r="E89" s="20"/>
       <c r="F89" s="20"/>
-      <c r="L89" s="19"/>
       <c r="M89" s="19"/>
-    </row>
-    <row r="90" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N89" s="19"/>
+    </row>
+    <row r="90" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B90" s="20"/>
       <c r="C90" s="20"/>
       <c r="D90" s="20"/>
       <c r="E90" s="20"/>
       <c r="F90" s="20"/>
-      <c r="L90" s="19"/>
       <c r="M90" s="19"/>
-    </row>
-    <row r="91" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N90" s="19"/>
+    </row>
+    <row r="91" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B91" s="20"/>
       <c r="C91" s="20"/>
       <c r="D91" s="20"/>
       <c r="E91" s="20"/>
       <c r="F91" s="20"/>
-      <c r="L91" s="19"/>
       <c r="M91" s="19"/>
-    </row>
-    <row r="92" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N91" s="19"/>
+    </row>
+    <row r="92" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B92" s="20"/>
       <c r="C92" s="20"/>
       <c r="D92" s="20"/>
       <c r="E92" s="20"/>
       <c r="F92" s="20"/>
-      <c r="L92" s="19"/>
       <c r="M92" s="19"/>
-    </row>
-    <row r="93" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N92" s="19"/>
+    </row>
+    <row r="93" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B93" s="20"/>
       <c r="C93" s="20"/>
       <c r="D93" s="20"/>
       <c r="E93" s="20"/>
       <c r="F93" s="20"/>
-      <c r="L93" s="19"/>
       <c r="M93" s="19"/>
-    </row>
-    <row r="94" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N93" s="19"/>
+    </row>
+    <row r="94" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B94" s="20"/>
       <c r="C94" s="20"/>
       <c r="D94" s="20"/>
       <c r="E94" s="20"/>
       <c r="F94" s="20"/>
-      <c r="L94" s="19"/>
       <c r="M94" s="19"/>
-    </row>
-    <row r="95" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N94" s="19"/>
+    </row>
+    <row r="95" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B95" s="20"/>
       <c r="C95" s="20"/>
       <c r="D95" s="20"/>
       <c r="E95" s="20"/>
       <c r="F95" s="20"/>
-      <c r="L95" s="19"/>
       <c r="M95" s="19"/>
-    </row>
-    <row r="96" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N95" s="19"/>
+    </row>
+    <row r="96" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B96" s="20"/>
       <c r="C96" s="20"/>
       <c r="D96" s="20"/>
       <c r="E96" s="20"/>
       <c r="F96" s="20"/>
-      <c r="L96" s="19"/>
       <c r="M96" s="19"/>
-    </row>
-    <row r="97" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N96" s="19"/>
+    </row>
+    <row r="97" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B97" s="20"/>
       <c r="C97" s="20"/>
       <c r="D97" s="20"/>
       <c r="E97" s="20"/>
       <c r="F97" s="20"/>
-      <c r="L97" s="19"/>
       <c r="M97" s="19"/>
-    </row>
-    <row r="98" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N97" s="19"/>
+    </row>
+    <row r="98" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B98" s="20"/>
       <c r="C98" s="20"/>
       <c r="D98" s="20"/>
       <c r="E98" s="20"/>
       <c r="F98" s="20"/>
-      <c r="L98" s="19"/>
       <c r="M98" s="19"/>
-    </row>
-    <row r="99" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N98" s="19"/>
+    </row>
+    <row r="99" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B99" s="20"/>
       <c r="C99" s="20"/>
       <c r="D99" s="20"/>
       <c r="E99" s="20"/>
       <c r="F99" s="20"/>
-      <c r="L99" s="19"/>
       <c r="M99" s="19"/>
-    </row>
-    <row r="100" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N99" s="19"/>
+    </row>
+    <row r="100" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B100" s="20"/>
       <c r="C100" s="20"/>
       <c r="D100" s="20"/>
       <c r="E100" s="20"/>
       <c r="F100" s="20"/>
-      <c r="L100" s="19"/>
       <c r="M100" s="19"/>
-    </row>
-    <row r="101" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N100" s="19"/>
+    </row>
+    <row r="101" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B101" s="20"/>
       <c r="C101" s="20"/>
       <c r="D101" s="20"/>
       <c r="E101" s="20"/>
       <c r="F101" s="20"/>
-      <c r="L101" s="19"/>
       <c r="M101" s="19"/>
-    </row>
-    <row r="102" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N101" s="19"/>
+    </row>
+    <row r="102" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B102" s="20"/>
       <c r="C102" s="20"/>
       <c r="D102" s="20"/>
       <c r="E102" s="20"/>
       <c r="F102" s="20"/>
-      <c r="L102" s="19"/>
       <c r="M102" s="19"/>
-    </row>
-    <row r="103" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N102" s="19"/>
+    </row>
+    <row r="103" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B103" s="20"/>
       <c r="C103" s="20"/>
       <c r="D103" s="20"/>
       <c r="E103" s="20"/>
       <c r="F103" s="20"/>
-      <c r="L103" s="19"/>
       <c r="M103" s="19"/>
-    </row>
-    <row r="104" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N103" s="19"/>
+    </row>
+    <row r="104" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B104" s="20"/>
       <c r="C104" s="20"/>
       <c r="D104" s="20"/>
       <c r="E104" s="20"/>
       <c r="F104" s="20"/>
-      <c r="L104" s="19"/>
       <c r="M104" s="19"/>
-    </row>
-    <row r="105" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N104" s="19"/>
+    </row>
+    <row r="105" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B105" s="20"/>
       <c r="C105" s="20"/>
       <c r="D105" s="20"/>
       <c r="E105" s="20"/>
       <c r="F105" s="20"/>
-      <c r="L105" s="19"/>
       <c r="M105" s="19"/>
-    </row>
-    <row r="106" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N105" s="19"/>
+    </row>
+    <row r="106" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B106" s="20"/>
       <c r="C106" s="20"/>
       <c r="D106" s="20"/>
       <c r="E106" s="20"/>
       <c r="F106" s="20"/>
-      <c r="L106" s="19"/>
       <c r="M106" s="19"/>
+      <c r="N106" s="19"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -8769,33 +9836,33 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="B1:L106"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="B1:M106"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="6" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="3.140625" style="3" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.140625" style="3" customWidth="1"/>
-    <col min="5" max="5" width="6.28515625" style="3" customWidth="1"/>
-    <col min="6" max="6" width="4.28515625" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="3.1796875" style="3" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.1796875" style="3" customWidth="1"/>
+    <col min="5" max="5" width="6.26953125" style="3" customWidth="1"/>
+    <col min="6" max="6" width="4.26953125" style="3" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="21" style="3" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="20.42578125" style="3" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="16.5703125" style="3" customWidth="1"/>
-    <col min="10" max="10" width="19.5703125" style="3" customWidth="1"/>
-    <col min="11" max="11" width="75.7109375" style="3" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="15.28515625" style="19" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="6.85546875" customWidth="1"/>
-    <col min="14" max="14" width="3.140625" customWidth="1"/>
-    <col min="15" max="15" width="24.7109375" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="4.42578125" customWidth="1"/>
-    <col min="17" max="17" width="23.5703125" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="30.42578125" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="46.140625" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="18.85546875" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="2" customWidth="1"/>
+    <col min="8" max="8" width="20.453125" style="3" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="16.54296875" style="3" customWidth="1"/>
+    <col min="10" max="11" width="19.54296875" style="3" customWidth="1"/>
+    <col min="12" max="12" width="75.7265625" style="3" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="15.26953125" style="19" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="6.81640625" customWidth="1"/>
+    <col min="15" max="15" width="3.1796875" customWidth="1"/>
+    <col min="16" max="16" width="24.7265625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="4.453125" customWidth="1"/>
+    <col min="18" max="18" width="23.54296875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="30.453125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="46.1796875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="18.81640625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B1" s="1"/>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
@@ -8806,9 +9873,10 @@
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
       <c r="K1" s="2"/>
-      <c r="L1" s="4"/>
-    </row>
-    <row r="2" spans="2:12" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L1" s="2"/>
+      <c r="M1" s="4"/>
+    </row>
+    <row r="2" spans="2:13" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B2" s="24" t="s">
         <v>0</v>
       </c>
@@ -8837,13 +9905,16 @@
         <v>9</v>
       </c>
       <c r="K2" s="25" t="s">
+        <v>503</v>
+      </c>
+      <c r="L2" s="25" t="s">
         <v>2</v>
       </c>
-      <c r="L2" s="28" t="s">
+      <c r="M2" s="28" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="2:12" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:13" ht="15" thickTop="1" x14ac:dyDescent="0.35">
       <c r="B3" s="46">
         <v>1</v>
       </c>
@@ -8871,12 +9942,15 @@
       <c r="J3" s="7" t="s">
         <v>430</v>
       </c>
-      <c r="K3" s="32" t="s">
+      <c r="K3" s="7" t="s">
+        <v>654</v>
+      </c>
+      <c r="L3" s="32" t="s">
         <v>431</v>
       </c>
-      <c r="L3" s="39"/>
-    </row>
-    <row r="4" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="M3" s="39"/>
+    </row>
+    <row r="4" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B4" s="46"/>
       <c r="C4" s="5">
         <v>2</v>
@@ -8902,12 +9976,15 @@
       <c r="J4" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="K4" s="35" t="s">
+      <c r="K4" s="8" t="s">
+        <v>655</v>
+      </c>
+      <c r="L4" s="35" t="s">
         <v>432</v>
       </c>
-      <c r="L4" s="40"/>
-    </row>
-    <row r="5" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="M4" s="40"/>
+    </row>
+    <row r="5" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B5" s="46"/>
       <c r="C5" s="5">
         <v>3</v>
@@ -8933,12 +10010,15 @@
       <c r="J5" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="K5" s="35" t="s">
+      <c r="K5" s="8" t="s">
+        <v>656</v>
+      </c>
+      <c r="L5" s="35" t="s">
         <v>433</v>
       </c>
-      <c r="L5" s="40"/>
-    </row>
-    <row r="6" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="M5" s="40"/>
+    </row>
+    <row r="6" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B6" s="46"/>
       <c r="C6" s="5">
         <v>4</v>
@@ -8964,12 +10044,15 @@
       <c r="J6" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="K6" s="35" t="s">
+      <c r="K6" s="8" t="s">
+        <v>657</v>
+      </c>
+      <c r="L6" s="35" t="s">
         <v>434</v>
       </c>
-      <c r="L6" s="40"/>
-    </row>
-    <row r="7" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="M6" s="40"/>
+    </row>
+    <row r="7" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B7" s="46"/>
       <c r="C7" s="23">
         <v>5</v>
@@ -8995,12 +10078,15 @@
       <c r="J7" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="K7" s="35" t="s">
+      <c r="K7" s="8" t="s">
+        <v>658</v>
+      </c>
+      <c r="L7" s="35" t="s">
         <v>436</v>
       </c>
-      <c r="L7" s="40"/>
-    </row>
-    <row r="8" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="M7" s="40"/>
+    </row>
+    <row r="8" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B8" s="46"/>
       <c r="C8" s="5">
         <v>6</v>
@@ -9026,12 +10112,15 @@
       <c r="J8" s="8" t="s">
         <v>437</v>
       </c>
-      <c r="K8" s="35" t="s">
+      <c r="K8" s="8" t="s">
+        <v>659</v>
+      </c>
+      <c r="L8" s="35" t="s">
         <v>438</v>
       </c>
-      <c r="L8" s="40"/>
-    </row>
-    <row r="9" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="M8" s="40"/>
+    </row>
+    <row r="9" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B9" s="46"/>
       <c r="C9" s="5">
         <v>7</v>
@@ -9057,12 +10146,15 @@
       <c r="J9" s="8" t="s">
         <v>419</v>
       </c>
-      <c r="K9" s="35" t="s">
+      <c r="K9" s="8" t="s">
+        <v>660</v>
+      </c>
+      <c r="L9" s="35" t="s">
         <v>440</v>
       </c>
-      <c r="L9" s="40"/>
-    </row>
-    <row r="10" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="M9" s="40"/>
+    </row>
+    <row r="10" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B10" s="46"/>
       <c r="C10" s="5">
         <v>8</v>
@@ -9088,12 +10180,15 @@
       <c r="J10" s="8" t="s">
         <v>67</v>
       </c>
-      <c r="K10" s="35" t="s">
+      <c r="K10" s="8" t="s">
+        <v>661</v>
+      </c>
+      <c r="L10" s="35" t="s">
         <v>441</v>
       </c>
-      <c r="L10" s="40"/>
-    </row>
-    <row r="11" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="M10" s="40"/>
+    </row>
+    <row r="11" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B11" s="46"/>
       <c r="C11" s="5">
         <v>9</v>
@@ -9119,12 +10214,15 @@
       <c r="J11" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="K11" s="35" t="s">
+      <c r="K11" s="8" t="s">
+        <v>662</v>
+      </c>
+      <c r="L11" s="35" t="s">
         <v>442</v>
       </c>
-      <c r="L11" s="40"/>
-    </row>
-    <row r="12" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="M11" s="40"/>
+    </row>
+    <row r="12" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B12" s="47"/>
       <c r="C12" s="10">
         <v>10</v>
@@ -9150,12 +10248,15 @@
       <c r="J12" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="K12" s="36" t="s">
+      <c r="K12" s="12" t="s">
+        <v>663</v>
+      </c>
+      <c r="L12" s="36" t="s">
         <v>443</v>
       </c>
-      <c r="L12" s="40"/>
-    </row>
-    <row r="13" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="M12" s="40"/>
+    </row>
+    <row r="13" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B13" s="48">
         <v>2</v>
       </c>
@@ -9183,12 +10284,15 @@
       <c r="J13" s="15" t="s">
         <v>430</v>
       </c>
-      <c r="K13" s="37" t="s">
+      <c r="K13" s="15" t="s">
+        <v>664</v>
+      </c>
+      <c r="L13" s="37" t="s">
         <v>444</v>
       </c>
-      <c r="L13" s="40"/>
-    </row>
-    <row r="14" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="M13" s="40"/>
+    </row>
+    <row r="14" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B14" s="46"/>
       <c r="C14" s="5">
         <v>2</v>
@@ -9214,12 +10318,15 @@
       <c r="J14" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="K14" s="35" t="s">
+      <c r="K14" s="8" t="s">
+        <v>665</v>
+      </c>
+      <c r="L14" s="35" t="s">
         <v>445</v>
       </c>
-      <c r="L14" s="40"/>
-    </row>
-    <row r="15" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="M14" s="40"/>
+    </row>
+    <row r="15" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B15" s="46"/>
       <c r="C15" s="5">
         <v>3</v>
@@ -9245,12 +10352,15 @@
       <c r="J15" s="8" t="s">
         <v>446</v>
       </c>
-      <c r="K15" s="35" t="s">
+      <c r="K15" s="8" t="s">
+        <v>666</v>
+      </c>
+      <c r="L15" s="35" t="s">
         <v>447</v>
       </c>
-      <c r="L15" s="40"/>
-    </row>
-    <row r="16" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="M15" s="40"/>
+    </row>
+    <row r="16" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B16" s="46"/>
       <c r="C16" s="5">
         <v>4</v>
@@ -9276,12 +10386,15 @@
       <c r="J16" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="K16" s="35" t="s">
+      <c r="K16" s="8" t="s">
+        <v>667</v>
+      </c>
+      <c r="L16" s="35" t="s">
         <v>448</v>
       </c>
-      <c r="L16" s="40"/>
-    </row>
-    <row r="17" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="M16" s="40"/>
+    </row>
+    <row r="17" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B17" s="46"/>
       <c r="C17" s="23">
         <v>5</v>
@@ -9307,12 +10420,15 @@
       <c r="J17" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="K17" s="35" t="s">
+      <c r="K17" s="8" t="s">
+        <v>668</v>
+      </c>
+      <c r="L17" s="35" t="s">
         <v>449</v>
       </c>
-      <c r="L17" s="40"/>
-    </row>
-    <row r="18" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="M17" s="40"/>
+    </row>
+    <row r="18" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B18" s="46"/>
       <c r="C18" s="5">
         <v>6</v>
@@ -9338,12 +10454,15 @@
       <c r="J18" s="8" t="s">
         <v>450</v>
       </c>
-      <c r="K18" s="35" t="s">
+      <c r="K18" s="8" t="s">
+        <v>669</v>
+      </c>
+      <c r="L18" s="35" t="s">
         <v>451</v>
       </c>
-      <c r="L18" s="40"/>
-    </row>
-    <row r="19" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="M18" s="40"/>
+    </row>
+    <row r="19" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B19" s="46"/>
       <c r="C19" s="5">
         <v>7</v>
@@ -9369,12 +10488,15 @@
       <c r="J19" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="K19" s="35" t="s">
+      <c r="K19" s="8" t="s">
+        <v>670</v>
+      </c>
+      <c r="L19" s="35" t="s">
         <v>452</v>
       </c>
-      <c r="L19" s="40"/>
-    </row>
-    <row r="20" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="M19" s="40"/>
+    </row>
+    <row r="20" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B20" s="46"/>
       <c r="C20" s="5">
         <v>8</v>
@@ -9400,12 +10522,15 @@
       <c r="J20" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="K20" s="35" t="s">
+      <c r="K20" s="8" t="s">
+        <v>671</v>
+      </c>
+      <c r="L20" s="35" t="s">
         <v>454</v>
       </c>
-      <c r="L20" s="40"/>
-    </row>
-    <row r="21" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="M20" s="40"/>
+    </row>
+    <row r="21" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B21" s="46"/>
       <c r="C21" s="5">
         <v>9</v>
@@ -9431,12 +10556,15 @@
       <c r="J21" s="8" t="s">
         <v>138</v>
       </c>
-      <c r="K21" s="35" t="s">
+      <c r="K21" s="8" t="s">
+        <v>672</v>
+      </c>
+      <c r="L21" s="35" t="s">
         <v>455</v>
       </c>
-      <c r="L21" s="40"/>
-    </row>
-    <row r="22" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="M21" s="40"/>
+    </row>
+    <row r="22" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B22" s="47"/>
       <c r="C22" s="10">
         <v>10</v>
@@ -9462,12 +10590,15 @@
       <c r="J22" s="12" t="s">
         <v>419</v>
       </c>
-      <c r="K22" s="36" t="s">
+      <c r="K22" s="12" t="s">
+        <v>673</v>
+      </c>
+      <c r="L22" s="36" t="s">
         <v>456</v>
       </c>
-      <c r="L22" s="40"/>
-    </row>
-    <row r="23" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="M22" s="40"/>
+    </row>
+    <row r="23" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B23" s="48">
         <v>3</v>
       </c>
@@ -9495,12 +10626,15 @@
       <c r="J23" s="15" t="s">
         <v>91</v>
       </c>
-      <c r="K23" s="37" t="s">
+      <c r="K23" s="15" t="s">
+        <v>674</v>
+      </c>
+      <c r="L23" s="37" t="s">
         <v>457</v>
       </c>
-      <c r="L23" s="40"/>
-    </row>
-    <row r="24" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="M23" s="40"/>
+    </row>
+    <row r="24" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B24" s="46"/>
       <c r="C24" s="5">
         <v>2</v>
@@ -9526,12 +10660,15 @@
       <c r="J24" s="8" t="s">
         <v>96</v>
       </c>
-      <c r="K24" s="35" t="s">
+      <c r="K24" s="8" t="s">
+        <v>675</v>
+      </c>
+      <c r="L24" s="35" t="s">
         <v>458</v>
       </c>
-      <c r="L24" s="40"/>
-    </row>
-    <row r="25" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="M24" s="40"/>
+    </row>
+    <row r="25" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B25" s="46"/>
       <c r="C25" s="5">
         <v>3</v>
@@ -9557,12 +10694,15 @@
       <c r="J25" s="8" t="s">
         <v>419</v>
       </c>
-      <c r="K25" s="35" t="s">
+      <c r="K25" s="8" t="s">
+        <v>676</v>
+      </c>
+      <c r="L25" s="35" t="s">
         <v>459</v>
       </c>
-      <c r="L25" s="40"/>
-    </row>
-    <row r="26" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="M25" s="40"/>
+    </row>
+    <row r="26" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B26" s="46"/>
       <c r="C26" s="5">
         <v>4</v>
@@ -9588,12 +10728,15 @@
       <c r="J26" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="K26" s="35" t="s">
+      <c r="K26" s="8" t="s">
+        <v>677</v>
+      </c>
+      <c r="L26" s="35" t="s">
         <v>460</v>
       </c>
-      <c r="L26" s="40"/>
-    </row>
-    <row r="27" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="M26" s="40"/>
+    </row>
+    <row r="27" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B27" s="46"/>
       <c r="C27" s="23">
         <v>5</v>
@@ -9619,12 +10762,15 @@
       <c r="J27" s="8" t="s">
         <v>461</v>
       </c>
-      <c r="K27" s="35" t="s">
+      <c r="K27" s="8" t="s">
+        <v>678</v>
+      </c>
+      <c r="L27" s="35" t="s">
         <v>462</v>
       </c>
-      <c r="L27" s="40"/>
-    </row>
-    <row r="28" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="M27" s="40"/>
+    </row>
+    <row r="28" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B28" s="46"/>
       <c r="C28" s="5">
         <v>6</v>
@@ -9650,12 +10796,15 @@
       <c r="J28" s="8" t="s">
         <v>464</v>
       </c>
-      <c r="K28" s="35" t="s">
+      <c r="K28" s="8" t="s">
+        <v>679</v>
+      </c>
+      <c r="L28" s="35" t="s">
         <v>465</v>
       </c>
-      <c r="L28" s="40"/>
-    </row>
-    <row r="29" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="M28" s="40"/>
+    </row>
+    <row r="29" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B29" s="46"/>
       <c r="C29" s="5">
         <v>7</v>
@@ -9681,12 +10830,15 @@
       <c r="J29" s="8" t="s">
         <v>466</v>
       </c>
-      <c r="K29" s="35" t="s">
+      <c r="K29" s="8" t="s">
+        <v>680</v>
+      </c>
+      <c r="L29" s="35" t="s">
         <v>467</v>
       </c>
-      <c r="L29" s="40"/>
-    </row>
-    <row r="30" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="M29" s="40"/>
+    </row>
+    <row r="30" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B30" s="46"/>
       <c r="C30" s="5">
         <v>8</v>
@@ -9712,12 +10864,15 @@
       <c r="J30" s="8" t="s">
         <v>468</v>
       </c>
-      <c r="K30" s="35" t="s">
+      <c r="K30" s="8" t="s">
+        <v>681</v>
+      </c>
+      <c r="L30" s="35" t="s">
         <v>469</v>
       </c>
-      <c r="L30" s="40"/>
-    </row>
-    <row r="31" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="M30" s="40"/>
+    </row>
+    <row r="31" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B31" s="46"/>
       <c r="C31" s="5">
         <v>9</v>
@@ -9743,12 +10898,15 @@
       <c r="J31" s="8" t="s">
         <v>470</v>
       </c>
-      <c r="K31" s="35" t="s">
+      <c r="K31" s="8" t="s">
+        <v>682</v>
+      </c>
+      <c r="L31" s="35" t="s">
         <v>471</v>
       </c>
-      <c r="L31" s="40"/>
-    </row>
-    <row r="32" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="M31" s="40"/>
+    </row>
+    <row r="32" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B32" s="47"/>
       <c r="C32" s="10">
         <v>10</v>
@@ -9774,12 +10932,15 @@
       <c r="J32" s="12" t="s">
         <v>67</v>
       </c>
-      <c r="K32" s="36" t="s">
+      <c r="K32" s="12" t="s">
+        <v>683</v>
+      </c>
+      <c r="L32" s="36" t="s">
         <v>473</v>
       </c>
-      <c r="L32" s="40"/>
-    </row>
-    <row r="33" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="M32" s="40"/>
+    </row>
+    <row r="33" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B33" s="48">
         <v>4</v>
       </c>
@@ -9807,12 +10968,15 @@
       <c r="J33" s="15" t="s">
         <v>91</v>
       </c>
-      <c r="K33" s="37" t="s">
+      <c r="K33" s="15" t="s">
+        <v>684</v>
+      </c>
+      <c r="L33" s="37" t="s">
         <v>474</v>
       </c>
-      <c r="L33" s="40"/>
-    </row>
-    <row r="34" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="M33" s="40"/>
+    </row>
+    <row r="34" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B34" s="46"/>
       <c r="C34" s="5">
         <v>2</v>
@@ -9838,12 +11002,15 @@
       <c r="J34" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="K34" s="35" t="s">
+      <c r="K34" s="8" t="s">
+        <v>685</v>
+      </c>
+      <c r="L34" s="35" t="s">
         <v>475</v>
       </c>
-      <c r="L34" s="40"/>
-    </row>
-    <row r="35" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="M34" s="40"/>
+    </row>
+    <row r="35" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B35" s="46"/>
       <c r="C35" s="5">
         <v>3</v>
@@ -9869,12 +11036,15 @@
       <c r="J35" s="8" t="s">
         <v>476</v>
       </c>
-      <c r="K35" s="35" t="s">
+      <c r="K35" s="8" t="s">
+        <v>686</v>
+      </c>
+      <c r="L35" s="35" t="s">
         <v>477</v>
       </c>
-      <c r="L35" s="40"/>
-    </row>
-    <row r="36" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="M35" s="40"/>
+    </row>
+    <row r="36" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B36" s="46"/>
       <c r="C36" s="5">
         <v>4</v>
@@ -9900,12 +11070,15 @@
       <c r="J36" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="K36" s="35" t="s">
+      <c r="K36" s="8" t="s">
+        <v>687</v>
+      </c>
+      <c r="L36" s="35" t="s">
         <v>478</v>
       </c>
-      <c r="L36" s="40"/>
-    </row>
-    <row r="37" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="M36" s="40"/>
+    </row>
+    <row r="37" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B37" s="46"/>
       <c r="C37" s="23">
         <v>5</v>
@@ -9931,12 +11104,15 @@
       <c r="J37" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="K37" s="35" t="s">
+      <c r="K37" s="8" t="s">
+        <v>688</v>
+      </c>
+      <c r="L37" s="35" t="s">
         <v>481</v>
       </c>
-      <c r="L37" s="40"/>
-    </row>
-    <row r="38" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="M37" s="40"/>
+    </row>
+    <row r="38" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B38" s="46"/>
       <c r="C38" s="5">
         <v>6</v>
@@ -9962,12 +11138,15 @@
       <c r="J38" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="K38" s="35" t="s">
+      <c r="K38" s="8" t="s">
+        <v>689</v>
+      </c>
+      <c r="L38" s="35" t="s">
         <v>483</v>
       </c>
-      <c r="L38" s="40"/>
-    </row>
-    <row r="39" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="M38" s="40"/>
+    </row>
+    <row r="39" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B39" s="46"/>
       <c r="C39" s="5">
         <v>7</v>
@@ -9993,12 +11172,15 @@
       <c r="J39" s="8" t="s">
         <v>485</v>
       </c>
-      <c r="K39" s="35" t="s">
+      <c r="K39" s="8" t="s">
+        <v>690</v>
+      </c>
+      <c r="L39" s="35" t="s">
         <v>486</v>
       </c>
-      <c r="L39" s="40"/>
-    </row>
-    <row r="40" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="M39" s="40"/>
+    </row>
+    <row r="40" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B40" s="46"/>
       <c r="C40" s="5">
         <v>8</v>
@@ -10024,12 +11206,15 @@
       <c r="J40" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="K40" s="35" t="s">
+      <c r="K40" s="8" t="s">
+        <v>691</v>
+      </c>
+      <c r="L40" s="35" t="s">
         <v>488</v>
       </c>
-      <c r="L40" s="40"/>
-    </row>
-    <row r="41" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="M40" s="40"/>
+    </row>
+    <row r="41" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B41" s="46"/>
       <c r="C41" s="5">
         <v>9</v>
@@ -10055,12 +11240,15 @@
       <c r="J41" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="K41" s="35" t="s">
+      <c r="K41" s="8" t="s">
+        <v>692</v>
+      </c>
+      <c r="L41" s="35" t="s">
         <v>490</v>
       </c>
-      <c r="L41" s="40"/>
-    </row>
-    <row r="42" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="M41" s="40"/>
+    </row>
+    <row r="42" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B42" s="47"/>
       <c r="C42" s="10">
         <v>10</v>
@@ -10086,12 +11274,15 @@
       <c r="J42" s="12" t="s">
         <v>132</v>
       </c>
-      <c r="K42" s="36" t="s">
+      <c r="K42" s="12" t="s">
+        <v>693</v>
+      </c>
+      <c r="L42" s="36" t="s">
         <v>491</v>
       </c>
-      <c r="L42" s="40"/>
-    </row>
-    <row r="43" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="M42" s="40"/>
+    </row>
+    <row r="43" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B43" s="48">
         <v>5</v>
       </c>
@@ -10119,12 +11310,15 @@
       <c r="J43" s="15" t="s">
         <v>91</v>
       </c>
-      <c r="K43" s="37" t="s">
+      <c r="K43" s="15" t="s">
+        <v>694</v>
+      </c>
+      <c r="L43" s="37" t="s">
         <v>492</v>
       </c>
-      <c r="L43" s="40"/>
-    </row>
-    <row r="44" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="M43" s="40"/>
+    </row>
+    <row r="44" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B44" s="46"/>
       <c r="C44" s="5">
         <v>2</v>
@@ -10150,12 +11344,15 @@
       <c r="J44" s="8" t="s">
         <v>96</v>
       </c>
-      <c r="K44" s="35" t="s">
+      <c r="K44" s="8" t="s">
+        <v>695</v>
+      </c>
+      <c r="L44" s="35" t="s">
         <v>493</v>
       </c>
-      <c r="L44" s="40"/>
-    </row>
-    <row r="45" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="M44" s="40"/>
+    </row>
+    <row r="45" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B45" s="46"/>
       <c r="C45" s="5">
         <v>3</v>
@@ -10181,12 +11378,15 @@
       <c r="J45" s="8" t="s">
         <v>476</v>
       </c>
-      <c r="K45" s="35" t="s">
+      <c r="K45" s="8" t="s">
+        <v>696</v>
+      </c>
+      <c r="L45" s="35" t="s">
         <v>494</v>
       </c>
-      <c r="L45" s="40"/>
-    </row>
-    <row r="46" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="M45" s="40"/>
+    </row>
+    <row r="46" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B46" s="46"/>
       <c r="C46" s="5">
         <v>4</v>
@@ -10212,12 +11412,15 @@
       <c r="J46" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="K46" s="35" t="s">
+      <c r="K46" s="8" t="s">
+        <v>697</v>
+      </c>
+      <c r="L46" s="35" t="s">
         <v>495</v>
       </c>
-      <c r="L46" s="40"/>
-    </row>
-    <row r="47" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="M46" s="40"/>
+    </row>
+    <row r="47" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B47" s="46"/>
       <c r="C47" s="23">
         <v>5</v>
@@ -10243,12 +11446,15 @@
       <c r="J47" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="K47" s="35" t="s">
+      <c r="K47" s="8" t="s">
+        <v>698</v>
+      </c>
+      <c r="L47" s="35" t="s">
         <v>496</v>
       </c>
-      <c r="L47" s="40"/>
-    </row>
-    <row r="48" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="M47" s="40"/>
+    </row>
+    <row r="48" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B48" s="46"/>
       <c r="C48" s="5">
         <v>6</v>
@@ -10274,12 +11480,15 @@
       <c r="J48" s="8" t="s">
         <v>464</v>
       </c>
-      <c r="K48" s="35" t="s">
+      <c r="K48" s="8" t="s">
+        <v>699</v>
+      </c>
+      <c r="L48" s="35" t="s">
         <v>498</v>
       </c>
-      <c r="L48" s="40"/>
-    </row>
-    <row r="49" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="M48" s="40"/>
+    </row>
+    <row r="49" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B49" s="46"/>
       <c r="C49" s="5">
         <v>7</v>
@@ -10305,12 +11514,15 @@
       <c r="J49" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="K49" s="35" t="s">
+      <c r="K49" s="8" t="s">
+        <v>700</v>
+      </c>
+      <c r="L49" s="35" t="s">
         <v>499</v>
       </c>
-      <c r="L49" s="40"/>
-    </row>
-    <row r="50" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="M49" s="40"/>
+    </row>
+    <row r="50" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B50" s="46"/>
       <c r="C50" s="5">
         <v>8</v>
@@ -10336,12 +11548,15 @@
       <c r="J50" s="8" t="s">
         <v>468</v>
       </c>
-      <c r="K50" s="35" t="s">
+      <c r="K50" s="8" t="s">
+        <v>701</v>
+      </c>
+      <c r="L50" s="35" t="s">
         <v>500</v>
       </c>
-      <c r="L50" s="40"/>
-    </row>
-    <row r="51" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="M50" s="40"/>
+    </row>
+    <row r="51" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B51" s="46"/>
       <c r="C51" s="5">
         <v>9</v>
@@ -10367,12 +11582,15 @@
       <c r="J51" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="K51" s="35" t="s">
+      <c r="K51" s="8" t="s">
+        <v>702</v>
+      </c>
+      <c r="L51" s="35" t="s">
         <v>501</v>
       </c>
-      <c r="L51" s="40"/>
-    </row>
-    <row r="52" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="M51" s="40"/>
+    </row>
+    <row r="52" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B52" s="49"/>
       <c r="C52" s="5">
         <v>10</v>
@@ -10398,426 +11616,429 @@
       <c r="J52" s="17" t="s">
         <v>33</v>
       </c>
-      <c r="K52" s="38" t="s">
+      <c r="K52" s="17" t="s">
+        <v>703</v>
+      </c>
+      <c r="L52" s="38" t="s">
         <v>502</v>
       </c>
-      <c r="L52" s="41"/>
-    </row>
-    <row r="53" spans="2:12" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="M52" s="41"/>
+    </row>
+    <row r="53" spans="2:13" ht="15" thickTop="1" x14ac:dyDescent="0.35">
       <c r="C53" s="21"/>
-      <c r="L53" s="18"/>
-    </row>
-    <row r="54" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="M53" s="18"/>
+    </row>
+    <row r="54" spans="2:13" x14ac:dyDescent="0.35">
       <c r="C54"/>
       <c r="D54"/>
       <c r="E54"/>
       <c r="F54"/>
     </row>
-    <row r="55" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="55" spans="2:13" x14ac:dyDescent="0.35">
       <c r="C55"/>
       <c r="D55"/>
       <c r="E55"/>
       <c r="F55"/>
     </row>
-    <row r="56" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="56" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B56" s="20"/>
       <c r="C56" s="20"/>
       <c r="D56" s="20"/>
       <c r="E56" s="20"/>
       <c r="F56" s="20"/>
     </row>
-    <row r="57" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="57" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B57" s="20"/>
       <c r="C57" s="20"/>
       <c r="D57" s="20"/>
       <c r="E57" s="20"/>
       <c r="F57" s="20"/>
     </row>
-    <row r="58" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="58" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B58" s="20"/>
       <c r="C58" s="20"/>
       <c r="D58" s="20"/>
       <c r="E58" s="20"/>
       <c r="F58" s="20"/>
     </row>
-    <row r="59" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="59" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B59" s="20"/>
       <c r="C59" s="20"/>
       <c r="D59" s="20"/>
       <c r="E59" s="20"/>
       <c r="F59" s="20"/>
     </row>
-    <row r="60" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="60" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B60" s="20"/>
       <c r="C60" s="20"/>
       <c r="D60" s="20"/>
       <c r="E60" s="20"/>
       <c r="F60" s="20"/>
     </row>
-    <row r="61" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="61" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B61" s="20"/>
       <c r="C61" s="20"/>
       <c r="D61" s="20"/>
       <c r="E61" s="20"/>
       <c r="F61" s="20"/>
     </row>
-    <row r="62" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="62" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B62" s="20"/>
       <c r="C62" s="20"/>
       <c r="D62" s="20"/>
       <c r="E62" s="20"/>
       <c r="F62" s="20"/>
     </row>
-    <row r="63" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="63" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B63" s="20"/>
       <c r="C63" s="20"/>
       <c r="D63" s="20"/>
       <c r="E63" s="20"/>
       <c r="F63" s="20"/>
     </row>
-    <row r="64" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B64" s="20"/>
       <c r="C64" s="20"/>
       <c r="D64" s="20"/>
       <c r="E64" s="20"/>
       <c r="F64" s="20"/>
-      <c r="L64" s="19"/>
-    </row>
-    <row r="65" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="M64" s="19"/>
+    </row>
+    <row r="65" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B65" s="20"/>
       <c r="C65" s="20"/>
       <c r="D65" s="20"/>
       <c r="E65" s="20"/>
       <c r="F65" s="20"/>
-      <c r="L65" s="19"/>
-    </row>
-    <row r="66" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="M65" s="19"/>
+    </row>
+    <row r="66" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B66" s="20"/>
       <c r="C66" s="20"/>
       <c r="D66" s="20"/>
       <c r="E66" s="20"/>
       <c r="F66" s="20"/>
-      <c r="L66" s="19"/>
-    </row>
-    <row r="67" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="M66" s="19"/>
+    </row>
+    <row r="67" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B67" s="20"/>
       <c r="C67" s="20"/>
       <c r="D67" s="20"/>
       <c r="E67" s="20"/>
       <c r="F67" s="20"/>
-      <c r="L67" s="19"/>
-    </row>
-    <row r="68" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="M67" s="19"/>
+    </row>
+    <row r="68" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B68" s="20"/>
       <c r="C68" s="20"/>
       <c r="D68" s="20"/>
       <c r="E68" s="20"/>
       <c r="F68" s="20"/>
-      <c r="L68" s="19"/>
-    </row>
-    <row r="69" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="M68" s="19"/>
+    </row>
+    <row r="69" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B69" s="20"/>
       <c r="C69" s="20"/>
       <c r="D69" s="20"/>
       <c r="E69" s="20"/>
       <c r="F69" s="20"/>
-      <c r="L69" s="19"/>
-    </row>
-    <row r="70" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="M69" s="19"/>
+    </row>
+    <row r="70" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B70" s="20"/>
       <c r="C70" s="20"/>
       <c r="D70" s="20"/>
       <c r="E70" s="20"/>
       <c r="F70" s="20"/>
-      <c r="L70" s="19"/>
-    </row>
-    <row r="71" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="M70" s="19"/>
+    </row>
+    <row r="71" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B71" s="20"/>
       <c r="C71" s="20"/>
       <c r="D71" s="20"/>
       <c r="E71" s="20"/>
       <c r="F71" s="20"/>
-      <c r="L71" s="19"/>
-    </row>
-    <row r="72" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="M71" s="19"/>
+    </row>
+    <row r="72" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B72" s="20"/>
       <c r="C72" s="20"/>
       <c r="D72" s="20"/>
       <c r="E72" s="20"/>
       <c r="F72" s="20"/>
-      <c r="L72" s="19"/>
-    </row>
-    <row r="73" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="M72" s="19"/>
+    </row>
+    <row r="73" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B73" s="20"/>
       <c r="C73" s="20"/>
       <c r="D73" s="20"/>
       <c r="E73" s="20"/>
       <c r="F73" s="20"/>
-      <c r="L73" s="19"/>
-    </row>
-    <row r="74" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="M73" s="19"/>
+    </row>
+    <row r="74" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B74" s="20"/>
       <c r="C74" s="20"/>
       <c r="D74" s="20"/>
       <c r="E74" s="20"/>
       <c r="F74" s="20"/>
-      <c r="L74" s="19"/>
-    </row>
-    <row r="75" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="M74" s="19"/>
+    </row>
+    <row r="75" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B75" s="20"/>
       <c r="C75" s="20"/>
       <c r="D75" s="20"/>
       <c r="E75" s="20"/>
       <c r="F75" s="20"/>
-      <c r="L75" s="19"/>
-    </row>
-    <row r="76" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="M75" s="19"/>
+    </row>
+    <row r="76" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B76" s="20"/>
       <c r="C76" s="20"/>
       <c r="D76" s="20"/>
       <c r="E76" s="20"/>
       <c r="F76" s="20"/>
-      <c r="L76" s="19"/>
-    </row>
-    <row r="77" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="M76" s="19"/>
+    </row>
+    <row r="77" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B77" s="20"/>
       <c r="C77" s="20"/>
       <c r="D77" s="20"/>
       <c r="E77" s="20"/>
       <c r="F77" s="20"/>
-      <c r="L77" s="19"/>
-    </row>
-    <row r="78" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="M77" s="19"/>
+    </row>
+    <row r="78" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B78" s="20"/>
       <c r="C78" s="20"/>
       <c r="D78" s="20"/>
       <c r="E78" s="20"/>
       <c r="F78" s="20"/>
-      <c r="L78" s="19"/>
-    </row>
-    <row r="79" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="M78" s="19"/>
+    </row>
+    <row r="79" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B79" s="20"/>
       <c r="C79" s="20"/>
       <c r="D79" s="20"/>
       <c r="E79" s="20"/>
       <c r="F79" s="20"/>
-      <c r="L79" s="19"/>
-    </row>
-    <row r="80" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="M79" s="19"/>
+    </row>
+    <row r="80" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B80" s="20"/>
       <c r="C80" s="20"/>
       <c r="D80" s="20"/>
       <c r="E80" s="20"/>
       <c r="F80" s="20"/>
-      <c r="L80" s="19"/>
-    </row>
-    <row r="81" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="M80" s="19"/>
+    </row>
+    <row r="81" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B81" s="20"/>
       <c r="C81" s="20"/>
       <c r="D81" s="20"/>
       <c r="E81" s="20"/>
       <c r="F81" s="20"/>
-      <c r="L81" s="19"/>
-    </row>
-    <row r="82" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="M81" s="19"/>
+    </row>
+    <row r="82" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B82" s="20"/>
       <c r="C82" s="20"/>
       <c r="D82" s="20"/>
       <c r="E82" s="20"/>
       <c r="F82" s="20"/>
-      <c r="L82" s="19"/>
-    </row>
-    <row r="83" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="M82" s="19"/>
+    </row>
+    <row r="83" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B83" s="20"/>
       <c r="C83" s="20"/>
       <c r="D83" s="20"/>
       <c r="E83" s="20"/>
       <c r="F83" s="20"/>
-      <c r="L83" s="19"/>
-    </row>
-    <row r="84" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="M83" s="19"/>
+    </row>
+    <row r="84" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B84" s="20"/>
       <c r="C84" s="20"/>
       <c r="D84" s="20"/>
       <c r="E84" s="20"/>
       <c r="F84" s="20"/>
-      <c r="L84" s="19"/>
-    </row>
-    <row r="85" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="M84" s="19"/>
+    </row>
+    <row r="85" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B85" s="20"/>
       <c r="C85" s="20"/>
       <c r="D85" s="20"/>
       <c r="E85" s="20"/>
       <c r="F85" s="20"/>
-      <c r="L85" s="19"/>
-    </row>
-    <row r="86" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="M85" s="19"/>
+    </row>
+    <row r="86" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B86" s="20"/>
       <c r="C86" s="20"/>
       <c r="D86" s="20"/>
       <c r="E86" s="20"/>
       <c r="F86" s="20"/>
-      <c r="L86" s="19"/>
-    </row>
-    <row r="87" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="M86" s="19"/>
+    </row>
+    <row r="87" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B87" s="20"/>
       <c r="C87" s="20"/>
       <c r="D87" s="20"/>
       <c r="E87" s="20"/>
       <c r="F87" s="20"/>
-      <c r="L87" s="19"/>
-    </row>
-    <row r="88" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="M87" s="19"/>
+    </row>
+    <row r="88" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B88" s="20"/>
       <c r="C88" s="20"/>
       <c r="D88" s="20"/>
       <c r="E88" s="20"/>
       <c r="F88" s="20"/>
-      <c r="L88" s="19"/>
-    </row>
-    <row r="89" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="M88" s="19"/>
+    </row>
+    <row r="89" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B89" s="20"/>
       <c r="C89" s="20"/>
       <c r="D89" s="20"/>
       <c r="E89" s="20"/>
       <c r="F89" s="20"/>
-      <c r="L89" s="19"/>
-    </row>
-    <row r="90" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="M89" s="19"/>
+    </row>
+    <row r="90" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B90" s="20"/>
       <c r="C90" s="20"/>
       <c r="D90" s="20"/>
       <c r="E90" s="20"/>
       <c r="F90" s="20"/>
-      <c r="L90" s="19"/>
-    </row>
-    <row r="91" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="M90" s="19"/>
+    </row>
+    <row r="91" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B91" s="20"/>
       <c r="C91" s="20"/>
       <c r="D91" s="20"/>
       <c r="E91" s="20"/>
       <c r="F91" s="20"/>
-      <c r="L91" s="19"/>
-    </row>
-    <row r="92" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="M91" s="19"/>
+    </row>
+    <row r="92" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B92" s="20"/>
       <c r="C92" s="20"/>
       <c r="D92" s="20"/>
       <c r="E92" s="20"/>
       <c r="F92" s="20"/>
-      <c r="L92" s="19"/>
-    </row>
-    <row r="93" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="M92" s="19"/>
+    </row>
+    <row r="93" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B93" s="20"/>
       <c r="C93" s="20"/>
       <c r="D93" s="20"/>
       <c r="E93" s="20"/>
       <c r="F93" s="20"/>
-      <c r="L93" s="19"/>
-    </row>
-    <row r="94" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="M93" s="19"/>
+    </row>
+    <row r="94" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B94" s="20"/>
       <c r="C94" s="20"/>
       <c r="D94" s="20"/>
       <c r="E94" s="20"/>
       <c r="F94" s="20"/>
-      <c r="L94" s="19"/>
-    </row>
-    <row r="95" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="M94" s="19"/>
+    </row>
+    <row r="95" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B95" s="20"/>
       <c r="C95" s="20"/>
       <c r="D95" s="20"/>
       <c r="E95" s="20"/>
       <c r="F95" s="20"/>
-      <c r="L95" s="19"/>
-    </row>
-    <row r="96" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="M95" s="19"/>
+    </row>
+    <row r="96" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B96" s="20"/>
       <c r="C96" s="20"/>
       <c r="D96" s="20"/>
       <c r="E96" s="20"/>
       <c r="F96" s="20"/>
-      <c r="L96" s="19"/>
-    </row>
-    <row r="97" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="M96" s="19"/>
+    </row>
+    <row r="97" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B97" s="20"/>
       <c r="C97" s="20"/>
       <c r="D97" s="20"/>
       <c r="E97" s="20"/>
       <c r="F97" s="20"/>
-      <c r="L97" s="19"/>
-    </row>
-    <row r="98" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="M97" s="19"/>
+    </row>
+    <row r="98" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B98" s="20"/>
       <c r="C98" s="20"/>
       <c r="D98" s="20"/>
       <c r="E98" s="20"/>
       <c r="F98" s="20"/>
-      <c r="L98" s="19"/>
-    </row>
-    <row r="99" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="M98" s="19"/>
+    </row>
+    <row r="99" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B99" s="20"/>
       <c r="C99" s="20"/>
       <c r="D99" s="20"/>
       <c r="E99" s="20"/>
       <c r="F99" s="20"/>
-      <c r="L99" s="19"/>
-    </row>
-    <row r="100" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="M99" s="19"/>
+    </row>
+    <row r="100" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B100" s="20"/>
       <c r="C100" s="20"/>
       <c r="D100" s="20"/>
       <c r="E100" s="20"/>
       <c r="F100" s="20"/>
-      <c r="L100" s="19"/>
-    </row>
-    <row r="101" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="M100" s="19"/>
+    </row>
+    <row r="101" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B101" s="20"/>
       <c r="C101" s="20"/>
       <c r="D101" s="20"/>
       <c r="E101" s="20"/>
       <c r="F101" s="20"/>
-      <c r="L101" s="19"/>
-    </row>
-    <row r="102" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="M101" s="19"/>
+    </row>
+    <row r="102" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B102" s="20"/>
       <c r="C102" s="20"/>
       <c r="D102" s="20"/>
       <c r="E102" s="20"/>
       <c r="F102" s="20"/>
-      <c r="L102" s="19"/>
-    </row>
-    <row r="103" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="M102" s="19"/>
+    </row>
+    <row r="103" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B103" s="20"/>
       <c r="C103" s="20"/>
       <c r="D103" s="20"/>
       <c r="E103" s="20"/>
       <c r="F103" s="20"/>
-      <c r="L103" s="19"/>
-    </row>
-    <row r="104" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="M103" s="19"/>
+    </row>
+    <row r="104" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B104" s="20"/>
       <c r="C104" s="20"/>
       <c r="D104" s="20"/>
       <c r="E104" s="20"/>
       <c r="F104" s="20"/>
-      <c r="L104" s="19"/>
-    </row>
-    <row r="105" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="M104" s="19"/>
+    </row>
+    <row r="105" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B105" s="20"/>
       <c r="C105" s="20"/>
       <c r="D105" s="20"/>
       <c r="E105" s="20"/>
       <c r="F105" s="20"/>
-      <c r="L105" s="19"/>
-    </row>
-    <row r="106" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="M105" s="19"/>
+    </row>
+    <row r="106" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B106" s="20"/>
       <c r="C106" s="20"/>
       <c r="D106" s="20"/>
       <c r="E106" s="20"/>
       <c r="F106" s="20"/>
-      <c r="L106" s="19"/>
+      <c r="M106" s="19"/>
     </row>
   </sheetData>
   <mergeCells count="5">
